--- a/research/traditional_assets/database/data/gabon/gabon_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/gabon/gabon_oil_gas_production_and_exploration.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtpa_ec" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.106</v>
+        <v>-0.05110000000000001</v>
+      </c>
+      <c r="E2">
+        <v>0.745</v>
       </c>
       <c r="G2">
-        <v>0.1102164966899267</v>
+        <v>0.534845496383958</v>
       </c>
       <c r="H2">
-        <v>0.1102164966899267</v>
+        <v>0.534845496383958</v>
       </c>
       <c r="I2">
-        <v>-0.01043120415101092</v>
+        <v>0.2882971729125576</v>
       </c>
       <c r="J2">
-        <v>-0.01043120415101092</v>
+        <v>0.1826019183640165</v>
       </c>
       <c r="K2">
-        <v>-16.1</v>
+        <v>44.4</v>
       </c>
       <c r="L2">
-        <v>-0.02880658436213992</v>
+        <v>0.07297830374753451</v>
       </c>
       <c r="M2">
-        <v>20.3</v>
+        <v>75</v>
       </c>
       <c r="N2">
-        <v>0.02874539790427641</v>
+        <v>0.09869719699960522</v>
       </c>
       <c r="O2">
-        <v>-1.260869565217391</v>
+        <v>1.689189189189189</v>
       </c>
       <c r="P2">
-        <v>20.3</v>
+        <v>75</v>
       </c>
       <c r="Q2">
-        <v>0.02874539790427641</v>
+        <v>0.09869719699960522</v>
       </c>
       <c r="R2">
-        <v>-1.260869565217391</v>
+        <v>1.689189189189189</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>502.1</v>
+        <v>948.3</v>
       </c>
       <c r="V2">
-        <v>0.710988388558482</v>
+        <v>1.247927358863008</v>
       </c>
       <c r="W2">
-        <v>-0.00803112685189804</v>
+        <v>0.02512306908843999</v>
       </c>
       <c r="X2">
-        <v>0.1566616008597872</v>
+        <v>0.2684707776582099</v>
       </c>
       <c r="Y2">
-        <v>-0.1646927277116852</v>
+        <v>-0.2433477085697699</v>
       </c>
       <c r="Z2">
-        <v>0.4102319436288901</v>
+        <v>0.4712260862830145</v>
       </c>
       <c r="AA2">
-        <v>-0.004279213153258955</v>
+        <v>0.08604678733844599</v>
       </c>
       <c r="AB2">
-        <v>0.1532771158167179</v>
+        <v>0.2600756485648377</v>
       </c>
       <c r="AC2">
-        <v>-0.1575563289699769</v>
+        <v>-0.1740288612263917</v>
       </c>
       <c r="AD2">
-        <v>25.9</v>
+        <v>39.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>25.9</v>
+        <v>39.2</v>
       </c>
       <c r="AG2">
-        <v>-476.2</v>
+        <v>-909.0999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.03537768064472066</v>
+        <v>0.04905518708547116</v>
       </c>
       <c r="AI2">
-        <v>0.01444345304483605</v>
+        <v>0.02198665096191598</v>
       </c>
       <c r="AJ2">
-        <v>-2.070434782608696</v>
+        <v>6.093163538873997</v>
       </c>
       <c r="AK2">
-        <v>-0.3688327782511038</v>
+        <v>-1.089264318236281</v>
       </c>
       <c r="AL2">
-        <v>5.04</v>
+        <v>0.963</v>
       </c>
       <c r="AM2">
-        <v>5.04</v>
+        <v>0.963</v>
       </c>
       <c r="AN2">
-        <v>0.1628930817610063</v>
+        <v>0.1215127092374458</v>
       </c>
       <c r="AO2">
-        <v>-1.156746031746032</v>
+        <v>182.1391484942887</v>
       </c>
       <c r="AP2">
-        <v>-2.99496855345912</v>
+        <v>-2.818040917544947</v>
       </c>
       <c r="AQ2">
-        <v>-1.156746031746032</v>
+        <v>182.1391484942887</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Total Gabon (ENXTPA:EC)</t>
+          <t>TotalEnergies EP Gabon Société anonyme (ENXTPA:EC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,43 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.106</v>
+        <v>-0.05110000000000001</v>
+      </c>
+      <c r="E3">
+        <v>0.745</v>
       </c>
       <c r="G3">
-        <v>0.1102164966899267</v>
+        <v>0.534845496383958</v>
       </c>
       <c r="H3">
-        <v>0.1102164966899267</v>
+        <v>0.534845496383958</v>
       </c>
       <c r="I3">
-        <v>-0.01043120415101092</v>
+        <v>0.2882971729125576</v>
       </c>
       <c r="J3">
-        <v>-0.01043120415101092</v>
+        <v>0.1826019183640165</v>
       </c>
       <c r="K3">
-        <v>-16.1</v>
+        <v>44.4</v>
       </c>
       <c r="L3">
-        <v>-0.02880658436213992</v>
+        <v>0.07297830374753451</v>
       </c>
       <c r="M3">
-        <v>20.3</v>
+        <v>75</v>
       </c>
       <c r="N3">
-        <v>0.02874539790427641</v>
+        <v>0.09869719699960522</v>
       </c>
       <c r="O3">
-        <v>-1.260869565217391</v>
+        <v>1.689189189189189</v>
       </c>
       <c r="P3">
-        <v>20.3</v>
+        <v>75</v>
       </c>
       <c r="Q3">
-        <v>0.02874539790427641</v>
+        <v>0.09869719699960522</v>
       </c>
       <c r="R3">
-        <v>-1.260869565217391</v>
+        <v>1.689189189189189</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +772,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>502.1</v>
+        <v>948.3</v>
       </c>
       <c r="V3">
-        <v>0.710988388558482</v>
+        <v>1.247927358863008</v>
       </c>
       <c r="W3">
-        <v>-0.00803112685189804</v>
+        <v>0.02512306908843999</v>
       </c>
       <c r="X3">
-        <v>0.1566616008597872</v>
+        <v>0.2684707776582099</v>
       </c>
       <c r="Y3">
-        <v>-0.1646927277116852</v>
+        <v>-0.2433477085697699</v>
       </c>
       <c r="Z3">
-        <v>0.4102319436288901</v>
+        <v>0.4712260862830145</v>
       </c>
       <c r="AA3">
-        <v>-0.004279213153258955</v>
+        <v>0.08604678733844599</v>
       </c>
       <c r="AB3">
-        <v>0.1532771158167179</v>
+        <v>0.2600756485648377</v>
       </c>
       <c r="AC3">
-        <v>-0.1575563289699769</v>
+        <v>-0.1740288612263917</v>
       </c>
       <c r="AD3">
-        <v>25.9</v>
+        <v>39.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>25.9</v>
+        <v>39.2</v>
       </c>
       <c r="AG3">
-        <v>-476.2</v>
+        <v>-909.0999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.03537768064472066</v>
+        <v>0.04905518708547116</v>
       </c>
       <c r="AI3">
-        <v>0.01444345304483605</v>
+        <v>0.02198665096191598</v>
       </c>
       <c r="AJ3">
-        <v>-2.070434782608696</v>
+        <v>6.093163538873997</v>
       </c>
       <c r="AK3">
-        <v>-0.3688327782511038</v>
+        <v>-1.089264318236281</v>
       </c>
       <c r="AL3">
-        <v>5.04</v>
+        <v>0.963</v>
       </c>
       <c r="AM3">
-        <v>5.04</v>
+        <v>0.963</v>
       </c>
       <c r="AN3">
-        <v>0.1628930817610063</v>
+        <v>0.1215127092374458</v>
       </c>
       <c r="AO3">
-        <v>-1.156746031746032</v>
+        <v>182.1391484942887</v>
       </c>
       <c r="AP3">
-        <v>-2.99496855345912</v>
+        <v>-2.818040917544947</v>
       </c>
       <c r="AQ3">
-        <v>-1.156746031746032</v>
+        <v>182.1391484942887</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TotalEnergies EP Gabon Société anonyme (ENXTPA:EC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTPA:EC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oil/Gas (Production and Exploration)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0490551870854712</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>759.9</v>
+      </c>
+      <c r="H2">
+        <v>799.115803219769</v>
+      </c>
+      <c r="I2">
+        <v>-149.2</v>
+      </c>
+      <c r="J2">
+        <v>-149.184196780231</v>
+      </c>
+      <c r="K2">
+        <v>39.2</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.260075648564838</v>
+      </c>
+      <c r="N2">
+        <v>0.260466400719478</v>
+      </c>
+      <c r="O2">
+        <v>0.0973343577981651</v>
+      </c>
+      <c r="P2">
+        <v>0.03199</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.26847077765821</v>
+      </c>
+      <c r="T2">
+        <v>0.260466400719478</v>
+      </c>
+      <c r="U2">
+        <v>1.21798669987994</v>
+      </c>
+      <c r="V2">
+        <v>1.17553800548526</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>759.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.1885659159339335</v>
+      </c>
+      <c r="AC2">
+        <v>0.1390490825688074</v>
+      </c>
+      <c r="AD2">
+        <v>0.3</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>322.6</v>
+      </c>
+      <c r="AH2">
+        <v>147.3</v>
+      </c>
+      <c r="AI2">
+        <v>43.39999999999995</v>
+      </c>
+      <c r="AJ2">
+        <v>39.2</v>
+      </c>
+      <c r="AK2">
+        <v>39.2</v>
+      </c>
+      <c r="AL2">
+        <v>0.963</v>
+      </c>
+      <c r="AM2">
+        <v>39.2</v>
+      </c>
+      <c r="AN2">
+        <v>948.3</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2604664007194779</v>
+      </c>
+      <c r="C2">
+        <v>799.1158032197693</v>
+      </c>
+      <c r="D2">
+        <v>-149.1841967802306</v>
+      </c>
+      <c r="E2">
+        <v>-39.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>948.3</v>
+      </c>
+      <c r="H2">
+        <v>759.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>322.6</v>
+      </c>
+      <c r="K2">
+        <v>147.3</v>
+      </c>
+      <c r="L2">
+        <v>175.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>175.3</v>
+      </c>
+      <c r="O2">
+        <v>52.59000000000001</v>
+      </c>
+      <c r="P2">
+        <v>122.71</v>
+      </c>
+      <c r="Q2">
+        <v>270.01</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2604664007194779</v>
+      </c>
+      <c r="T2">
+        <v>1.175538005485263</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.03199</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2597333015173195</v>
+      </c>
+      <c r="C3">
+        <v>791.095151679825</v>
+      </c>
+      <c r="D3">
+        <v>-149.2138483201749</v>
+      </c>
+      <c r="E3">
+        <v>-31.209</v>
+      </c>
+      <c r="F3">
+        <v>7.991000000000001</v>
+      </c>
+      <c r="G3">
+        <v>948.3</v>
+      </c>
+      <c r="H3">
+        <v>759.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>322.6</v>
+      </c>
+      <c r="K3">
+        <v>147.3</v>
+      </c>
+      <c r="L3">
+        <v>175.3</v>
+      </c>
+      <c r="M3">
+        <v>0.3651887000000001</v>
+      </c>
+      <c r="N3">
+        <v>174.9348113</v>
+      </c>
+      <c r="O3">
+        <v>52.48044339000001</v>
+      </c>
+      <c r="P3">
+        <v>122.45436791</v>
+      </c>
+      <c r="Q3">
+        <v>269.75436791</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2620337389063833</v>
+      </c>
+      <c r="T3">
+        <v>1.183849890372533</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.3</v>
+      </c>
+      <c r="W3">
+        <v>0.03199</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>480.0258058368179</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2590002023151611</v>
+      </c>
+      <c r="C4">
+        <v>783.0744883505811</v>
+      </c>
+      <c r="D4">
+        <v>-149.243511649419</v>
+      </c>
+      <c r="E4">
+        <v>-23.218</v>
+      </c>
+      <c r="F4">
+        <v>15.982</v>
+      </c>
+      <c r="G4">
+        <v>948.3</v>
+      </c>
+      <c r="H4">
+        <v>759.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>322.6</v>
+      </c>
+      <c r="K4">
+        <v>147.3</v>
+      </c>
+      <c r="L4">
+        <v>175.3</v>
+      </c>
+      <c r="M4">
+        <v>0.7303774000000002</v>
+      </c>
+      <c r="N4">
+        <v>174.5696226</v>
+      </c>
+      <c r="O4">
+        <v>52.37088678000001</v>
+      </c>
+      <c r="P4">
+        <v>122.19873582</v>
+      </c>
+      <c r="Q4">
+        <v>269.49873582</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2636330635868991</v>
+      </c>
+      <c r="T4">
+        <v>1.192331405563624</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.3</v>
+      </c>
+      <c r="W4">
+        <v>0.03199</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>240.012902918409</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2582671031130027</v>
+      </c>
+      <c r="C5">
+        <v>775.0538132250048</v>
+      </c>
+      <c r="D5">
+        <v>-149.2731867749952</v>
+      </c>
+      <c r="E5">
+        <v>-15.227</v>
+      </c>
+      <c r="F5">
+        <v>23.973</v>
+      </c>
+      <c r="G5">
+        <v>948.3</v>
+      </c>
+      <c r="H5">
+        <v>759.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>322.6</v>
+      </c>
+      <c r="K5">
+        <v>147.3</v>
+      </c>
+      <c r="L5">
+        <v>175.3</v>
+      </c>
+      <c r="M5">
+        <v>1.0955661</v>
+      </c>
+      <c r="N5">
+        <v>174.2044339</v>
+      </c>
+      <c r="O5">
+        <v>52.26133017000001</v>
+      </c>
+      <c r="P5">
+        <v>121.94310373</v>
+      </c>
+      <c r="Q5">
+        <v>269.24310373</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2652653640340233</v>
+      </c>
+      <c r="T5">
+        <v>1.200987797356593</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.3</v>
+      </c>
+      <c r="W5">
+        <v>0.03199</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>160.008601945606</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2575340039108441</v>
+      </c>
+      <c r="C6">
+        <v>767.0331262960582</v>
+      </c>
+      <c r="D6">
+        <v>-149.3028737039417</v>
+      </c>
+      <c r="E6">
+        <v>-7.236000000000001</v>
+      </c>
+      <c r="F6">
+        <v>31.964</v>
+      </c>
+      <c r="G6">
+        <v>948.3</v>
+      </c>
+      <c r="H6">
+        <v>759.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>322.6</v>
+      </c>
+      <c r="K6">
+        <v>147.3</v>
+      </c>
+      <c r="L6">
+        <v>175.3</v>
+      </c>
+      <c r="M6">
+        <v>1.4607548</v>
+      </c>
+      <c r="N6">
+        <v>173.8392452</v>
+      </c>
+      <c r="O6">
+        <v>52.15177356000002</v>
+      </c>
+      <c r="P6">
+        <v>121.68747164</v>
+      </c>
+      <c r="Q6">
+        <v>268.98747164</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2669316707404626</v>
+      </c>
+      <c r="T6">
+        <v>1.20982453064525</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.3</v>
+      </c>
+      <c r="W6">
+        <v>0.03199</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>120.0064514592045</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2568009047086857</v>
+      </c>
+      <c r="C7">
+        <v>759.0124275566978</v>
+      </c>
+      <c r="D7">
+        <v>-149.332572443302</v>
+      </c>
+      <c r="E7">
+        <v>0.7550000000000026</v>
+      </c>
+      <c r="F7">
+        <v>39.95500000000001</v>
+      </c>
+      <c r="G7">
+        <v>948.3</v>
+      </c>
+      <c r="H7">
+        <v>759.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>322.6</v>
+      </c>
+      <c r="K7">
+        <v>147.3</v>
+      </c>
+      <c r="L7">
+        <v>175.3</v>
+      </c>
+      <c r="M7">
+        <v>1.8259435</v>
+      </c>
+      <c r="N7">
+        <v>173.4740565</v>
+      </c>
+      <c r="O7">
+        <v>52.04221695000001</v>
+      </c>
+      <c r="P7">
+        <v>121.43183955</v>
+      </c>
+      <c r="Q7">
+        <v>268.73183955</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2686330575880903</v>
+      </c>
+      <c r="T7">
+        <v>1.218847300424194</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.3</v>
+      </c>
+      <c r="W7">
+        <v>0.03199</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>96.0051611673636</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2560678055065273</v>
+      </c>
+      <c r="C8">
+        <v>750.9917169998745</v>
+      </c>
+      <c r="D8">
+        <v>-149.3622830001254</v>
+      </c>
+      <c r="E8">
+        <v>8.745999999999995</v>
+      </c>
+      <c r="F8">
+        <v>47.946</v>
+      </c>
+      <c r="G8">
+        <v>948.3</v>
+      </c>
+      <c r="H8">
+        <v>759.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>322.6</v>
+      </c>
+      <c r="K8">
+        <v>147.3</v>
+      </c>
+      <c r="L8">
+        <v>175.3</v>
+      </c>
+      <c r="M8">
+        <v>2.1911322</v>
+      </c>
+      <c r="N8">
+        <v>173.1088678</v>
+      </c>
+      <c r="O8">
+        <v>51.93266034000001</v>
+      </c>
+      <c r="P8">
+        <v>121.17620746</v>
+      </c>
+      <c r="Q8">
+        <v>268.47620746</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2703706441558801</v>
+      </c>
+      <c r="T8">
+        <v>1.228062044028222</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.3</v>
+      </c>
+      <c r="W8">
+        <v>0.03199</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>80.00430097280301</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2553347063043689</v>
+      </c>
+      <c r="C9">
+        <v>742.970994618533</v>
+      </c>
+      <c r="D9">
+        <v>-149.3920053814669</v>
+      </c>
+      <c r="E9">
+        <v>16.737</v>
+      </c>
+      <c r="F9">
+        <v>55.937</v>
+      </c>
+      <c r="G9">
+        <v>948.3</v>
+      </c>
+      <c r="H9">
+        <v>759.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>322.6</v>
+      </c>
+      <c r="K9">
+        <v>147.3</v>
+      </c>
+      <c r="L9">
+        <v>175.3</v>
+      </c>
+      <c r="M9">
+        <v>2.556320900000001</v>
+      </c>
+      <c r="N9">
+        <v>172.7436791</v>
+      </c>
+      <c r="O9">
+        <v>51.82310373000001</v>
+      </c>
+      <c r="P9">
+        <v>120.92057537</v>
+      </c>
+      <c r="Q9">
+        <v>268.22057537</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2721455981767408</v>
+      </c>
+      <c r="T9">
+        <v>1.237474954161368</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.3</v>
+      </c>
+      <c r="W9">
+        <v>0.03199</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>68.57511511954543</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2546016071022105</v>
+      </c>
+      <c r="C10">
+        <v>734.9502604056132</v>
+      </c>
+      <c r="D10">
+        <v>-149.4217395943867</v>
+      </c>
+      <c r="E10">
+        <v>24.728</v>
+      </c>
+      <c r="F10">
+        <v>63.928</v>
+      </c>
+      <c r="G10">
+        <v>948.3</v>
+      </c>
+      <c r="H10">
+        <v>759.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>322.6</v>
+      </c>
+      <c r="K10">
+        <v>147.3</v>
+      </c>
+      <c r="L10">
+        <v>175.3</v>
+      </c>
+      <c r="M10">
+        <v>2.921509600000001</v>
+      </c>
+      <c r="N10">
+        <v>172.3784904</v>
+      </c>
+      <c r="O10">
+        <v>51.71354712000001</v>
+      </c>
+      <c r="P10">
+        <v>120.66494328</v>
+      </c>
+      <c r="Q10">
+        <v>267.96494328</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2739591381545766</v>
+      </c>
+      <c r="T10">
+        <v>1.247092492775671</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.03199</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>60.00322572960224</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2538685079000521</v>
+      </c>
+      <c r="C11">
+        <v>726.9295143540488</v>
+      </c>
+      <c r="D11">
+        <v>-149.4514856459511</v>
+      </c>
+      <c r="E11">
+        <v>32.71899999999999</v>
+      </c>
+      <c r="F11">
+        <v>71.919</v>
+      </c>
+      <c r="G11">
+        <v>948.3</v>
+      </c>
+      <c r="H11">
+        <v>759.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>322.6</v>
+      </c>
+      <c r="K11">
+        <v>147.3</v>
+      </c>
+      <c r="L11">
+        <v>175.3</v>
+      </c>
+      <c r="M11">
+        <v>3.2866983</v>
+      </c>
+      <c r="N11">
+        <v>172.0133017</v>
+      </c>
+      <c r="O11">
+        <v>51.60399051000001</v>
+      </c>
+      <c r="P11">
+        <v>120.40931119</v>
+      </c>
+      <c r="Q11">
+        <v>267.70931119</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2758125361539033</v>
+      </c>
+      <c r="T11">
+        <v>1.256921405865012</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.3</v>
+      </c>
+      <c r="W11">
+        <v>0.03199</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>53.33620064853533</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2531354086978936</v>
+      </c>
+      <c r="C12">
+        <v>718.9087564567682</v>
+      </c>
+      <c r="D12">
+        <v>-149.4812435432318</v>
+      </c>
+      <c r="E12">
+        <v>40.71000000000001</v>
+      </c>
+      <c r="F12">
+        <v>79.91000000000001</v>
+      </c>
+      <c r="G12">
+        <v>948.3</v>
+      </c>
+      <c r="H12">
+        <v>759.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>322.6</v>
+      </c>
+      <c r="K12">
+        <v>147.3</v>
+      </c>
+      <c r="L12">
+        <v>175.3</v>
+      </c>
+      <c r="M12">
+        <v>3.651887000000001</v>
+      </c>
+      <c r="N12">
+        <v>171.648113</v>
+      </c>
+      <c r="O12">
+        <v>51.49443390000001</v>
+      </c>
+      <c r="P12">
+        <v>120.1536791</v>
+      </c>
+      <c r="Q12">
+        <v>267.4536791</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2777071207754374</v>
+      </c>
+      <c r="T12">
+        <v>1.266968739245228</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.3</v>
+      </c>
+      <c r="W12">
+        <v>0.03199</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>48.00258058368181</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2524023094957352</v>
+      </c>
+      <c r="C13">
+        <v>710.8879867066938</v>
+      </c>
+      <c r="D13">
+        <v>-149.5110132933061</v>
+      </c>
+      <c r="E13">
+        <v>48.70099999999999</v>
+      </c>
+      <c r="F13">
+        <v>87.901</v>
+      </c>
+      <c r="G13">
+        <v>948.3</v>
+      </c>
+      <c r="H13">
+        <v>759.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>322.6</v>
+      </c>
+      <c r="K13">
+        <v>147.3</v>
+      </c>
+      <c r="L13">
+        <v>175.3</v>
+      </c>
+      <c r="M13">
+        <v>4.0170757</v>
+      </c>
+      <c r="N13">
+        <v>171.2829243</v>
+      </c>
+      <c r="O13">
+        <v>51.38487729000001</v>
+      </c>
+      <c r="P13">
+        <v>119.89804701</v>
+      </c>
+      <c r="Q13">
+        <v>267.19804701</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2796442803322867</v>
+      </c>
+      <c r="T13">
+        <v>1.277241855398033</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.3</v>
+      </c>
+      <c r="W13">
+        <v>0.03199</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>43.63870962152892</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2516692102935767</v>
+      </c>
+      <c r="C14">
+        <v>702.867205096743</v>
+      </c>
+      <c r="D14">
+        <v>-149.540794903257</v>
+      </c>
+      <c r="E14">
+        <v>56.69199999999999</v>
+      </c>
+      <c r="F14">
+        <v>95.892</v>
+      </c>
+      <c r="G14">
+        <v>948.3</v>
+      </c>
+      <c r="H14">
+        <v>759.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>322.6</v>
+      </c>
+      <c r="K14">
+        <v>147.3</v>
+      </c>
+      <c r="L14">
+        <v>175.3</v>
+      </c>
+      <c r="M14">
+        <v>4.3822644</v>
+      </c>
+      <c r="N14">
+        <v>170.9177356</v>
+      </c>
+      <c r="O14">
+        <v>51.27532068000001</v>
+      </c>
+      <c r="P14">
+        <v>119.64241492</v>
+      </c>
+      <c r="Q14">
+        <v>266.94241492</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2816254662427008</v>
+      </c>
+      <c r="T14">
+        <v>1.287748451463402</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.3</v>
+      </c>
+      <c r="W14">
+        <v>0.03199</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>40.0021504864015</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2509361110914183</v>
+      </c>
+      <c r="C15">
+        <v>694.8464116198268</v>
+      </c>
+      <c r="D15">
+        <v>-149.5705883801731</v>
+      </c>
+      <c r="E15">
+        <v>64.68300000000001</v>
+      </c>
+      <c r="F15">
+        <v>103.883</v>
+      </c>
+      <c r="G15">
+        <v>948.3</v>
+      </c>
+      <c r="H15">
+        <v>759.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>322.6</v>
+      </c>
+      <c r="K15">
+        <v>147.3</v>
+      </c>
+      <c r="L15">
+        <v>175.3</v>
+      </c>
+      <c r="M15">
+        <v>4.747453100000001</v>
+      </c>
+      <c r="N15">
+        <v>170.5525469</v>
+      </c>
+      <c r="O15">
+        <v>51.16576407000001</v>
+      </c>
+      <c r="P15">
+        <v>119.38678283</v>
+      </c>
+      <c r="Q15">
+        <v>266.68678283</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2836521966568026</v>
+      </c>
+      <c r="T15">
+        <v>1.298496578472802</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.3</v>
+      </c>
+      <c r="W15">
+        <v>0.03199</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>36.92506198744753</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2502030118892598</v>
+      </c>
+      <c r="C16">
+        <v>686.8256062688511</v>
+      </c>
+      <c r="D16">
+        <v>-149.6003937311488</v>
+      </c>
+      <c r="E16">
+        <v>72.67400000000001</v>
+      </c>
+      <c r="F16">
+        <v>111.874</v>
+      </c>
+      <c r="G16">
+        <v>948.3</v>
+      </c>
+      <c r="H16">
+        <v>759.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>322.6</v>
+      </c>
+      <c r="K16">
+        <v>147.3</v>
+      </c>
+      <c r="L16">
+        <v>175.3</v>
+      </c>
+      <c r="M16">
+        <v>5.112641800000001</v>
+      </c>
+      <c r="N16">
+        <v>170.1873582</v>
+      </c>
+      <c r="O16">
+        <v>51.05620746000001</v>
+      </c>
+      <c r="P16">
+        <v>119.13115074</v>
+      </c>
+      <c r="Q16">
+        <v>266.43115074</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2857260603363486</v>
+      </c>
+      <c r="T16">
+        <v>1.309494661924281</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.3</v>
+      </c>
+      <c r="W16">
+        <v>0.03199</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>34.28755755977271</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2494699126871014</v>
+      </c>
+      <c r="C17">
+        <v>678.8047890367159</v>
+      </c>
+      <c r="D17">
+        <v>-149.630210963284</v>
+      </c>
+      <c r="E17">
+        <v>80.66499999999999</v>
+      </c>
+      <c r="F17">
+        <v>119.865</v>
+      </c>
+      <c r="G17">
+        <v>948.3</v>
+      </c>
+      <c r="H17">
+        <v>759.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>322.6</v>
+      </c>
+      <c r="K17">
+        <v>147.3</v>
+      </c>
+      <c r="L17">
+        <v>175.3</v>
+      </c>
+      <c r="M17">
+        <v>5.4778305</v>
+      </c>
+      <c r="N17">
+        <v>169.8221695</v>
+      </c>
+      <c r="O17">
+        <v>50.94665085</v>
+      </c>
+      <c r="P17">
+        <v>118.87551865</v>
+      </c>
+      <c r="Q17">
+        <v>266.17551865</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2878487208083546</v>
+      </c>
+      <c r="T17">
+        <v>1.320751523809913</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.3</v>
+      </c>
+      <c r="W17">
+        <v>0.03199</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>32.0017203891212</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.248736813484943</v>
+      </c>
+      <c r="C18">
+        <v>670.7839599163157</v>
+      </c>
+      <c r="D18">
+        <v>-149.6600400836843</v>
+      </c>
+      <c r="E18">
+        <v>88.65600000000001</v>
+      </c>
+      <c r="F18">
+        <v>127.856</v>
+      </c>
+      <c r="G18">
+        <v>948.3</v>
+      </c>
+      <c r="H18">
+        <v>759.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>322.6</v>
+      </c>
+      <c r="K18">
+        <v>147.3</v>
+      </c>
+      <c r="L18">
+        <v>175.3</v>
+      </c>
+      <c r="M18">
+        <v>5.843019200000001</v>
+      </c>
+      <c r="N18">
+        <v>169.4569808</v>
+      </c>
+      <c r="O18">
+        <v>50.83709424000001</v>
+      </c>
+      <c r="P18">
+        <v>118.61988656</v>
+      </c>
+      <c r="Q18">
+        <v>265.91988656</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2900219208154083</v>
+      </c>
+      <c r="T18">
+        <v>1.332276406216631</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.3</v>
+      </c>
+      <c r="W18">
+        <v>0.03199</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>30.00161286480112</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2480037142827846</v>
+      </c>
+      <c r="C19">
+        <v>662.763118900539</v>
+      </c>
+      <c r="D19">
+        <v>-149.689881099461</v>
+      </c>
+      <c r="E19">
+        <v>96.64700000000001</v>
+      </c>
+      <c r="F19">
+        <v>135.847</v>
+      </c>
+      <c r="G19">
+        <v>948.3</v>
+      </c>
+      <c r="H19">
+        <v>759.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>322.6</v>
+      </c>
+      <c r="K19">
+        <v>147.3</v>
+      </c>
+      <c r="L19">
+        <v>175.3</v>
+      </c>
+      <c r="M19">
+        <v>6.208207900000001</v>
+      </c>
+      <c r="N19">
+        <v>169.0917921</v>
+      </c>
+      <c r="O19">
+        <v>50.72753763000001</v>
+      </c>
+      <c r="P19">
+        <v>118.36425447</v>
+      </c>
+      <c r="Q19">
+        <v>265.66425447</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2922474870876923</v>
+      </c>
+      <c r="T19">
+        <v>1.34407899663315</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.3</v>
+      </c>
+      <c r="W19">
+        <v>0.03199</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>28.23681210804812</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2472706150806261</v>
+      </c>
+      <c r="C20">
+        <v>654.742265982269</v>
+      </c>
+      <c r="D20">
+        <v>-149.719734017731</v>
+      </c>
+      <c r="E20">
+        <v>104.638</v>
+      </c>
+      <c r="F20">
+        <v>143.838</v>
+      </c>
+      <c r="G20">
+        <v>948.3</v>
+      </c>
+      <c r="H20">
+        <v>759.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>322.6</v>
+      </c>
+      <c r="K20">
+        <v>147.3</v>
+      </c>
+      <c r="L20">
+        <v>175.3</v>
+      </c>
+      <c r="M20">
+        <v>6.573396600000001</v>
+      </c>
+      <c r="N20">
+        <v>168.7266034</v>
+      </c>
+      <c r="O20">
+        <v>50.61798102000001</v>
+      </c>
+      <c r="P20">
+        <v>118.10862238</v>
+      </c>
+      <c r="Q20">
+        <v>265.40862238</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2945273354641782</v>
+      </c>
+      <c r="T20">
+        <v>1.356169455108608</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.3</v>
+      </c>
+      <c r="W20">
+        <v>0.03199</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>26.66810032426767</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2465375158784677</v>
+      </c>
+      <c r="C21">
+        <v>646.7214011543831</v>
+      </c>
+      <c r="D21">
+        <v>-149.7495988456169</v>
+      </c>
+      <c r="E21">
+        <v>112.629</v>
+      </c>
+      <c r="F21">
+        <v>151.829</v>
+      </c>
+      <c r="G21">
+        <v>948.3</v>
+      </c>
+      <c r="H21">
+        <v>759.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>322.6</v>
+      </c>
+      <c r="K21">
+        <v>147.3</v>
+      </c>
+      <c r="L21">
+        <v>175.3</v>
+      </c>
+      <c r="M21">
+        <v>6.938585300000001</v>
+      </c>
+      <c r="N21">
+        <v>168.3614147</v>
+      </c>
+      <c r="O21">
+        <v>50.50842441000001</v>
+      </c>
+      <c r="P21">
+        <v>117.85299029</v>
+      </c>
+      <c r="Q21">
+        <v>265.15299029</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.29686347639317</v>
+      </c>
+      <c r="T21">
+        <v>1.368558443422967</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.3</v>
+      </c>
+      <c r="W21">
+        <v>0.03199</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>25.26451609667463</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2458044166763093</v>
+      </c>
+      <c r="C22">
+        <v>638.7005244097528</v>
+      </c>
+      <c r="D22">
+        <v>-149.7794755902471</v>
+      </c>
+      <c r="E22">
+        <v>120.62</v>
+      </c>
+      <c r="F22">
+        <v>159.82</v>
+      </c>
+      <c r="G22">
+        <v>948.3</v>
+      </c>
+      <c r="H22">
+        <v>759.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>322.6</v>
+      </c>
+      <c r="K22">
+        <v>147.3</v>
+      </c>
+      <c r="L22">
+        <v>175.3</v>
+      </c>
+      <c r="M22">
+        <v>7.303774000000002</v>
+      </c>
+      <c r="N22">
+        <v>167.996226</v>
+      </c>
+      <c r="O22">
+        <v>50.39886780000001</v>
+      </c>
+      <c r="P22">
+        <v>117.5973582</v>
+      </c>
+      <c r="Q22">
+        <v>264.8973582</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2992580208453866</v>
+      </c>
+      <c r="T22">
+        <v>1.381257156445184</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.3</v>
+      </c>
+      <c r="W22">
+        <v>0.03199</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>24.0012902918409</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2450713174741508</v>
+      </c>
+      <c r="C23">
+        <v>630.6796357412444</v>
+      </c>
+      <c r="D23">
+        <v>-149.8093642587556</v>
+      </c>
+      <c r="E23">
+        <v>128.611</v>
+      </c>
+      <c r="F23">
+        <v>167.811</v>
+      </c>
+      <c r="G23">
+        <v>948.3</v>
+      </c>
+      <c r="H23">
+        <v>759.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>322.6</v>
+      </c>
+      <c r="K23">
+        <v>147.3</v>
+      </c>
+      <c r="L23">
+        <v>175.3</v>
+      </c>
+      <c r="M23">
+        <v>7.668962700000001</v>
+      </c>
+      <c r="N23">
+        <v>167.6310373</v>
+      </c>
+      <c r="O23">
+        <v>50.28931119000001</v>
+      </c>
+      <c r="P23">
+        <v>117.34172611</v>
+      </c>
+      <c r="Q23">
+        <v>264.64172611</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.3017131866761402</v>
+      </c>
+      <c r="T23">
+        <v>1.394277355873027</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.3</v>
+      </c>
+      <c r="W23">
+        <v>0.03199</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>22.85837170651514</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2443382182719924</v>
+      </c>
+      <c r="C24">
+        <v>622.658735141718</v>
+      </c>
+      <c r="D24">
+        <v>-149.839264858282</v>
+      </c>
+      <c r="E24">
+        <v>136.602</v>
+      </c>
+      <c r="F24">
+        <v>175.802</v>
+      </c>
+      <c r="G24">
+        <v>948.3</v>
+      </c>
+      <c r="H24">
+        <v>759.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>322.6</v>
+      </c>
+      <c r="K24">
+        <v>147.3</v>
+      </c>
+      <c r="L24">
+        <v>175.3</v>
+      </c>
+      <c r="M24">
+        <v>8.034151400000001</v>
+      </c>
+      <c r="N24">
+        <v>167.2658486</v>
+      </c>
+      <c r="O24">
+        <v>50.17975458000001</v>
+      </c>
+      <c r="P24">
+        <v>117.08609402</v>
+      </c>
+      <c r="Q24">
+        <v>264.38609402</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.3042313054769133</v>
+      </c>
+      <c r="T24">
+        <v>1.407631406568251</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.03199</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>21.81935481076446</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.243605119069834</v>
+      </c>
+      <c r="C25">
+        <v>614.6378226040282</v>
+      </c>
+      <c r="D25">
+        <v>-149.8691773959717</v>
+      </c>
+      <c r="E25">
+        <v>144.593</v>
+      </c>
+      <c r="F25">
+        <v>183.793</v>
+      </c>
+      <c r="G25">
+        <v>948.3</v>
+      </c>
+      <c r="H25">
+        <v>759.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>322.6</v>
+      </c>
+      <c r="K25">
+        <v>147.3</v>
+      </c>
+      <c r="L25">
+        <v>175.3</v>
+      </c>
+      <c r="M25">
+        <v>8.399340100000002</v>
+      </c>
+      <c r="N25">
+        <v>166.9006599</v>
+      </c>
+      <c r="O25">
+        <v>50.07019797000002</v>
+      </c>
+      <c r="P25">
+        <v>116.83046193</v>
+      </c>
+      <c r="Q25">
+        <v>264.13046193</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.3068148299608233</v>
+      </c>
+      <c r="T25">
+        <v>1.421332315723091</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.3</v>
+      </c>
+      <c r="W25">
+        <v>0.03199</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>20.87068721029643</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2428720198676755</v>
+      </c>
+      <c r="C26">
+        <v>606.6168981210241</v>
+      </c>
+      <c r="D26">
+        <v>-149.8991018789759</v>
+      </c>
+      <c r="E26">
+        <v>152.584</v>
+      </c>
+      <c r="F26">
+        <v>191.784</v>
+      </c>
+      <c r="G26">
+        <v>948.3</v>
+      </c>
+      <c r="H26">
+        <v>759.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>322.6</v>
+      </c>
+      <c r="K26">
+        <v>147.3</v>
+      </c>
+      <c r="L26">
+        <v>175.3</v>
+      </c>
+      <c r="M26">
+        <v>8.764528800000001</v>
+      </c>
+      <c r="N26">
+        <v>166.5354712</v>
+      </c>
+      <c r="O26">
+        <v>49.96064136000001</v>
+      </c>
+      <c r="P26">
+        <v>116.57482984</v>
+      </c>
+      <c r="Q26">
+        <v>263.87482984</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.309466341931152</v>
+      </c>
+      <c r="T26">
+        <v>1.435393775118848</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.3</v>
+      </c>
+      <c r="W26">
+        <v>0.03199</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>20.00107524320075</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2421389206655171</v>
+      </c>
+      <c r="C27">
+        <v>598.5959616855486</v>
+      </c>
+      <c r="D27">
+        <v>-149.9290383144514</v>
+      </c>
+      <c r="E27">
+        <v>160.575</v>
+      </c>
+      <c r="F27">
+        <v>199.775</v>
+      </c>
+      <c r="G27">
+        <v>948.3</v>
+      </c>
+      <c r="H27">
+        <v>759.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>322.6</v>
+      </c>
+      <c r="K27">
+        <v>147.3</v>
+      </c>
+      <c r="L27">
+        <v>175.3</v>
+      </c>
+      <c r="M27">
+        <v>9.129717500000002</v>
+      </c>
+      <c r="N27">
+        <v>166.1702825</v>
+      </c>
+      <c r="O27">
+        <v>49.85108475000001</v>
+      </c>
+      <c r="P27">
+        <v>116.31919775</v>
+      </c>
+      <c r="Q27">
+        <v>263.61919775</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.3121885608873561</v>
+      </c>
+      <c r="T27">
+        <v>1.449830206765158</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.3</v>
+      </c>
+      <c r="W27">
+        <v>0.03199</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>19.20103223347272</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2414058214633586</v>
+      </c>
+      <c r="C28">
+        <v>590.5750132904393</v>
+      </c>
+      <c r="D28">
+        <v>-149.9589867095607</v>
+      </c>
+      <c r="E28">
+        <v>168.566</v>
+      </c>
+      <c r="F28">
+        <v>207.766</v>
+      </c>
+      <c r="G28">
+        <v>948.3</v>
+      </c>
+      <c r="H28">
+        <v>759.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>322.6</v>
+      </c>
+      <c r="K28">
+        <v>147.3</v>
+      </c>
+      <c r="L28">
+        <v>175.3</v>
+      </c>
+      <c r="M28">
+        <v>9.494906200000003</v>
+      </c>
+      <c r="N28">
+        <v>165.8050938</v>
+      </c>
+      <c r="O28">
+        <v>49.74152814000001</v>
+      </c>
+      <c r="P28">
+        <v>116.06356566</v>
+      </c>
+      <c r="Q28">
+        <v>263.36356566</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.314984353328863</v>
+      </c>
+      <c r="T28">
+        <v>1.464656812239747</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.3</v>
+      </c>
+      <c r="W28">
+        <v>0.03199</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>18.46253099372377</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2406727222612002</v>
+      </c>
+      <c r="C29">
+        <v>582.5540529285279</v>
+      </c>
+      <c r="D29">
+        <v>-149.9889470714721</v>
+      </c>
+      <c r="E29">
+        <v>176.557</v>
+      </c>
+      <c r="F29">
+        <v>215.757</v>
+      </c>
+      <c r="G29">
+        <v>948.3</v>
+      </c>
+      <c r="H29">
+        <v>759.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>322.6</v>
+      </c>
+      <c r="K29">
+        <v>147.3</v>
+      </c>
+      <c r="L29">
+        <v>175.3</v>
+      </c>
+      <c r="M29">
+        <v>9.860094900000002</v>
+      </c>
+      <c r="N29">
+        <v>165.4399051</v>
+      </c>
+      <c r="O29">
+        <v>49.63197153000001</v>
+      </c>
+      <c r="P29">
+        <v>115.80793357</v>
+      </c>
+      <c r="Q29">
+        <v>263.10793357</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.317856742823562</v>
+      </c>
+      <c r="T29">
+        <v>1.479889626083503</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.3</v>
+      </c>
+      <c r="W29">
+        <v>0.03199</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>17.77873354951178</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2399396230590418</v>
+      </c>
+      <c r="C30">
+        <v>574.5330805926404</v>
+      </c>
+      <c r="D30">
+        <v>-150.0189194073595</v>
+      </c>
+      <c r="E30">
+        <v>184.548</v>
+      </c>
+      <c r="F30">
+        <v>223.748</v>
+      </c>
+      <c r="G30">
+        <v>948.3</v>
+      </c>
+      <c r="H30">
+        <v>759.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>322.6</v>
+      </c>
+      <c r="K30">
+        <v>147.3</v>
+      </c>
+      <c r="L30">
+        <v>175.3</v>
+      </c>
+      <c r="M30">
+        <v>10.2252836</v>
+      </c>
+      <c r="N30">
+        <v>165.0747164</v>
+      </c>
+      <c r="O30">
+        <v>49.52241492000001</v>
+      </c>
+      <c r="P30">
+        <v>115.55230148</v>
+      </c>
+      <c r="Q30">
+        <v>262.85230148</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.3208089209153358</v>
+      </c>
+      <c r="T30">
+        <v>1.49554557364514</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.3</v>
+      </c>
+      <c r="W30">
+        <v>0.03199</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>17.14377877988635</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2392065238568834</v>
+      </c>
+      <c r="C31">
+        <v>566.5120962755972</v>
+      </c>
+      <c r="D31">
+        <v>-150.0489037244027</v>
+      </c>
+      <c r="E31">
+        <v>192.539</v>
+      </c>
+      <c r="F31">
+        <v>231.739</v>
+      </c>
+      <c r="G31">
+        <v>948.3</v>
+      </c>
+      <c r="H31">
+        <v>759.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>322.6</v>
+      </c>
+      <c r="K31">
+        <v>147.3</v>
+      </c>
+      <c r="L31">
+        <v>175.3</v>
+      </c>
+      <c r="M31">
+        <v>10.5904723</v>
+      </c>
+      <c r="N31">
+        <v>164.7095277</v>
+      </c>
+      <c r="O31">
+        <v>49.41285831000001</v>
+      </c>
+      <c r="P31">
+        <v>115.29666939</v>
+      </c>
+      <c r="Q31">
+        <v>262.59666939</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.3238442589533569</v>
+      </c>
+      <c r="T31">
+        <v>1.511642533814148</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.3</v>
+      </c>
+      <c r="W31">
+        <v>0.03199</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>16.55261399437304</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2384734246547249</v>
+      </c>
+      <c r="C32">
+        <v>558.4910999702128</v>
+      </c>
+      <c r="D32">
+        <v>-150.0789000297871</v>
+      </c>
+      <c r="E32">
+        <v>200.53</v>
+      </c>
+      <c r="F32">
+        <v>239.73</v>
+      </c>
+      <c r="G32">
+        <v>948.3</v>
+      </c>
+      <c r="H32">
+        <v>759.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>322.6</v>
+      </c>
+      <c r="K32">
+        <v>147.3</v>
+      </c>
+      <c r="L32">
+        <v>175.3</v>
+      </c>
+      <c r="M32">
+        <v>10.955661</v>
+      </c>
+      <c r="N32">
+        <v>164.344339</v>
+      </c>
+      <c r="O32">
+        <v>49.30330170000001</v>
+      </c>
+      <c r="P32">
+        <v>115.0410373</v>
+      </c>
+      <c r="Q32">
+        <v>262.3410373</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.3269663209353213</v>
+      </c>
+      <c r="T32">
+        <v>1.528199407130842</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.3</v>
+      </c>
+      <c r="W32">
+        <v>0.03199</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>16.0008601945606</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2377403254525665</v>
+      </c>
+      <c r="C33">
+        <v>550.4700916692959</v>
+      </c>
+      <c r="D33">
+        <v>-150.1089083307041</v>
+      </c>
+      <c r="E33">
+        <v>208.521</v>
+      </c>
+      <c r="F33">
+        <v>247.721</v>
+      </c>
+      <c r="G33">
+        <v>948.3</v>
+      </c>
+      <c r="H33">
+        <v>759.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>322.6</v>
+      </c>
+      <c r="K33">
+        <v>147.3</v>
+      </c>
+      <c r="L33">
+        <v>175.3</v>
+      </c>
+      <c r="M33">
+        <v>11.3208497</v>
+      </c>
+      <c r="N33">
+        <v>163.9791503</v>
+      </c>
+      <c r="O33">
+        <v>49.19374509000001</v>
+      </c>
+      <c r="P33">
+        <v>114.78540521</v>
+      </c>
+      <c r="Q33">
+        <v>262.08540521</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.3301788774674876</v>
+      </c>
+      <c r="T33">
+        <v>1.545236189819034</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.3</v>
+      </c>
+      <c r="W33">
+        <v>0.03199</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>15.4847034140909</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.237007226250408</v>
+      </c>
+      <c r="C34">
+        <v>542.4490713656496</v>
+      </c>
+      <c r="D34">
+        <v>-150.1389286343504</v>
+      </c>
+      <c r="E34">
+        <v>216.512</v>
+      </c>
+      <c r="F34">
+        <v>255.712</v>
+      </c>
+      <c r="G34">
+        <v>948.3</v>
+      </c>
+      <c r="H34">
+        <v>759.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>322.6</v>
+      </c>
+      <c r="K34">
+        <v>147.3</v>
+      </c>
+      <c r="L34">
+        <v>175.3</v>
+      </c>
+      <c r="M34">
+        <v>11.6860384</v>
+      </c>
+      <c r="N34">
+        <v>163.6139616</v>
+      </c>
+      <c r="O34">
+        <v>49.08418848000001</v>
+      </c>
+      <c r="P34">
+        <v>114.52977312</v>
+      </c>
+      <c r="Q34">
+        <v>261.82977312</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.3334859209564824</v>
+      </c>
+      <c r="T34">
+        <v>1.562774054350997</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.3</v>
+      </c>
+      <c r="W34">
+        <v>0.03199</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>15.00080643240056</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2362741270482496</v>
+      </c>
+      <c r="C35">
+        <v>534.428039052071</v>
+      </c>
+      <c r="D35">
+        <v>-150.1689609479289</v>
+      </c>
+      <c r="E35">
+        <v>224.503</v>
+      </c>
+      <c r="F35">
+        <v>263.703</v>
+      </c>
+      <c r="G35">
+        <v>948.3</v>
+      </c>
+      <c r="H35">
+        <v>759.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>322.6</v>
+      </c>
+      <c r="K35">
+        <v>147.3</v>
+      </c>
+      <c r="L35">
+        <v>175.3</v>
+      </c>
+      <c r="M35">
+        <v>12.0512271</v>
+      </c>
+      <c r="N35">
+        <v>163.2487729</v>
+      </c>
+      <c r="O35">
+        <v>48.97463187000001</v>
+      </c>
+      <c r="P35">
+        <v>114.27414103</v>
+      </c>
+      <c r="Q35">
+        <v>261.57414103</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.3368916821615666</v>
+      </c>
+      <c r="T35">
+        <v>1.580835437227197</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.3</v>
+      </c>
+      <c r="W35">
+        <v>0.03199</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>14.54623654050964</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2355410278460912</v>
+      </c>
+      <c r="C36">
+        <v>526.406994721352</v>
+      </c>
+      <c r="D36">
+        <v>-150.199005278648</v>
+      </c>
+      <c r="E36">
+        <v>232.494</v>
+      </c>
+      <c r="F36">
+        <v>271.694</v>
+      </c>
+      <c r="G36">
+        <v>948.3</v>
+      </c>
+      <c r="H36">
+        <v>759.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>322.6</v>
+      </c>
+      <c r="K36">
+        <v>147.3</v>
+      </c>
+      <c r="L36">
+        <v>175.3</v>
+      </c>
+      <c r="M36">
+        <v>12.4164158</v>
+      </c>
+      <c r="N36">
+        <v>162.8835842</v>
+      </c>
+      <c r="O36">
+        <v>48.86507526</v>
+      </c>
+      <c r="P36">
+        <v>114.01850894</v>
+      </c>
+      <c r="Q36">
+        <v>261.31850894</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.3404006482516533</v>
+      </c>
+      <c r="T36">
+        <v>1.59944413473601</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.3</v>
+      </c>
+      <c r="W36">
+        <v>0.03199</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>14.11840605402406</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2348079286439327</v>
+      </c>
+      <c r="C37">
+        <v>518.3859383662779</v>
+      </c>
+      <c r="D37">
+        <v>-150.229061633722</v>
+      </c>
+      <c r="E37">
+        <v>240.4850000000001</v>
+      </c>
+      <c r="F37">
+        <v>279.6850000000001</v>
+      </c>
+      <c r="G37">
+        <v>948.3</v>
+      </c>
+      <c r="H37">
+        <v>759.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>322.6</v>
+      </c>
+      <c r="K37">
+        <v>147.3</v>
+      </c>
+      <c r="L37">
+        <v>175.3</v>
+      </c>
+      <c r="M37">
+        <v>12.7816045</v>
+      </c>
+      <c r="N37">
+        <v>162.5183955</v>
+      </c>
+      <c r="O37">
+        <v>48.75551865000001</v>
+      </c>
+      <c r="P37">
+        <v>113.76287685</v>
+      </c>
+      <c r="Q37">
+        <v>261.06287685</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.3440175825291273</v>
+      </c>
+      <c r="T37">
+        <v>1.618625407552785</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.3</v>
+      </c>
+      <c r="W37">
+        <v>0.03199</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>13.71502302390908</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2340748294417743</v>
+      </c>
+      <c r="C38">
+        <v>510.364869979629</v>
+      </c>
+      <c r="D38">
+        <v>-150.2591300203709</v>
+      </c>
+      <c r="E38">
+        <v>248.476</v>
+      </c>
+      <c r="F38">
+        <v>287.676</v>
+      </c>
+      <c r="G38">
+        <v>948.3</v>
+      </c>
+      <c r="H38">
+        <v>759.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>322.6</v>
+      </c>
+      <c r="K38">
+        <v>147.3</v>
+      </c>
+      <c r="L38">
+        <v>175.3</v>
+      </c>
+      <c r="M38">
+        <v>13.1467932</v>
+      </c>
+      <c r="N38">
+        <v>162.1532068</v>
+      </c>
+      <c r="O38">
+        <v>48.64596204000001</v>
+      </c>
+      <c r="P38">
+        <v>113.50724476</v>
+      </c>
+      <c r="Q38">
+        <v>260.80724476</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.3477475460027724</v>
+      </c>
+      <c r="T38">
+        <v>1.638406095145085</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.3</v>
+      </c>
+      <c r="W38">
+        <v>0.03199</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>13.33405016213383</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2333417302396159</v>
+      </c>
+      <c r="C39">
+        <v>502.3437895541792</v>
+      </c>
+      <c r="D39">
+        <v>-150.2892104458207</v>
+      </c>
+      <c r="E39">
+        <v>256.467</v>
+      </c>
+      <c r="F39">
+        <v>295.667</v>
+      </c>
+      <c r="G39">
+        <v>948.3</v>
+      </c>
+      <c r="H39">
+        <v>759.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>322.6</v>
+      </c>
+      <c r="K39">
+        <v>147.3</v>
+      </c>
+      <c r="L39">
+        <v>175.3</v>
+      </c>
+      <c r="M39">
+        <v>13.5119819</v>
+      </c>
+      <c r="N39">
+        <v>161.7880181</v>
+      </c>
+      <c r="O39">
+        <v>48.53640543000001</v>
+      </c>
+      <c r="P39">
+        <v>113.25161267</v>
+      </c>
+      <c r="Q39">
+        <v>260.5516126700001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3515959210152633</v>
+      </c>
+      <c r="T39">
+        <v>1.658814741073649</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.3</v>
+      </c>
+      <c r="W39">
+        <v>0.03199</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>12.97367042802211</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2330342310374575</v>
+      </c>
+      <c r="C40">
+        <v>494.3401687036587</v>
+      </c>
+      <c r="D40">
+        <v>-150.3018312963412</v>
+      </c>
+      <c r="E40">
+        <v>264.458</v>
+      </c>
+      <c r="F40">
+        <v>303.658</v>
+      </c>
+      <c r="G40">
+        <v>948.3</v>
+      </c>
+      <c r="H40">
+        <v>759.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>322.6</v>
+      </c>
+      <c r="K40">
+        <v>147.3</v>
+      </c>
+      <c r="L40">
+        <v>175.3</v>
+      </c>
+      <c r="M40">
+        <v>14.3630234</v>
+      </c>
+      <c r="N40">
+        <v>160.9369766</v>
+      </c>
+      <c r="O40">
+        <v>48.28109298000001</v>
+      </c>
+      <c r="P40">
+        <v>112.65588362</v>
+      </c>
+      <c r="Q40">
+        <v>259.95588362</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.3555684371571894</v>
+      </c>
+      <c r="T40">
+        <v>1.679881730419263</v>
+      </c>
+      <c r="U40">
+        <v>0.0473</v>
+      </c>
+      <c r="V40">
+        <v>0.3</v>
+      </c>
+      <c r="W40">
+        <v>0.03311</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>12.20495122217791</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.232312331835299</v>
+      </c>
+      <c r="C41">
+        <v>486.31953108609</v>
+      </c>
+      <c r="D41">
+        <v>-150.33146891391</v>
+      </c>
+      <c r="E41">
+        <v>272.449</v>
+      </c>
+      <c r="F41">
+        <v>311.649</v>
+      </c>
+      <c r="G41">
+        <v>948.3</v>
+      </c>
+      <c r="H41">
+        <v>759.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>322.6</v>
+      </c>
+      <c r="K41">
+        <v>147.3</v>
+      </c>
+      <c r="L41">
+        <v>175.3</v>
+      </c>
+      <c r="M41">
+        <v>14.7409977</v>
+      </c>
+      <c r="N41">
+        <v>160.5590023</v>
+      </c>
+      <c r="O41">
+        <v>48.16770069000001</v>
+      </c>
+      <c r="P41">
+        <v>112.39130161</v>
+      </c>
+      <c r="Q41">
+        <v>259.69130161</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3596711997299984</v>
+      </c>
+      <c r="T41">
+        <v>1.701639440727028</v>
+      </c>
+      <c r="U41">
+        <v>0.0473</v>
+      </c>
+      <c r="V41">
+        <v>0.3</v>
+      </c>
+      <c r="W41">
+        <v>0.03311</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>11.89200375494258</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2315904326331406</v>
+      </c>
+      <c r="C42">
+        <v>478.2988817778904</v>
+      </c>
+      <c r="D42">
+        <v>-150.3611182221096</v>
+      </c>
+      <c r="E42">
+        <v>280.4400000000001</v>
+      </c>
+      <c r="F42">
+        <v>319.64</v>
+      </c>
+      <c r="G42">
+        <v>948.3</v>
+      </c>
+      <c r="H42">
+        <v>759.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>322.6</v>
+      </c>
+      <c r="K42">
+        <v>147.3</v>
+      </c>
+      <c r="L42">
+        <v>175.3</v>
+      </c>
+      <c r="M42">
+        <v>15.118972</v>
+      </c>
+      <c r="N42">
+        <v>160.181028</v>
+      </c>
+      <c r="O42">
+        <v>48.0543084</v>
+      </c>
+      <c r="P42">
+        <v>112.1267196</v>
+      </c>
+      <c r="Q42">
+        <v>259.4267196</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.3639107210552344</v>
+      </c>
+      <c r="T42">
+        <v>1.724122408045053</v>
+      </c>
+      <c r="U42">
+        <v>0.0473</v>
+      </c>
+      <c r="V42">
+        <v>0.3</v>
+      </c>
+      <c r="W42">
+        <v>0.03311</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>11.59470366106902</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2308685334309821</v>
+      </c>
+      <c r="C43">
+        <v>470.2782207721413</v>
+      </c>
+      <c r="D43">
+        <v>-150.3907792278586</v>
+      </c>
+      <c r="E43">
+        <v>288.431</v>
+      </c>
+      <c r="F43">
+        <v>327.631</v>
+      </c>
+      <c r="G43">
+        <v>948.3</v>
+      </c>
+      <c r="H43">
+        <v>759.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>322.6</v>
+      </c>
+      <c r="K43">
+        <v>147.3</v>
+      </c>
+      <c r="L43">
+        <v>175.3</v>
+      </c>
+      <c r="M43">
+        <v>15.4969463</v>
+      </c>
+      <c r="N43">
+        <v>159.8030537</v>
+      </c>
+      <c r="O43">
+        <v>47.94091611000001</v>
+      </c>
+      <c r="P43">
+        <v>111.86213759</v>
+      </c>
+      <c r="Q43">
+        <v>259.16213759</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.3682939549677663</v>
+      </c>
+      <c r="T43">
+        <v>1.747367509848433</v>
+      </c>
+      <c r="U43">
+        <v>0.0473</v>
+      </c>
+      <c r="V43">
+        <v>0.3</v>
+      </c>
+      <c r="W43">
+        <v>0.03311</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>11.31190601079904</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2301466342288237</v>
+      </c>
+      <c r="C44">
+        <v>462.2575480619192</v>
+      </c>
+      <c r="D44">
+        <v>-150.4204519380808</v>
+      </c>
+      <c r="E44">
+        <v>296.422</v>
+      </c>
+      <c r="F44">
+        <v>335.622</v>
+      </c>
+      <c r="G44">
+        <v>948.3</v>
+      </c>
+      <c r="H44">
+        <v>759.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>322.6</v>
+      </c>
+      <c r="K44">
+        <v>147.3</v>
+      </c>
+      <c r="L44">
+        <v>175.3</v>
+      </c>
+      <c r="M44">
+        <v>15.8749206</v>
+      </c>
+      <c r="N44">
+        <v>159.4250794</v>
+      </c>
+      <c r="O44">
+        <v>47.82752382000001</v>
+      </c>
+      <c r="P44">
+        <v>111.59755558</v>
+      </c>
+      <c r="Q44">
+        <v>258.89755558</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.3728283348772822</v>
+      </c>
+      <c r="T44">
+        <v>1.771414166886413</v>
+      </c>
+      <c r="U44">
+        <v>0.0473</v>
+      </c>
+      <c r="V44">
+        <v>0.3</v>
+      </c>
+      <c r="W44">
+        <v>0.03311</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>11.04257491530383</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2294247350266653</v>
+      </c>
+      <c r="C45">
+        <v>454.2368636402942</v>
+      </c>
+      <c r="D45">
+        <v>-150.4501363597057</v>
+      </c>
+      <c r="E45">
+        <v>304.413</v>
+      </c>
+      <c r="F45">
+        <v>343.613</v>
+      </c>
+      <c r="G45">
+        <v>948.3</v>
+      </c>
+      <c r="H45">
+        <v>759.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>322.6</v>
+      </c>
+      <c r="K45">
+        <v>147.3</v>
+      </c>
+      <c r="L45">
+        <v>175.3</v>
+      </c>
+      <c r="M45">
+        <v>16.2528949</v>
+      </c>
+      <c r="N45">
+        <v>159.0471051</v>
+      </c>
+      <c r="O45">
+        <v>47.71413153000001</v>
+      </c>
+      <c r="P45">
+        <v>111.33297357</v>
+      </c>
+      <c r="Q45">
+        <v>258.63297357</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3775218158362549</v>
+      </c>
+      <c r="T45">
+        <v>1.796304566276604</v>
+      </c>
+      <c r="U45">
+        <v>0.0473</v>
+      </c>
+      <c r="V45">
+        <v>0.3</v>
+      </c>
+      <c r="W45">
+        <v>0.03311</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>10.78577084750606</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2287028358245068</v>
+      </c>
+      <c r="C46">
+        <v>446.2161675003318</v>
+      </c>
+      <c r="D46">
+        <v>-150.4798324996682</v>
+      </c>
+      <c r="E46">
+        <v>312.404</v>
+      </c>
+      <c r="F46">
+        <v>351.604</v>
+      </c>
+      <c r="G46">
+        <v>948.3</v>
+      </c>
+      <c r="H46">
+        <v>759.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>322.6</v>
+      </c>
+      <c r="K46">
+        <v>147.3</v>
+      </c>
+      <c r="L46">
+        <v>175.3</v>
+      </c>
+      <c r="M46">
+        <v>16.6308692</v>
+      </c>
+      <c r="N46">
+        <v>158.6691308</v>
+      </c>
+      <c r="O46">
+        <v>47.60073924000001</v>
+      </c>
+      <c r="P46">
+        <v>111.06839156</v>
+      </c>
+      <c r="Q46">
+        <v>258.36839156</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3823829211151907</v>
+      </c>
+      <c r="T46">
+        <v>1.822083908502158</v>
+      </c>
+      <c r="U46">
+        <v>0.0473</v>
+      </c>
+      <c r="V46">
+        <v>0.3</v>
+      </c>
+      <c r="W46">
+        <v>0.03311</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>10.54063969188093</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2279809366223484</v>
+      </c>
+      <c r="C47">
+        <v>438.1954596350914</v>
+      </c>
+      <c r="D47">
+        <v>-150.5095403649085</v>
+      </c>
+      <c r="E47">
+        <v>320.395</v>
+      </c>
+      <c r="F47">
+        <v>359.595</v>
+      </c>
+      <c r="G47">
+        <v>948.3</v>
+      </c>
+      <c r="H47">
+        <v>759.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>322.6</v>
+      </c>
+      <c r="K47">
+        <v>147.3</v>
+      </c>
+      <c r="L47">
+        <v>175.3</v>
+      </c>
+      <c r="M47">
+        <v>17.0088435</v>
+      </c>
+      <c r="N47">
+        <v>158.2911565</v>
+      </c>
+      <c r="O47">
+        <v>47.48734695000001</v>
+      </c>
+      <c r="P47">
+        <v>110.80380955</v>
+      </c>
+      <c r="Q47">
+        <v>258.10380955</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.3874207938588153</v>
+      </c>
+      <c r="T47">
+        <v>1.848800681354096</v>
+      </c>
+      <c r="U47">
+        <v>0.0473</v>
+      </c>
+      <c r="V47">
+        <v>0.3</v>
+      </c>
+      <c r="W47">
+        <v>0.03311</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>10.30640325428357</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.22848263742019</v>
+      </c>
+      <c r="C48">
+        <v>430.2251070565756</v>
+      </c>
+      <c r="D48">
+        <v>-150.4888929434244</v>
+      </c>
+      <c r="E48">
+        <v>328.386</v>
+      </c>
+      <c r="F48">
+        <v>367.586</v>
+      </c>
+      <c r="G48">
+        <v>948.3</v>
+      </c>
+      <c r="H48">
+        <v>759.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>322.6</v>
+      </c>
+      <c r="K48">
+        <v>147.3</v>
+      </c>
+      <c r="L48">
+        <v>175.3</v>
+      </c>
+      <c r="M48">
+        <v>18.7836446</v>
+      </c>
+      <c r="N48">
+        <v>156.5163554</v>
+      </c>
+      <c r="O48">
+        <v>46.95490662000001</v>
+      </c>
+      <c r="P48">
+        <v>109.56144878</v>
+      </c>
+      <c r="Q48">
+        <v>256.86144878</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.3926452544818332</v>
+      </c>
+      <c r="T48">
+        <v>1.876506964311661</v>
+      </c>
+      <c r="U48">
+        <v>0.0511</v>
+      </c>
+      <c r="V48">
+        <v>0.3</v>
+      </c>
+      <c r="W48">
+        <v>0.03577</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>9.332587138067977</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2277873382180315</v>
+      </c>
+      <c r="C49">
+        <v>422.2054906065707</v>
+      </c>
+      <c r="D49">
+        <v>-150.5175093934292</v>
+      </c>
+      <c r="E49">
+        <v>336.3770000000001</v>
+      </c>
+      <c r="F49">
+        <v>375.5770000000001</v>
+      </c>
+      <c r="G49">
+        <v>948.3</v>
+      </c>
+      <c r="H49">
+        <v>759.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>322.6</v>
+      </c>
+      <c r="K49">
+        <v>147.3</v>
+      </c>
+      <c r="L49">
+        <v>175.3</v>
+      </c>
+      <c r="M49">
+        <v>19.1919847</v>
+      </c>
+      <c r="N49">
+        <v>156.1080153</v>
+      </c>
+      <c r="O49">
+        <v>46.83240459000001</v>
+      </c>
+      <c r="P49">
+        <v>109.27561071</v>
+      </c>
+      <c r="Q49">
+        <v>256.57561071</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3980668645623237</v>
+      </c>
+      <c r="T49">
+        <v>1.905258767380832</v>
+      </c>
+      <c r="U49">
+        <v>0.0511</v>
+      </c>
+      <c r="V49">
+        <v>0.3</v>
+      </c>
+      <c r="W49">
+        <v>0.03577</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>9.134021454279296</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2270920390158731</v>
+      </c>
+      <c r="C50">
+        <v>414.1858632712847</v>
+      </c>
+      <c r="D50">
+        <v>-150.5461367287153</v>
+      </c>
+      <c r="E50">
+        <v>344.368</v>
+      </c>
+      <c r="F50">
+        <v>383.568</v>
+      </c>
+      <c r="G50">
+        <v>948.3</v>
+      </c>
+      <c r="H50">
+        <v>759.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>322.6</v>
+      </c>
+      <c r="K50">
+        <v>147.3</v>
+      </c>
+      <c r="L50">
+        <v>175.3</v>
+      </c>
+      <c r="M50">
+        <v>19.6003248</v>
+      </c>
+      <c r="N50">
+        <v>155.6996752</v>
+      </c>
+      <c r="O50">
+        <v>46.70990256000001</v>
+      </c>
+      <c r="P50">
+        <v>108.98977264</v>
+      </c>
+      <c r="Q50">
+        <v>256.28977264</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.4036969981074483</v>
+      </c>
+      <c r="T50">
+        <v>1.935116409029587</v>
+      </c>
+      <c r="U50">
+        <v>0.0511</v>
+      </c>
+      <c r="V50">
+        <v>0.3</v>
+      </c>
+      <c r="W50">
+        <v>0.03577</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>8.943729340648478</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2263967398137147</v>
+      </c>
+      <c r="C51">
+        <v>406.1662250445053</v>
+      </c>
+      <c r="D51">
+        <v>-150.5747749554947</v>
+      </c>
+      <c r="E51">
+        <v>352.359</v>
+      </c>
+      <c r="F51">
+        <v>391.559</v>
+      </c>
+      <c r="G51">
+        <v>948.3</v>
+      </c>
+      <c r="H51">
+        <v>759.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>322.6</v>
+      </c>
+      <c r="K51">
+        <v>147.3</v>
+      </c>
+      <c r="L51">
+        <v>175.3</v>
+      </c>
+      <c r="M51">
+        <v>20.0086649</v>
+      </c>
+      <c r="N51">
+        <v>155.2913351</v>
+      </c>
+      <c r="O51">
+        <v>46.58740053000002</v>
+      </c>
+      <c r="P51">
+        <v>108.70393457</v>
+      </c>
+      <c r="Q51">
+        <v>256.00393457</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.4095479212033621</v>
+      </c>
+      <c r="T51">
+        <v>1.966144938586136</v>
+      </c>
+      <c r="U51">
+        <v>0.0511</v>
+      </c>
+      <c r="V51">
+        <v>0.3</v>
+      </c>
+      <c r="W51">
+        <v>0.03577</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>8.761204252063816</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2257014406115562</v>
+      </c>
+      <c r="C52">
+        <v>398.1465759200158</v>
+      </c>
+      <c r="D52">
+        <v>-150.6034240799842</v>
+      </c>
+      <c r="E52">
+        <v>360.35</v>
+      </c>
+      <c r="F52">
+        <v>399.55</v>
+      </c>
+      <c r="G52">
+        <v>948.3</v>
+      </c>
+      <c r="H52">
+        <v>759.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>322.6</v>
+      </c>
+      <c r="K52">
+        <v>147.3</v>
+      </c>
+      <c r="L52">
+        <v>175.3</v>
+      </c>
+      <c r="M52">
+        <v>20.417005</v>
+      </c>
+      <c r="N52">
+        <v>154.882995</v>
+      </c>
+      <c r="O52">
+        <v>46.46489850000001</v>
+      </c>
+      <c r="P52">
+        <v>108.4180965</v>
+      </c>
+      <c r="Q52">
+        <v>255.7180965</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.4156328812231125</v>
+      </c>
+      <c r="T52">
+        <v>1.998414609324947</v>
+      </c>
+      <c r="U52">
+        <v>0.0511</v>
+      </c>
+      <c r="V52">
+        <v>0.3</v>
+      </c>
+      <c r="W52">
+        <v>0.03577</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>8.585980167022541</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2250061414093978</v>
+      </c>
+      <c r="C53">
+        <v>390.1269158915947</v>
+      </c>
+      <c r="D53">
+        <v>-150.6320841084053</v>
+      </c>
+      <c r="E53">
+        <v>368.341</v>
+      </c>
+      <c r="F53">
+        <v>407.541</v>
+      </c>
+      <c r="G53">
+        <v>948.3</v>
+      </c>
+      <c r="H53">
+        <v>759.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>322.6</v>
+      </c>
+      <c r="K53">
+        <v>147.3</v>
+      </c>
+      <c r="L53">
+        <v>175.3</v>
+      </c>
+      <c r="M53">
+        <v>20.8253451</v>
+      </c>
+      <c r="N53">
+        <v>154.4746549</v>
+      </c>
+      <c r="O53">
+        <v>46.34239647000001</v>
+      </c>
+      <c r="P53">
+        <v>108.13225843</v>
+      </c>
+      <c r="Q53">
+        <v>255.43225843</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.4219662069579547</v>
+      </c>
+      <c r="T53">
+        <v>2.032001409481669</v>
+      </c>
+      <c r="U53">
+        <v>0.0511</v>
+      </c>
+      <c r="V53">
+        <v>0.3</v>
+      </c>
+      <c r="W53">
+        <v>0.03577</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>8.41762761472798</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2243108422072394</v>
+      </c>
+      <c r="C54">
+        <v>382.1072449530155</v>
+      </c>
+      <c r="D54">
+        <v>-150.6607550469844</v>
+      </c>
+      <c r="E54">
+        <v>376.3320000000001</v>
+      </c>
+      <c r="F54">
+        <v>415.532</v>
+      </c>
+      <c r="G54">
+        <v>948.3</v>
+      </c>
+      <c r="H54">
+        <v>759.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>322.6</v>
+      </c>
+      <c r="K54">
+        <v>147.3</v>
+      </c>
+      <c r="L54">
+        <v>175.3</v>
+      </c>
+      <c r="M54">
+        <v>21.2336852</v>
+      </c>
+      <c r="N54">
+        <v>154.0663148</v>
+      </c>
+      <c r="O54">
+        <v>46.21989444000001</v>
+      </c>
+      <c r="P54">
+        <v>107.84642036</v>
+      </c>
+      <c r="Q54">
+        <v>255.14642036</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.4285634212650821</v>
+      </c>
+      <c r="T54">
+        <v>2.066987659644921</v>
+      </c>
+      <c r="U54">
+        <v>0.0511</v>
+      </c>
+      <c r="V54">
+        <v>0.3</v>
+      </c>
+      <c r="W54">
+        <v>0.03577</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>8.255750160598595</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.223615543005081</v>
+      </c>
+      <c r="C55">
+        <v>374.0875630980474</v>
+      </c>
+      <c r="D55">
+        <v>-150.6894369019525</v>
+      </c>
+      <c r="E55">
+        <v>384.323</v>
+      </c>
+      <c r="F55">
+        <v>423.523</v>
+      </c>
+      <c r="G55">
+        <v>948.3</v>
+      </c>
+      <c r="H55">
+        <v>759.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>322.6</v>
+      </c>
+      <c r="K55">
+        <v>147.3</v>
+      </c>
+      <c r="L55">
+        <v>175.3</v>
+      </c>
+      <c r="M55">
+        <v>21.6420253</v>
+      </c>
+      <c r="N55">
+        <v>153.6579747</v>
+      </c>
+      <c r="O55">
+        <v>46.09739241000001</v>
+      </c>
+      <c r="P55">
+        <v>107.56058229</v>
+      </c>
+      <c r="Q55">
+        <v>254.86058229</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.4354413680959169</v>
+      </c>
+      <c r="T55">
+        <v>2.103462686410865</v>
+      </c>
+      <c r="U55">
+        <v>0.0511</v>
+      </c>
+      <c r="V55">
+        <v>0.3</v>
+      </c>
+      <c r="W55">
+        <v>0.03577</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>8.099981289643903</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2229202438029225</v>
+      </c>
+      <c r="C56">
+        <v>366.0678703204546</v>
+      </c>
+      <c r="D56">
+        <v>-150.7181296795453</v>
+      </c>
+      <c r="E56">
+        <v>392.3140000000001</v>
+      </c>
+      <c r="F56">
+        <v>431.5140000000001</v>
+      </c>
+      <c r="G56">
+        <v>948.3</v>
+      </c>
+      <c r="H56">
+        <v>759.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>322.6</v>
+      </c>
+      <c r="K56">
+        <v>147.3</v>
+      </c>
+      <c r="L56">
+        <v>175.3</v>
+      </c>
+      <c r="M56">
+        <v>22.0503654</v>
+      </c>
+      <c r="N56">
+        <v>153.2496346</v>
+      </c>
+      <c r="O56">
+        <v>45.97489038000001</v>
+      </c>
+      <c r="P56">
+        <v>107.27474422</v>
+      </c>
+      <c r="Q56">
+        <v>254.57474422</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.4426183560933098</v>
+      </c>
+      <c r="T56">
+        <v>2.141523583905762</v>
+      </c>
+      <c r="U56">
+        <v>0.0511</v>
+      </c>
+      <c r="V56">
+        <v>0.3</v>
+      </c>
+      <c r="W56">
+        <v>0.03577</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>7.949981636131979</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2222249446007641</v>
+      </c>
+      <c r="C57">
+        <v>358.0481666139966</v>
+      </c>
+      <c r="D57">
+        <v>-150.7468333860033</v>
+      </c>
+      <c r="E57">
+        <v>400.3050000000001</v>
+      </c>
+      <c r="F57">
+        <v>439.5050000000001</v>
+      </c>
+      <c r="G57">
+        <v>948.3</v>
+      </c>
+      <c r="H57">
+        <v>759.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>322.6</v>
+      </c>
+      <c r="K57">
+        <v>147.3</v>
+      </c>
+      <c r="L57">
+        <v>175.3</v>
+      </c>
+      <c r="M57">
+        <v>22.4587055</v>
+      </c>
+      <c r="N57">
+        <v>152.8412945</v>
+      </c>
+      <c r="O57">
+        <v>45.85238835000001</v>
+      </c>
+      <c r="P57">
+        <v>106.98890615</v>
+      </c>
+      <c r="Q57">
+        <v>254.28890615</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.4501143213350313</v>
+      </c>
+      <c r="T57">
+        <v>2.181276076844877</v>
+      </c>
+      <c r="U57">
+        <v>0.0511</v>
+      </c>
+      <c r="V57">
+        <v>0.3</v>
+      </c>
+      <c r="W57">
+        <v>0.03577</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>7.805436515475034</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2222744453986056</v>
+      </c>
+      <c r="C58">
+        <v>350.0592104933724</v>
+      </c>
+      <c r="D58">
+        <v>-150.7447895066275</v>
+      </c>
+      <c r="E58">
+        <v>408.296</v>
+      </c>
+      <c r="F58">
+        <v>447.496</v>
+      </c>
+      <c r="G58">
+        <v>948.3</v>
+      </c>
+      <c r="H58">
+        <v>759.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>322.6</v>
+      </c>
+      <c r="K58">
+        <v>147.3</v>
+      </c>
+      <c r="L58">
+        <v>175.3</v>
+      </c>
+      <c r="M58">
+        <v>23.717288</v>
+      </c>
+      <c r="N58">
+        <v>151.582712</v>
+      </c>
+      <c r="O58">
+        <v>45.47481360000001</v>
+      </c>
+      <c r="P58">
+        <v>106.1078984</v>
+      </c>
+      <c r="Q58">
+        <v>253.4078984</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.4579510122695583</v>
+      </c>
+      <c r="T58">
+        <v>2.222835501281225</v>
+      </c>
+      <c r="U58">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.3</v>
+      </c>
+      <c r="W58">
+        <v>0.0371</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>7.391232926800062</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2215924461964472</v>
+      </c>
+      <c r="C59">
+        <v>342.0400459849934</v>
+      </c>
+      <c r="D59">
+        <v>-150.7729540150065</v>
+      </c>
+      <c r="E59">
+        <v>416.2870000000001</v>
+      </c>
+      <c r="F59">
+        <v>455.4870000000001</v>
+      </c>
+      <c r="G59">
+        <v>948.3</v>
+      </c>
+      <c r="H59">
+        <v>759.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>322.6</v>
+      </c>
+      <c r="K59">
+        <v>147.3</v>
+      </c>
+      <c r="L59">
+        <v>175.3</v>
+      </c>
+      <c r="M59">
+        <v>24.14081100000001</v>
+      </c>
+      <c r="N59">
+        <v>151.159189</v>
+      </c>
+      <c r="O59">
+        <v>45.34775670000001</v>
+      </c>
+      <c r="P59">
+        <v>105.8114323</v>
+      </c>
+      <c r="Q59">
+        <v>253.1114323</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.466152200456854</v>
+      </c>
+      <c r="T59">
+        <v>2.266327922202984</v>
+      </c>
+      <c r="U59">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V59">
+        <v>0.3</v>
+      </c>
+      <c r="W59">
+        <v>0.0371</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>7.261562173698305</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2209104469942888</v>
+      </c>
+      <c r="C60">
+        <v>334.0208709503764</v>
+      </c>
+      <c r="D60">
+        <v>-150.8011290496235</v>
+      </c>
+      <c r="E60">
+        <v>424.278</v>
+      </c>
+      <c r="F60">
+        <v>463.478</v>
+      </c>
+      <c r="G60">
+        <v>948.3</v>
+      </c>
+      <c r="H60">
+        <v>759.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>322.6</v>
+      </c>
+      <c r="K60">
+        <v>147.3</v>
+      </c>
+      <c r="L60">
+        <v>175.3</v>
+      </c>
+      <c r="M60">
+        <v>24.564334</v>
+      </c>
+      <c r="N60">
+        <v>150.735666</v>
+      </c>
+      <c r="O60">
+        <v>45.22069980000001</v>
+      </c>
+      <c r="P60">
+        <v>105.5149662</v>
+      </c>
+      <c r="Q60">
+        <v>252.8149662</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.4747439214149732</v>
+      </c>
+      <c r="T60">
+        <v>2.311891410787684</v>
+      </c>
+      <c r="U60">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V60">
+        <v>0.3</v>
+      </c>
+      <c r="W60">
+        <v>0.0371</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>7.136362825875922</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2202284477921303</v>
+      </c>
+      <c r="C61">
+        <v>326.0016853836192</v>
+      </c>
+      <c r="D61">
+        <v>-150.8293146163808</v>
+      </c>
+      <c r="E61">
+        <v>432.269</v>
+      </c>
+      <c r="F61">
+        <v>471.469</v>
+      </c>
+      <c r="G61">
+        <v>948.3</v>
+      </c>
+      <c r="H61">
+        <v>759.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>322.6</v>
+      </c>
+      <c r="K61">
+        <v>147.3</v>
+      </c>
+      <c r="L61">
+        <v>175.3</v>
+      </c>
+      <c r="M61">
+        <v>24.987857</v>
+      </c>
+      <c r="N61">
+        <v>150.312143</v>
+      </c>
+      <c r="O61">
+        <v>45.09364290000001</v>
+      </c>
+      <c r="P61">
+        <v>105.2185001</v>
+      </c>
+      <c r="Q61">
+        <v>252.5185001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.4837547507125129</v>
+      </c>
+      <c r="T61">
+        <v>2.359677508571637</v>
+      </c>
+      <c r="U61">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V61">
+        <v>0.3</v>
+      </c>
+      <c r="W61">
+        <v>0.0371</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>7.015407523742432</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2195464485899719</v>
+      </c>
+      <c r="C62">
+        <v>317.9824892788151</v>
+      </c>
+      <c r="D62">
+        <v>-150.8575107211849</v>
+      </c>
+      <c r="E62">
+        <v>440.26</v>
+      </c>
+      <c r="F62">
+        <v>479.46</v>
+      </c>
+      <c r="G62">
+        <v>948.3</v>
+      </c>
+      <c r="H62">
+        <v>759.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>322.6</v>
+      </c>
+      <c r="K62">
+        <v>147.3</v>
+      </c>
+      <c r="L62">
+        <v>175.3</v>
+      </c>
+      <c r="M62">
+        <v>25.41138</v>
+      </c>
+      <c r="N62">
+        <v>149.88862</v>
+      </c>
+      <c r="O62">
+        <v>44.96658600000001</v>
+      </c>
+      <c r="P62">
+        <v>104.922034</v>
+      </c>
+      <c r="Q62">
+        <v>252.222034</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4932161214749298</v>
+      </c>
+      <c r="T62">
+        <v>2.409852911244789</v>
+      </c>
+      <c r="U62">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V62">
+        <v>0.3</v>
+      </c>
+      <c r="W62">
+        <v>0.0371</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>6.898484065013392</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2188644493878134</v>
+      </c>
+      <c r="C63">
+        <v>309.9632826300528</v>
+      </c>
+      <c r="D63">
+        <v>-150.885717369947</v>
+      </c>
+      <c r="E63">
+        <v>448.251</v>
+      </c>
+      <c r="F63">
+        <v>487.451</v>
+      </c>
+      <c r="G63">
+        <v>948.3</v>
+      </c>
+      <c r="H63">
+        <v>759.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>322.6</v>
+      </c>
+      <c r="K63">
+        <v>147.3</v>
+      </c>
+      <c r="L63">
+        <v>175.3</v>
+      </c>
+      <c r="M63">
+        <v>25.834903</v>
+      </c>
+      <c r="N63">
+        <v>149.465097</v>
+      </c>
+      <c r="O63">
+        <v>44.83952910000001</v>
+      </c>
+      <c r="P63">
+        <v>104.6255679</v>
+      </c>
+      <c r="Q63">
+        <v>251.9255679</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.5031626907379831</v>
+      </c>
+      <c r="T63">
+        <v>2.462601411490922</v>
+      </c>
+      <c r="U63">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V63">
+        <v>0.3</v>
+      </c>
+      <c r="W63">
+        <v>0.0371</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>6.785394162308254</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.218182450185655</v>
+      </c>
+      <c r="C64">
+        <v>301.9440654314174</v>
+      </c>
+      <c r="D64">
+        <v>-150.9139345685825</v>
+      </c>
+      <c r="E64">
+        <v>456.242</v>
+      </c>
+      <c r="F64">
+        <v>495.442</v>
+      </c>
+      <c r="G64">
+        <v>948.3</v>
+      </c>
+      <c r="H64">
+        <v>759.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>322.6</v>
+      </c>
+      <c r="K64">
+        <v>147.3</v>
+      </c>
+      <c r="L64">
+        <v>175.3</v>
+      </c>
+      <c r="M64">
+        <v>26.258426</v>
+      </c>
+      <c r="N64">
+        <v>149.041574</v>
+      </c>
+      <c r="O64">
+        <v>44.71247220000001</v>
+      </c>
+      <c r="P64">
+        <v>104.3291018</v>
+      </c>
+      <c r="Q64">
+        <v>251.6291018</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.5136327636464606</v>
+      </c>
+      <c r="T64">
+        <v>2.518126148592116</v>
+      </c>
+      <c r="U64">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V64">
+        <v>0.3</v>
+      </c>
+      <c r="W64">
+        <v>0.0371</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>6.6759523209807</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2175004509834966</v>
+      </c>
+      <c r="C65">
+        <v>293.9248376769885</v>
+      </c>
+      <c r="D65">
+        <v>-150.9421623230114</v>
+      </c>
+      <c r="E65">
+        <v>464.233</v>
+      </c>
+      <c r="F65">
+        <v>503.433</v>
+      </c>
+      <c r="G65">
+        <v>948.3</v>
+      </c>
+      <c r="H65">
+        <v>759.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>322.6</v>
+      </c>
+      <c r="K65">
+        <v>147.3</v>
+      </c>
+      <c r="L65">
+        <v>175.3</v>
+      </c>
+      <c r="M65">
+        <v>26.681949</v>
+      </c>
+      <c r="N65">
+        <v>148.618051</v>
+      </c>
+      <c r="O65">
+        <v>44.58541530000001</v>
+      </c>
+      <c r="P65">
+        <v>104.0326357</v>
+      </c>
+      <c r="Q65">
+        <v>251.3326357</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.5246687864418828</v>
+      </c>
+      <c r="T65">
+        <v>2.576652222833915</v>
+      </c>
+      <c r="U65">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V65">
+        <v>0.3</v>
+      </c>
+      <c r="W65">
+        <v>0.0371</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>6.569984823822278</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2168184517813381</v>
+      </c>
+      <c r="C66">
+        <v>285.9055993608419</v>
+      </c>
+      <c r="D66">
+        <v>-150.970400639158</v>
+      </c>
+      <c r="E66">
+        <v>472.224</v>
+      </c>
+      <c r="F66">
+        <v>511.424</v>
+      </c>
+      <c r="G66">
+        <v>948.3</v>
+      </c>
+      <c r="H66">
+        <v>759.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>322.6</v>
+      </c>
+      <c r="K66">
+        <v>147.3</v>
+      </c>
+      <c r="L66">
+        <v>175.3</v>
+      </c>
+      <c r="M66">
+        <v>27.10547200000001</v>
+      </c>
+      <c r="N66">
+        <v>148.194528</v>
+      </c>
+      <c r="O66">
+        <v>44.4583584</v>
+      </c>
+      <c r="P66">
+        <v>103.7361696</v>
+      </c>
+      <c r="Q66">
+        <v>251.0361696</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.5363179216148282</v>
+      </c>
+      <c r="T66">
+        <v>2.638429745644701</v>
+      </c>
+      <c r="U66">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V66">
+        <v>0.3</v>
+      </c>
+      <c r="W66">
+        <v>0.0371</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>6.467328810950053</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2161364525791797</v>
+      </c>
+      <c r="C67">
+        <v>277.8863504770488</v>
+      </c>
+      <c r="D67">
+        <v>-150.9986495229511</v>
+      </c>
+      <c r="E67">
+        <v>480.2150000000001</v>
+      </c>
+      <c r="F67">
+        <v>519.4150000000001</v>
+      </c>
+      <c r="G67">
+        <v>948.3</v>
+      </c>
+      <c r="H67">
+        <v>759.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>322.6</v>
+      </c>
+      <c r="K67">
+        <v>147.3</v>
+      </c>
+      <c r="L67">
+        <v>175.3</v>
+      </c>
+      <c r="M67">
+        <v>27.52899500000001</v>
+      </c>
+      <c r="N67">
+        <v>147.771005</v>
+      </c>
+      <c r="O67">
+        <v>44.33130150000001</v>
+      </c>
+      <c r="P67">
+        <v>103.4397035</v>
+      </c>
+      <c r="Q67">
+        <v>250.7397035</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.5486327216547993</v>
+      </c>
+      <c r="T67">
+        <v>2.703737412616105</v>
+      </c>
+      <c r="U67">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V67">
+        <v>0.3</v>
+      </c>
+      <c r="W67">
+        <v>0.0371</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>6.367831444627745</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2154544533770213</v>
+      </c>
+      <c r="C68">
+        <v>269.8670910196761</v>
+      </c>
+      <c r="D68">
+        <v>-151.0269089803238</v>
+      </c>
+      <c r="E68">
+        <v>488.2060000000001</v>
+      </c>
+      <c r="F68">
+        <v>527.4060000000001</v>
+      </c>
+      <c r="G68">
+        <v>948.3</v>
+      </c>
+      <c r="H68">
+        <v>759.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>322.6</v>
+      </c>
+      <c r="K68">
+        <v>147.3</v>
+      </c>
+      <c r="L68">
+        <v>175.3</v>
+      </c>
+      <c r="M68">
+        <v>27.952518</v>
+      </c>
+      <c r="N68">
+        <v>147.347482</v>
+      </c>
+      <c r="O68">
+        <v>44.20424460000001</v>
+      </c>
+      <c r="P68">
+        <v>103.1432374</v>
+      </c>
+      <c r="Q68">
+        <v>250.4432374</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.5616719216971215</v>
+      </c>
+      <c r="T68">
+        <v>2.772886707056415</v>
+      </c>
+      <c r="U68">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.3</v>
+      </c>
+      <c r="W68">
+        <v>0.0371</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>6.271349150012174</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2157104541748628</v>
+      </c>
+      <c r="C69">
+        <v>261.8866999606527</v>
+      </c>
+      <c r="D69">
+        <v>-151.0163000393473</v>
+      </c>
+      <c r="E69">
+        <v>496.1970000000001</v>
+      </c>
+      <c r="F69">
+        <v>535.397</v>
+      </c>
+      <c r="G69">
+        <v>948.3</v>
+      </c>
+      <c r="H69">
+        <v>759.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>322.6</v>
+      </c>
+      <c r="K69">
+        <v>147.3</v>
+      </c>
+      <c r="L69">
+        <v>175.3</v>
+      </c>
+      <c r="M69">
+        <v>29.446835</v>
+      </c>
+      <c r="N69">
+        <v>145.853165</v>
+      </c>
+      <c r="O69">
+        <v>43.75594950000001</v>
+      </c>
+      <c r="P69">
+        <v>102.0972155</v>
+      </c>
+      <c r="Q69">
+        <v>249.3972155</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.5755013762874632</v>
+      </c>
+      <c r="T69">
+        <v>2.84622686782644</v>
+      </c>
+      <c r="U69">
+        <v>0.055</v>
+      </c>
+      <c r="V69">
+        <v>0.3</v>
+      </c>
+      <c r="W69">
+        <v>0.0385</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>5.953101581205586</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2150424549727044</v>
+      </c>
+      <c r="C70">
+        <v>253.8680142445304</v>
+      </c>
+      <c r="D70">
+        <v>-151.0439857554695</v>
+      </c>
+      <c r="E70">
+        <v>504.188</v>
+      </c>
+      <c r="F70">
+        <v>543.388</v>
+      </c>
+      <c r="G70">
+        <v>948.3</v>
+      </c>
+      <c r="H70">
+        <v>759.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>322.6</v>
+      </c>
+      <c r="K70">
+        <v>147.3</v>
+      </c>
+      <c r="L70">
+        <v>175.3</v>
+      </c>
+      <c r="M70">
+        <v>29.88634</v>
+      </c>
+      <c r="N70">
+        <v>145.41366</v>
+      </c>
+      <c r="O70">
+        <v>43.62409800000001</v>
+      </c>
+      <c r="P70">
+        <v>101.789562</v>
+      </c>
+      <c r="Q70">
+        <v>249.089562</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.5901951717897014</v>
+      </c>
+      <c r="T70">
+        <v>2.924150788644592</v>
+      </c>
+      <c r="U70">
+        <v>0.055</v>
+      </c>
+      <c r="V70">
+        <v>0.3</v>
+      </c>
+      <c r="W70">
+        <v>0.0385</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>5.86555596971727</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.214374455770546</v>
+      </c>
+      <c r="C71">
+        <v>245.8493183753396</v>
+      </c>
+      <c r="D71">
+        <v>-151.0716816246603</v>
+      </c>
+      <c r="E71">
+        <v>512.179</v>
+      </c>
+      <c r="F71">
+        <v>551.379</v>
+      </c>
+      <c r="G71">
+        <v>948.3</v>
+      </c>
+      <c r="H71">
+        <v>759.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>322.6</v>
+      </c>
+      <c r="K71">
+        <v>147.3</v>
+      </c>
+      <c r="L71">
+        <v>175.3</v>
+      </c>
+      <c r="M71">
+        <v>30.325845</v>
+      </c>
+      <c r="N71">
+        <v>144.974155</v>
+      </c>
+      <c r="O71">
+        <v>43.49224650000001</v>
+      </c>
+      <c r="P71">
+        <v>101.4819085</v>
+      </c>
+      <c r="Q71">
+        <v>248.7819085</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.6058369540985356</v>
+      </c>
+      <c r="T71">
+        <v>3.007102059192948</v>
+      </c>
+      <c r="U71">
+        <v>0.055</v>
+      </c>
+      <c r="V71">
+        <v>0.3</v>
+      </c>
+      <c r="W71">
+        <v>0.0385</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>5.780547912185134</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2137064565683876</v>
+      </c>
+      <c r="C72">
+        <v>237.830612347494</v>
+      </c>
+      <c r="D72">
+        <v>-151.0993876525058</v>
+      </c>
+      <c r="E72">
+        <v>520.1700000000001</v>
+      </c>
+      <c r="F72">
+        <v>559.3700000000001</v>
+      </c>
+      <c r="G72">
+        <v>948.3</v>
+      </c>
+      <c r="H72">
+        <v>759.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>322.6</v>
+      </c>
+      <c r="K72">
+        <v>147.3</v>
+      </c>
+      <c r="L72">
+        <v>175.3</v>
+      </c>
+      <c r="M72">
+        <v>30.76535000000001</v>
+      </c>
+      <c r="N72">
+        <v>144.53465</v>
+      </c>
+      <c r="O72">
+        <v>43.360395</v>
+      </c>
+      <c r="P72">
+        <v>101.174255</v>
+      </c>
+      <c r="Q72">
+        <v>248.474255</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.6225215218946254</v>
+      </c>
+      <c r="T72">
+        <v>3.095583414444527</v>
+      </c>
+      <c r="U72">
+        <v>0.055</v>
+      </c>
+      <c r="V72">
+        <v>0.3</v>
+      </c>
+      <c r="W72">
+        <v>0.0385</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>5.697968656296775</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2130384573662291</v>
+      </c>
+      <c r="C73">
+        <v>229.8118961554038</v>
+      </c>
+      <c r="D73">
+        <v>-151.1271038445961</v>
+      </c>
+      <c r="E73">
+        <v>528.1609999999999</v>
+      </c>
+      <c r="F73">
+        <v>567.361</v>
+      </c>
+      <c r="G73">
+        <v>948.3</v>
+      </c>
+      <c r="H73">
+        <v>759.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>322.6</v>
+      </c>
+      <c r="K73">
+        <v>147.3</v>
+      </c>
+      <c r="L73">
+        <v>175.3</v>
+      </c>
+      <c r="M73">
+        <v>31.204855</v>
+      </c>
+      <c r="N73">
+        <v>144.095145</v>
+      </c>
+      <c r="O73">
+        <v>43.22854350000001</v>
+      </c>
+      <c r="P73">
+        <v>100.8666015</v>
+      </c>
+      <c r="Q73">
+        <v>248.1666015</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.640356749538721</v>
+      </c>
+      <c r="T73">
+        <v>3.190166932127248</v>
+      </c>
+      <c r="U73">
+        <v>0.055</v>
+      </c>
+      <c r="V73">
+        <v>0.3</v>
+      </c>
+      <c r="W73">
+        <v>0.0385</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>5.617715576630624</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2123704581640707</v>
+      </c>
+      <c r="C74">
+        <v>221.7931697934742</v>
+      </c>
+      <c r="D74">
+        <v>-151.1548302065257</v>
+      </c>
+      <c r="E74">
+        <v>536.1519999999999</v>
+      </c>
+      <c r="F74">
+        <v>575.352</v>
+      </c>
+      <c r="G74">
+        <v>948.3</v>
+      </c>
+      <c r="H74">
+        <v>759.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>322.6</v>
+      </c>
+      <c r="K74">
+        <v>147.3</v>
+      </c>
+      <c r="L74">
+        <v>175.3</v>
+      </c>
+      <c r="M74">
+        <v>31.64436</v>
+      </c>
+      <c r="N74">
+        <v>143.65564</v>
+      </c>
+      <c r="O74">
+        <v>43.096692</v>
+      </c>
+      <c r="P74">
+        <v>100.558948</v>
+      </c>
+      <c r="Q74">
+        <v>247.858948</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.6594659220145382</v>
+      </c>
+      <c r="T74">
+        <v>3.291506415358736</v>
+      </c>
+      <c r="U74">
+        <v>0.055</v>
+      </c>
+      <c r="V74">
+        <v>0.3</v>
+      </c>
+      <c r="W74">
+        <v>0.0385</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>5.539691749177421</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2117024589619122</v>
+      </c>
+      <c r="C75">
+        <v>213.774433256107</v>
+      </c>
+      <c r="D75">
+        <v>-151.1825667438929</v>
+      </c>
+      <c r="E75">
+        <v>544.1429999999999</v>
+      </c>
+      <c r="F75">
+        <v>583.343</v>
+      </c>
+      <c r="G75">
+        <v>948.3</v>
+      </c>
+      <c r="H75">
+        <v>759.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>322.6</v>
+      </c>
+      <c r="K75">
+        <v>147.3</v>
+      </c>
+      <c r="L75">
+        <v>175.3</v>
+      </c>
+      <c r="M75">
+        <v>32.083865</v>
+      </c>
+      <c r="N75">
+        <v>143.216135</v>
+      </c>
+      <c r="O75">
+        <v>42.96484050000001</v>
+      </c>
+      <c r="P75">
+        <v>100.2512945</v>
+      </c>
+      <c r="Q75">
+        <v>247.5512945</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.679990588747823</v>
+      </c>
+      <c r="T75">
+        <v>3.400352526977742</v>
+      </c>
+      <c r="U75">
+        <v>0.055</v>
+      </c>
+      <c r="V75">
+        <v>0.3</v>
+      </c>
+      <c r="W75">
+        <v>0.0385</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>5.463805560832525</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2110344597597538</v>
+      </c>
+      <c r="C76">
+        <v>205.7556865376996</v>
+      </c>
+      <c r="D76">
+        <v>-151.2103134623003</v>
+      </c>
+      <c r="E76">
+        <v>552.134</v>
+      </c>
+      <c r="F76">
+        <v>591.3340000000001</v>
+      </c>
+      <c r="G76">
+        <v>948.3</v>
+      </c>
+      <c r="H76">
+        <v>759.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>322.6</v>
+      </c>
+      <c r="K76">
+        <v>147.3</v>
+      </c>
+      <c r="L76">
+        <v>175.3</v>
+      </c>
+      <c r="M76">
+        <v>32.52337000000001</v>
+      </c>
+      <c r="N76">
+        <v>142.77663</v>
+      </c>
+      <c r="O76">
+        <v>42.83298900000001</v>
+      </c>
+      <c r="P76">
+        <v>99.943641</v>
+      </c>
+      <c r="Q76">
+        <v>247.243641</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.702094075999053</v>
+      </c>
+      <c r="T76">
+        <v>3.517571416413594</v>
+      </c>
+      <c r="U76">
+        <v>0.055</v>
+      </c>
+      <c r="V76">
+        <v>0.3</v>
+      </c>
+      <c r="W76">
+        <v>0.0385</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>5.389970350551003</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2103664605575953</v>
+      </c>
+      <c r="C77">
+        <v>197.7369296326455</v>
+      </c>
+      <c r="D77">
+        <v>-151.2380703673545</v>
+      </c>
+      <c r="E77">
+        <v>560.125</v>
+      </c>
+      <c r="F77">
+        <v>599.325</v>
+      </c>
+      <c r="G77">
+        <v>948.3</v>
+      </c>
+      <c r="H77">
+        <v>759.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>322.6</v>
+      </c>
+      <c r="K77">
+        <v>147.3</v>
+      </c>
+      <c r="L77">
+        <v>175.3</v>
+      </c>
+      <c r="M77">
+        <v>32.962875</v>
+      </c>
+      <c r="N77">
+        <v>142.337125</v>
+      </c>
+      <c r="O77">
+        <v>42.70113750000001</v>
+      </c>
+      <c r="P77">
+        <v>99.6359875</v>
+      </c>
+      <c r="Q77">
+        <v>246.9359875</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.7259658422303814</v>
+      </c>
+      <c r="T77">
+        <v>3.644167817004315</v>
+      </c>
+      <c r="U77">
+        <v>0.055</v>
+      </c>
+      <c r="V77">
+        <v>0.3</v>
+      </c>
+      <c r="W77">
+        <v>0.0385</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>5.318104079210324</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.209698461355437</v>
+      </c>
+      <c r="C78">
+        <v>189.7181625353337</v>
+      </c>
+      <c r="D78">
+        <v>-151.2658374646662</v>
+      </c>
+      <c r="E78">
+        <v>568.116</v>
+      </c>
+      <c r="F78">
+        <v>607.316</v>
+      </c>
+      <c r="G78">
+        <v>948.3</v>
+      </c>
+      <c r="H78">
+        <v>759.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>322.6</v>
+      </c>
+      <c r="K78">
+        <v>147.3</v>
+      </c>
+      <c r="L78">
+        <v>175.3</v>
+      </c>
+      <c r="M78">
+        <v>33.40238</v>
+      </c>
+      <c r="N78">
+        <v>141.89762</v>
+      </c>
+      <c r="O78">
+        <v>42.56928600000001</v>
+      </c>
+      <c r="P78">
+        <v>99.32833400000001</v>
+      </c>
+      <c r="Q78">
+        <v>246.628334</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.7518269223143208</v>
+      </c>
+      <c r="T78">
+        <v>3.781313917644263</v>
+      </c>
+      <c r="U78">
+        <v>0.055</v>
+      </c>
+      <c r="V78">
+        <v>0.3</v>
+      </c>
+      <c r="W78">
+        <v>0.0385</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>5.248129025536504</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2090304621532785</v>
+      </c>
+      <c r="C79">
+        <v>181.6993852401496</v>
+      </c>
+      <c r="D79">
+        <v>-151.2936147598504</v>
+      </c>
+      <c r="E79">
+        <v>576.107</v>
+      </c>
+      <c r="F79">
+        <v>615.307</v>
+      </c>
+      <c r="G79">
+        <v>948.3</v>
+      </c>
+      <c r="H79">
+        <v>759.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>322.6</v>
+      </c>
+      <c r="K79">
+        <v>147.3</v>
+      </c>
+      <c r="L79">
+        <v>175.3</v>
+      </c>
+      <c r="M79">
+        <v>33.841885</v>
+      </c>
+      <c r="N79">
+        <v>141.458115</v>
+      </c>
+      <c r="O79">
+        <v>42.43743450000001</v>
+      </c>
+      <c r="P79">
+        <v>99.02068050000001</v>
+      </c>
+      <c r="Q79">
+        <v>246.3206805</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.7799367919707763</v>
+      </c>
+      <c r="T79">
+        <v>3.930385766165945</v>
+      </c>
+      <c r="U79">
+        <v>0.055</v>
+      </c>
+      <c r="V79">
+        <v>0.3</v>
+      </c>
+      <c r="W79">
+        <v>0.0385</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>5.179971505724343</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2083624629511201</v>
+      </c>
+      <c r="C80">
+        <v>173.6805977414739</v>
+      </c>
+      <c r="D80">
+        <v>-151.3214022585261</v>
+      </c>
+      <c r="E80">
+        <v>584.098</v>
+      </c>
+      <c r="F80">
+        <v>623.298</v>
+      </c>
+      <c r="G80">
+        <v>948.3</v>
+      </c>
+      <c r="H80">
+        <v>759.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>322.6</v>
+      </c>
+      <c r="K80">
+        <v>147.3</v>
+      </c>
+      <c r="L80">
+        <v>175.3</v>
+      </c>
+      <c r="M80">
+        <v>34.28139</v>
+      </c>
+      <c r="N80">
+        <v>141.01861</v>
+      </c>
+      <c r="O80">
+        <v>42.30558300000001</v>
+      </c>
+      <c r="P80">
+        <v>98.71302700000001</v>
+      </c>
+      <c r="Q80">
+        <v>246.013027</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.8106021043232732</v>
+      </c>
+      <c r="T80">
+        <v>4.09300960091687</v>
+      </c>
+      <c r="U80">
+        <v>0.055</v>
+      </c>
+      <c r="V80">
+        <v>0.3</v>
+      </c>
+      <c r="W80">
+        <v>0.0385</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>5.113561614625311</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2076944637489616</v>
+      </c>
+      <c r="C81">
+        <v>165.6618000336836</v>
+      </c>
+      <c r="D81">
+        <v>-151.3491999663163</v>
+      </c>
+      <c r="E81">
+        <v>592.0890000000001</v>
+      </c>
+      <c r="F81">
+        <v>631.2890000000001</v>
+      </c>
+      <c r="G81">
+        <v>948.3</v>
+      </c>
+      <c r="H81">
+        <v>759.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>322.6</v>
+      </c>
+      <c r="K81">
+        <v>147.3</v>
+      </c>
+      <c r="L81">
+        <v>175.3</v>
+      </c>
+      <c r="M81">
+        <v>34.72089500000001</v>
+      </c>
+      <c r="N81">
+        <v>140.579105</v>
+      </c>
+      <c r="O81">
+        <v>42.1737315</v>
+      </c>
+      <c r="P81">
+        <v>98.4053735</v>
+      </c>
+      <c r="Q81">
+        <v>245.7053735</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.8441879226141031</v>
+      </c>
+      <c r="T81">
+        <v>4.27112141992979</v>
+      </c>
+      <c r="U81">
+        <v>0.055</v>
+      </c>
+      <c r="V81">
+        <v>0.3</v>
+      </c>
+      <c r="W81">
+        <v>0.0385</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>5.048832986592079</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2070264645468032</v>
+      </c>
+      <c r="C82">
+        <v>157.6429921111514</v>
+      </c>
+      <c r="D82">
+        <v>-151.3770078888484</v>
+      </c>
+      <c r="E82">
+        <v>600.08</v>
+      </c>
+      <c r="F82">
+        <v>639.2800000000001</v>
+      </c>
+      <c r="G82">
+        <v>948.3</v>
+      </c>
+      <c r="H82">
+        <v>759.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>322.6</v>
+      </c>
+      <c r="K82">
+        <v>147.3</v>
+      </c>
+      <c r="L82">
+        <v>175.3</v>
+      </c>
+      <c r="M82">
+        <v>35.1604</v>
+      </c>
+      <c r="N82">
+        <v>140.1396</v>
+      </c>
+      <c r="O82">
+        <v>42.04188000000001</v>
+      </c>
+      <c r="P82">
+        <v>98.09772</v>
+      </c>
+      <c r="Q82">
+        <v>245.39772</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.8811323227340162</v>
+      </c>
+      <c r="T82">
+        <v>4.467044420844</v>
+      </c>
+      <c r="U82">
+        <v>0.055</v>
+      </c>
+      <c r="V82">
+        <v>0.3</v>
+      </c>
+      <c r="W82">
+        <v>0.0385</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>4.985722574259678</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2063584653446448</v>
+      </c>
+      <c r="C83">
+        <v>149.6241739682461</v>
+      </c>
+      <c r="D83">
+        <v>-151.4048260317538</v>
+      </c>
+      <c r="E83">
+        <v>608.071</v>
+      </c>
+      <c r="F83">
+        <v>647.2710000000001</v>
+      </c>
+      <c r="G83">
+        <v>948.3</v>
+      </c>
+      <c r="H83">
+        <v>759.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>322.6</v>
+      </c>
+      <c r="K83">
+        <v>147.3</v>
+      </c>
+      <c r="L83">
+        <v>175.3</v>
+      </c>
+      <c r="M83">
+        <v>35.59990500000001</v>
+      </c>
+      <c r="N83">
+        <v>139.700095</v>
+      </c>
+      <c r="O83">
+        <v>41.91002850000001</v>
+      </c>
+      <c r="P83">
+        <v>97.79006649999999</v>
+      </c>
+      <c r="Q83">
+        <v>245.0900665</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.9219656070770781</v>
+      </c>
+      <c r="T83">
+        <v>4.683590895538654</v>
+      </c>
+      <c r="U83">
+        <v>0.055</v>
+      </c>
+      <c r="V83">
+        <v>0.3</v>
+      </c>
+      <c r="W83">
+        <v>0.0385</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>4.924170443713262</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2056904661424863</v>
+      </c>
+      <c r="C84">
+        <v>141.6053455993318</v>
+      </c>
+      <c r="D84">
+        <v>-151.432654400668</v>
+      </c>
+      <c r="E84">
+        <v>616.062</v>
+      </c>
+      <c r="F84">
+        <v>655.2620000000001</v>
+      </c>
+      <c r="G84">
+        <v>948.3</v>
+      </c>
+      <c r="H84">
+        <v>759.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>322.6</v>
+      </c>
+      <c r="K84">
+        <v>147.3</v>
+      </c>
+      <c r="L84">
+        <v>175.3</v>
+      </c>
+      <c r="M84">
+        <v>36.03941</v>
+      </c>
+      <c r="N84">
+        <v>139.26059</v>
+      </c>
+      <c r="O84">
+        <v>41.77817700000001</v>
+      </c>
+      <c r="P84">
+        <v>97.48241300000001</v>
+      </c>
+      <c r="Q84">
+        <v>244.782413</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.9673359230138132</v>
+      </c>
+      <c r="T84">
+        <v>4.924198089643825</v>
+      </c>
+      <c r="U84">
+        <v>0.055</v>
+      </c>
+      <c r="V84">
+        <v>0.3</v>
+      </c>
+      <c r="W84">
+        <v>0.0385</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>4.864119584643589</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2050224669403279</v>
+      </c>
+      <c r="C85">
+        <v>133.5865069987691</v>
+      </c>
+      <c r="D85">
+        <v>-151.4604930012308</v>
+      </c>
+      <c r="E85">
+        <v>624.053</v>
+      </c>
+      <c r="F85">
+        <v>663.253</v>
+      </c>
+      <c r="G85">
+        <v>948.3</v>
+      </c>
+      <c r="H85">
+        <v>759.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>322.6</v>
+      </c>
+      <c r="K85">
+        <v>147.3</v>
+      </c>
+      <c r="L85">
+        <v>175.3</v>
+      </c>
+      <c r="M85">
+        <v>36.478915</v>
+      </c>
+      <c r="N85">
+        <v>138.821085</v>
+      </c>
+      <c r="O85">
+        <v>41.64632550000001</v>
+      </c>
+      <c r="P85">
+        <v>97.17475949999999</v>
+      </c>
+      <c r="Q85">
+        <v>244.4747595</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.0180439231784</v>
+      </c>
+      <c r="T85">
+        <v>5.193112012467252</v>
+      </c>
+      <c r="U85">
+        <v>0.055</v>
+      </c>
+      <c r="V85">
+        <v>0.3</v>
+      </c>
+      <c r="W85">
+        <v>0.0385</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>4.805515734226196</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2043544677381695</v>
+      </c>
+      <c r="C86">
+        <v>125.5676581609141</v>
+      </c>
+      <c r="D86">
+        <v>-151.4883418390858</v>
+      </c>
+      <c r="E86">
+        <v>632.044</v>
+      </c>
+      <c r="F86">
+        <v>671.244</v>
+      </c>
+      <c r="G86">
+        <v>948.3</v>
+      </c>
+      <c r="H86">
+        <v>759.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>322.6</v>
+      </c>
+      <c r="K86">
+        <v>147.3</v>
+      </c>
+      <c r="L86">
+        <v>175.3</v>
+      </c>
+      <c r="M86">
+        <v>36.91842</v>
+      </c>
+      <c r="N86">
+        <v>138.38158</v>
+      </c>
+      <c r="O86">
+        <v>41.51447400000001</v>
+      </c>
+      <c r="P86">
+        <v>96.86710600000001</v>
+      </c>
+      <c r="Q86">
+        <v>244.167106</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.075090423363559</v>
+      </c>
+      <c r="T86">
+        <v>5.495640175643604</v>
+      </c>
+      <c r="U86">
+        <v>0.055</v>
+      </c>
+      <c r="V86">
+        <v>0.3</v>
+      </c>
+      <c r="W86">
+        <v>0.0385</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>4.748307213580646</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2036864685360111</v>
+      </c>
+      <c r="C87">
+        <v>117.5487990801187</v>
+      </c>
+      <c r="D87">
+        <v>-151.5162009198813</v>
+      </c>
+      <c r="E87">
+        <v>640.035</v>
+      </c>
+      <c r="F87">
+        <v>679.235</v>
+      </c>
+      <c r="G87">
+        <v>948.3</v>
+      </c>
+      <c r="H87">
+        <v>759.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>322.6</v>
+      </c>
+      <c r="K87">
+        <v>147.3</v>
+      </c>
+      <c r="L87">
+        <v>175.3</v>
+      </c>
+      <c r="M87">
+        <v>37.357925</v>
+      </c>
+      <c r="N87">
+        <v>137.942075</v>
+      </c>
+      <c r="O87">
+        <v>41.38262250000001</v>
+      </c>
+      <c r="P87">
+        <v>96.55945250000001</v>
+      </c>
+      <c r="Q87">
+        <v>243.8594525</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.139743123573407</v>
+      </c>
+      <c r="T87">
+        <v>5.838505427243472</v>
+      </c>
+      <c r="U87">
+        <v>0.055</v>
+      </c>
+      <c r="V87">
+        <v>0.3</v>
+      </c>
+      <c r="W87">
+        <v>0.0385</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>4.692444775773815</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2030184693338526</v>
+      </c>
+      <c r="C88">
+        <v>109.5299297507307</v>
+      </c>
+      <c r="D88">
+        <v>-151.5440702492692</v>
+      </c>
+      <c r="E88">
+        <v>648.026</v>
+      </c>
+      <c r="F88">
+        <v>687.226</v>
+      </c>
+      <c r="G88">
+        <v>948.3</v>
+      </c>
+      <c r="H88">
+        <v>759.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>322.6</v>
+      </c>
+      <c r="K88">
+        <v>147.3</v>
+      </c>
+      <c r="L88">
+        <v>175.3</v>
+      </c>
+      <c r="M88">
+        <v>37.79743</v>
+      </c>
+      <c r="N88">
+        <v>137.50257</v>
+      </c>
+      <c r="O88">
+        <v>41.25077100000001</v>
+      </c>
+      <c r="P88">
+        <v>96.25179900000001</v>
+      </c>
+      <c r="Q88">
+        <v>243.551799</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.213631923813233</v>
+      </c>
+      <c r="T88">
+        <v>6.230351429071893</v>
+      </c>
+      <c r="U88">
+        <v>0.055</v>
+      </c>
+      <c r="V88">
+        <v>0.3</v>
+      </c>
+      <c r="W88">
+        <v>0.0385</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>4.637881464427609</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2023504701316942</v>
+      </c>
+      <c r="C89">
+        <v>101.5110501670941</v>
+      </c>
+      <c r="D89">
+        <v>-151.5719498329059</v>
+      </c>
+      <c r="E89">
+        <v>656.0169999999999</v>
+      </c>
+      <c r="F89">
+        <v>695.217</v>
+      </c>
+      <c r="G89">
+        <v>948.3</v>
+      </c>
+      <c r="H89">
+        <v>759.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>322.6</v>
+      </c>
+      <c r="K89">
+        <v>147.3</v>
+      </c>
+      <c r="L89">
+        <v>175.3</v>
+      </c>
+      <c r="M89">
+        <v>38.236935</v>
+      </c>
+      <c r="N89">
+        <v>137.063065</v>
+      </c>
+      <c r="O89">
+        <v>41.1189195</v>
+      </c>
+      <c r="P89">
+        <v>95.94414549999999</v>
+      </c>
+      <c r="Q89">
+        <v>243.2441455</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.298888231782263</v>
+      </c>
+      <c r="T89">
+        <v>6.682481431181611</v>
+      </c>
+      <c r="U89">
+        <v>0.055</v>
+      </c>
+      <c r="V89">
+        <v>0.3</v>
+      </c>
+      <c r="W89">
+        <v>0.0385</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>4.584572482077865</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2016824709295358</v>
+      </c>
+      <c r="C90">
+        <v>93.49216032354809</v>
+      </c>
+      <c r="D90">
+        <v>-151.5998396764519</v>
+      </c>
+      <c r="E90">
+        <v>664.0079999999999</v>
+      </c>
+      <c r="F90">
+        <v>703.208</v>
+      </c>
+      <c r="G90">
+        <v>948.3</v>
+      </c>
+      <c r="H90">
+        <v>759.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>322.6</v>
+      </c>
+      <c r="K90">
+        <v>147.3</v>
+      </c>
+      <c r="L90">
+        <v>175.3</v>
+      </c>
+      <c r="M90">
+        <v>38.67644</v>
+      </c>
+      <c r="N90">
+        <v>136.62356</v>
+      </c>
+      <c r="O90">
+        <v>40.98706800000001</v>
+      </c>
+      <c r="P90">
+        <v>95.63649199999999</v>
+      </c>
+      <c r="Q90">
+        <v>242.936492</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.398353924412798</v>
+      </c>
+      <c r="T90">
+        <v>7.209966433642948</v>
+      </c>
+      <c r="U90">
+        <v>0.055</v>
+      </c>
+      <c r="V90">
+        <v>0.3</v>
+      </c>
+      <c r="W90">
+        <v>0.0385</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>4.532475067508798</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2033818717273773</v>
+      </c>
+      <c r="C91">
+        <v>85.57209238913606</v>
+      </c>
+      <c r="D91">
+        <v>-151.5289076108638</v>
+      </c>
+      <c r="E91">
+        <v>671.999</v>
+      </c>
+      <c r="F91">
+        <v>711.1990000000001</v>
+      </c>
+      <c r="G91">
+        <v>948.3</v>
+      </c>
+      <c r="H91">
+        <v>759.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>322.6</v>
+      </c>
+      <c r="K91">
+        <v>147.3</v>
+      </c>
+      <c r="L91">
+        <v>175.3</v>
+      </c>
+      <c r="M91">
+        <v>41.81850120000001</v>
+      </c>
+      <c r="N91">
+        <v>133.4814988</v>
+      </c>
+      <c r="O91">
+        <v>40.04444964</v>
+      </c>
+      <c r="P91">
+        <v>93.43704915999999</v>
+      </c>
+      <c r="Q91">
+        <v>240.73704916</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.515904288430703</v>
+      </c>
+      <c r="T91">
+        <v>7.833357800188163</v>
+      </c>
+      <c r="U91">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V91">
+        <v>0.3</v>
+      </c>
+      <c r="W91">
+        <v>0.04116</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>4.191924506371356</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2027404725252189</v>
+      </c>
+      <c r="C92">
+        <v>77.55432853492266</v>
+      </c>
+      <c r="D92">
+        <v>-151.5556714650772</v>
+      </c>
+      <c r="E92">
+        <v>679.99</v>
+      </c>
+      <c r="F92">
+        <v>719.1900000000001</v>
+      </c>
+      <c r="G92">
+        <v>948.3</v>
+      </c>
+      <c r="H92">
+        <v>759.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>322.6</v>
+      </c>
+      <c r="K92">
+        <v>147.3</v>
+      </c>
+      <c r="L92">
+        <v>175.3</v>
+      </c>
+      <c r="M92">
+        <v>42.28837200000001</v>
+      </c>
+      <c r="N92">
+        <v>133.011628</v>
+      </c>
+      <c r="O92">
+        <v>39.90348840000001</v>
+      </c>
+      <c r="P92">
+        <v>93.10813959999999</v>
+      </c>
+      <c r="Q92">
+        <v>240.4081396</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.656964725252189</v>
+      </c>
+      <c r="T92">
+        <v>8.581427440042422</v>
+      </c>
+      <c r="U92">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V92">
+        <v>0.3</v>
+      </c>
+      <c r="W92">
+        <v>0.04116</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>4.145347567411674</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2020990733230605</v>
+      </c>
+      <c r="C93">
+        <v>69.53655522468614</v>
+      </c>
+      <c r="D93">
+        <v>-151.5824447753138</v>
+      </c>
+      <c r="E93">
+        <v>687.981</v>
+      </c>
+      <c r="F93">
+        <v>727.181</v>
+      </c>
+      <c r="G93">
+        <v>948.3</v>
+      </c>
+      <c r="H93">
+        <v>759.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>322.6</v>
+      </c>
+      <c r="K93">
+        <v>147.3</v>
+      </c>
+      <c r="L93">
+        <v>175.3</v>
+      </c>
+      <c r="M93">
+        <v>42.7582428</v>
+      </c>
+      <c r="N93">
+        <v>132.5417572</v>
+      </c>
+      <c r="O93">
+        <v>39.76252716</v>
+      </c>
+      <c r="P93">
+        <v>92.77923004</v>
+      </c>
+      <c r="Q93">
+        <v>240.07923004</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.829371925811783</v>
+      </c>
+      <c r="T93">
+        <v>9.495734777642072</v>
+      </c>
+      <c r="U93">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V93">
+        <v>0.3</v>
+      </c>
+      <c r="W93">
+        <v>0.04116</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>4.099794297440118</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.201457674120902</v>
+      </c>
+      <c r="C94">
+        <v>61.51877245341404</v>
+      </c>
+      <c r="D94">
+        <v>-151.6092275465859</v>
+      </c>
+      <c r="E94">
+        <v>695.972</v>
+      </c>
+      <c r="F94">
+        <v>735.172</v>
+      </c>
+      <c r="G94">
+        <v>948.3</v>
+      </c>
+      <c r="H94">
+        <v>759.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>322.6</v>
+      </c>
+      <c r="K94">
+        <v>147.3</v>
+      </c>
+      <c r="L94">
+        <v>175.3</v>
+      </c>
+      <c r="M94">
+        <v>43.22811360000001</v>
+      </c>
+      <c r="N94">
+        <v>132.0718864</v>
+      </c>
+      <c r="O94">
+        <v>39.62156592000001</v>
+      </c>
+      <c r="P94">
+        <v>92.45032048</v>
+      </c>
+      <c r="Q94">
+        <v>239.75032048</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>2.044880926511276</v>
+      </c>
+      <c r="T94">
+        <v>10.63861894964164</v>
+      </c>
+      <c r="U94">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V94">
+        <v>0.3</v>
+      </c>
+      <c r="W94">
+        <v>0.04116</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>4.055231315946203</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2008162749187436</v>
+      </c>
+      <c r="C95">
+        <v>53.50098021609062</v>
+      </c>
+      <c r="D95">
+        <v>-151.6360197839093</v>
+      </c>
+      <c r="E95">
+        <v>703.963</v>
+      </c>
+      <c r="F95">
+        <v>743.163</v>
+      </c>
+      <c r="G95">
+        <v>948.3</v>
+      </c>
+      <c r="H95">
+        <v>759.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>322.6</v>
+      </c>
+      <c r="K95">
+        <v>147.3</v>
+      </c>
+      <c r="L95">
+        <v>175.3</v>
+      </c>
+      <c r="M95">
+        <v>43.6979844</v>
+      </c>
+      <c r="N95">
+        <v>131.6020156</v>
+      </c>
+      <c r="O95">
+        <v>39.48060468000001</v>
+      </c>
+      <c r="P95">
+        <v>92.12141092</v>
+      </c>
+      <c r="Q95">
+        <v>239.42141092</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.321963927410624</v>
+      </c>
+      <c r="T95">
+        <v>12.10804145649822</v>
+      </c>
+      <c r="U95">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V95">
+        <v>0.3</v>
+      </c>
+      <c r="W95">
+        <v>0.04116</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>4.011626678140331</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2029384757165852</v>
+      </c>
+      <c r="C96">
+        <v>45.59859168140576</v>
+      </c>
+      <c r="D96">
+        <v>-151.5474083185941</v>
+      </c>
+      <c r="E96">
+        <v>711.9540000000001</v>
+      </c>
+      <c r="F96">
+        <v>751.1540000000001</v>
+      </c>
+      <c r="G96">
+        <v>948.3</v>
+      </c>
+      <c r="H96">
+        <v>759.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>322.6</v>
+      </c>
+      <c r="K96">
+        <v>147.3</v>
+      </c>
+      <c r="L96">
+        <v>175.3</v>
+      </c>
+      <c r="M96">
+        <v>47.32270200000001</v>
+      </c>
+      <c r="N96">
+        <v>127.977298</v>
+      </c>
+      <c r="O96">
+        <v>38.3931894</v>
+      </c>
+      <c r="P96">
+        <v>89.58410860000001</v>
+      </c>
+      <c r="Q96">
+        <v>236.8841086</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.691407928609755</v>
+      </c>
+      <c r="T96">
+        <v>14.06727146564033</v>
+      </c>
+      <c r="U96">
+        <v>0.063</v>
+      </c>
+      <c r="V96">
+        <v>0.3</v>
+      </c>
+      <c r="W96">
+        <v>0.0441</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>3.704353145346603</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2023264765144267</v>
+      </c>
+      <c r="C97">
+        <v>37.58204857975397</v>
+      </c>
+      <c r="D97">
+        <v>-151.5729514202459</v>
+      </c>
+      <c r="E97">
+        <v>719.9450000000001</v>
+      </c>
+      <c r="F97">
+        <v>759.1450000000001</v>
+      </c>
+      <c r="G97">
+        <v>948.3</v>
+      </c>
+      <c r="H97">
+        <v>759.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>322.6</v>
+      </c>
+      <c r="K97">
+        <v>147.3</v>
+      </c>
+      <c r="L97">
+        <v>175.3</v>
+      </c>
+      <c r="M97">
+        <v>47.82613500000001</v>
+      </c>
+      <c r="N97">
+        <v>127.473865</v>
+      </c>
+      <c r="O97">
+        <v>38.24215950000001</v>
+      </c>
+      <c r="P97">
+        <v>89.2317055</v>
+      </c>
+      <c r="Q97">
+        <v>236.5317055</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.208629530288539</v>
+      </c>
+      <c r="T97">
+        <v>16.81019347843928</v>
+      </c>
+      <c r="U97">
+        <v>0.063</v>
+      </c>
+      <c r="V97">
+        <v>0.3</v>
+      </c>
+      <c r="W97">
+        <v>0.0441</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>3.665359954342954</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2017144773122683</v>
+      </c>
+      <c r="C98">
+        <v>29.56549686614335</v>
+      </c>
+      <c r="D98">
+        <v>-151.5985031338566</v>
+      </c>
+      <c r="E98">
+        <v>727.9359999999999</v>
+      </c>
+      <c r="F98">
+        <v>767.136</v>
+      </c>
+      <c r="G98">
+        <v>948.3</v>
+      </c>
+      <c r="H98">
+        <v>759.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>322.6</v>
+      </c>
+      <c r="K98">
+        <v>147.3</v>
+      </c>
+      <c r="L98">
+        <v>175.3</v>
+      </c>
+      <c r="M98">
+        <v>48.32956799999999</v>
+      </c>
+      <c r="N98">
+        <v>126.970432</v>
+      </c>
+      <c r="O98">
+        <v>38.09112960000001</v>
+      </c>
+      <c r="P98">
+        <v>88.8793024</v>
+      </c>
+      <c r="Q98">
+        <v>236.1793024</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.984461932806703</v>
+      </c>
+      <c r="T98">
+        <v>20.92457649763766</v>
+      </c>
+      <c r="U98">
+        <v>0.063</v>
+      </c>
+      <c r="V98">
+        <v>0.3</v>
+      </c>
+      <c r="W98">
+        <v>0.0441</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>3.627179121485216</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2011024781101099</v>
+      </c>
+      <c r="C99">
+        <v>21.54893653621764</v>
+      </c>
+      <c r="D99">
+        <v>-151.6240634637823</v>
+      </c>
+      <c r="E99">
+        <v>735.9269999999999</v>
+      </c>
+      <c r="F99">
+        <v>775.127</v>
+      </c>
+      <c r="G99">
+        <v>948.3</v>
+      </c>
+      <c r="H99">
+        <v>759.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>322.6</v>
+      </c>
+      <c r="K99">
+        <v>147.3</v>
+      </c>
+      <c r="L99">
+        <v>175.3</v>
+      </c>
+      <c r="M99">
+        <v>48.833001</v>
+      </c>
+      <c r="N99">
+        <v>126.466999</v>
+      </c>
+      <c r="O99">
+        <v>37.94009970000001</v>
+      </c>
+      <c r="P99">
+        <v>88.5268993</v>
+      </c>
+      <c r="Q99">
+        <v>235.8268993</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>5.277515937003658</v>
+      </c>
+      <c r="T99">
+        <v>27.78188152963503</v>
+      </c>
+      <c r="U99">
+        <v>0.063</v>
+      </c>
+      <c r="V99">
+        <v>0.3</v>
+      </c>
+      <c r="W99">
+        <v>0.0441</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>3.589785522294647</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2004904789079514</v>
+      </c>
+      <c r="C100">
+        <v>13.53236758561786</v>
+      </c>
+      <c r="D100">
+        <v>-151.6496324143821</v>
+      </c>
+      <c r="E100">
+        <v>743.918</v>
+      </c>
+      <c r="F100">
+        <v>783.1180000000001</v>
+      </c>
+      <c r="G100">
+        <v>948.3</v>
+      </c>
+      <c r="H100">
+        <v>759.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>322.6</v>
+      </c>
+      <c r="K100">
+        <v>147.3</v>
+      </c>
+      <c r="L100">
+        <v>175.3</v>
+      </c>
+      <c r="M100">
+        <v>49.336434</v>
+      </c>
+      <c r="N100">
+        <v>125.963566</v>
+      </c>
+      <c r="O100">
+        <v>37.78906980000001</v>
+      </c>
+      <c r="P100">
+        <v>88.17449620000001</v>
+      </c>
+      <c r="Q100">
+        <v>235.4744962</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>7.863623945397564</v>
+      </c>
+      <c r="T100">
+        <v>41.49649159362975</v>
+      </c>
+      <c r="U100">
+        <v>0.063</v>
+      </c>
+      <c r="V100">
+        <v>0.3</v>
+      </c>
+      <c r="W100">
+        <v>0.0441</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>3.553155057781436</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.199878479705793</v>
+      </c>
+      <c r="C101">
+        <v>5.515790009982084</v>
+      </c>
+      <c r="D101">
+        <v>-151.6752099900178</v>
+      </c>
+      <c r="E101">
+        <v>751.909</v>
+      </c>
+      <c r="F101">
+        <v>791.109</v>
+      </c>
+      <c r="G101">
+        <v>948.3</v>
+      </c>
+      <c r="H101">
+        <v>759.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>322.6</v>
+      </c>
+      <c r="K101">
+        <v>147.3</v>
+      </c>
+      <c r="L101">
+        <v>175.3</v>
+      </c>
+      <c r="M101">
+        <v>49.83986700000001</v>
+      </c>
+      <c r="N101">
+        <v>125.460133</v>
+      </c>
+      <c r="O101">
+        <v>37.63803990000001</v>
+      </c>
+      <c r="P101">
+        <v>87.8220931</v>
+      </c>
+      <c r="Q101">
+        <v>235.1220931</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>15.62194797057928</v>
+      </c>
+      <c r="T101">
+        <v>82.64032178561392</v>
+      </c>
+      <c r="U101">
+        <v>0.063</v>
+      </c>
+      <c r="V101">
+        <v>0.3</v>
+      </c>
+      <c r="W101">
+        <v>0.0441</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>3.517264602652331</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/gabon/gabon_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/gabon/gabon_oil_gas_production_and_exploration.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2030658902398778</v>
+        <v>0.2024881925691582</v>
       </c>
       <c r="C2">
-        <v>984.1186051492233</v>
+        <v>974.5549496011655</v>
       </c>
       <c r="D2">
-        <v>247.3186051492234</v>
+        <v>247.5949496011655</v>
       </c>
       <c r="E2">
-        <v>-42.9</v>
+        <v>-33.06</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.84</v>
       </c>
       <c r="G2">
         <v>736.8</v>
@@ -1451,28 +1451,28 @@
         <v>145.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4949519999999999</v>
       </c>
       <c r="N2">
-        <v>145.5</v>
+        <v>145.005048</v>
       </c>
       <c r="O2">
-        <v>43.65</v>
+        <v>43.5015144</v>
       </c>
       <c r="P2">
-        <v>101.85</v>
+        <v>101.5035336</v>
       </c>
       <c r="Q2">
-        <v>261.15</v>
+        <v>260.8035336</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2030658902398778</v>
+        <v>0.204177871281978</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9686193451353977</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>293.9678999175678</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2024881925691582</v>
+        <v>0.2019104948984386</v>
       </c>
       <c r="C3">
-        <v>974.5549496011655</v>
+        <v>964.9919122975806</v>
       </c>
       <c r="D3">
-        <v>247.5949496011655</v>
+        <v>247.8719122975805</v>
       </c>
       <c r="E3">
-        <v>-33.06</v>
+        <v>-23.22</v>
       </c>
       <c r="F3">
-        <v>9.84</v>
+        <v>19.68</v>
       </c>
       <c r="G3">
         <v>736.8</v>
@@ -1533,28 +1533,28 @@
         <v>145.5</v>
       </c>
       <c r="M3">
-        <v>0.4949519999999999</v>
+        <v>0.9899039999999999</v>
       </c>
       <c r="N3">
-        <v>145.005048</v>
+        <v>144.510096</v>
       </c>
       <c r="O3">
-        <v>43.5015144</v>
+        <v>43.3530288</v>
       </c>
       <c r="P3">
-        <v>101.5035336</v>
+        <v>101.1570672</v>
       </c>
       <c r="Q3">
-        <v>260.8035336</v>
+        <v>260.4570672</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.204177871281978</v>
+        <v>0.2053125458147332</v>
       </c>
       <c r="T3">
-        <v>0.9686193451353977</v>
+        <v>0.9755588733280858</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>293.9678999175678</v>
+        <v>146.9839499587839</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2019104948984386</v>
+        <v>0.2013327972277189</v>
       </c>
       <c r="C4">
-        <v>964.9919122975806</v>
+        <v>955.429495315519</v>
       </c>
       <c r="D4">
-        <v>247.8719122975805</v>
+        <v>248.149495315519</v>
       </c>
       <c r="E4">
-        <v>-23.22</v>
+        <v>-13.38</v>
       </c>
       <c r="F4">
-        <v>19.68</v>
+        <v>29.52</v>
       </c>
       <c r="G4">
         <v>736.8</v>
@@ -1615,28 +1615,28 @@
         <v>145.5</v>
       </c>
       <c r="M4">
-        <v>0.9899039999999999</v>
+        <v>1.484856</v>
       </c>
       <c r="N4">
-        <v>144.510096</v>
+        <v>144.015144</v>
       </c>
       <c r="O4">
-        <v>43.3530288</v>
+        <v>43.2045432</v>
       </c>
       <c r="P4">
-        <v>101.1570672</v>
+        <v>100.8106008</v>
       </c>
       <c r="Q4">
-        <v>260.4570672</v>
+        <v>260.1106008</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2053125458147332</v>
+        <v>0.2064706156986793</v>
       </c>
       <c r="T4">
-        <v>0.9755588733280858</v>
+        <v>0.9826414845762931</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>146.9839499587839</v>
+        <v>97.98929997252259</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2013327972277189</v>
+        <v>0.2007550995569993</v>
       </c>
       <c r="C5">
-        <v>955.429495315519</v>
+        <v>945.867700741346</v>
       </c>
       <c r="D5">
-        <v>248.149495315519</v>
+        <v>248.427700741346</v>
       </c>
       <c r="E5">
-        <v>-13.38</v>
+        <v>-3.539999999999999</v>
       </c>
       <c r="F5">
-        <v>29.52</v>
+        <v>39.36</v>
       </c>
       <c r="G5">
         <v>736.8</v>
@@ -1697,28 +1697,28 @@
         <v>145.5</v>
       </c>
       <c r="M5">
-        <v>1.484856</v>
+        <v>1.979808</v>
       </c>
       <c r="N5">
-        <v>144.015144</v>
+        <v>143.520192</v>
       </c>
       <c r="O5">
-        <v>43.2045432</v>
+        <v>43.0560576</v>
       </c>
       <c r="P5">
-        <v>100.8106008</v>
+        <v>100.4641344</v>
       </c>
       <c r="Q5">
-        <v>260.1106008</v>
+        <v>259.7641344</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2064706156986793</v>
+        <v>0.2076528120385409</v>
       </c>
       <c r="T5">
-        <v>0.9826414845762931</v>
+        <v>0.9898716502255048</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>97.98929997252259</v>
+        <v>73.49197497939196</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2007550995569993</v>
+        <v>0.2001774018862796</v>
       </c>
       <c r="C6">
-        <v>945.867700741346</v>
+        <v>936.3065306707933</v>
       </c>
       <c r="D6">
-        <v>248.427700741346</v>
+        <v>248.7065306707934</v>
       </c>
       <c r="E6">
-        <v>-3.539999999999999</v>
+        <v>6.300000000000004</v>
       </c>
       <c r="F6">
-        <v>39.36</v>
+        <v>49.2</v>
       </c>
       <c r="G6">
         <v>736.8</v>
@@ -1779,28 +1779,28 @@
         <v>145.5</v>
       </c>
       <c r="M6">
-        <v>1.979808</v>
+        <v>2.47476</v>
       </c>
       <c r="N6">
-        <v>143.520192</v>
+        <v>143.02524</v>
       </c>
       <c r="O6">
-        <v>43.0560576</v>
+        <v>42.90757199999999</v>
       </c>
       <c r="P6">
-        <v>100.4641344</v>
+        <v>100.117668</v>
       </c>
       <c r="Q6">
-        <v>259.7641344</v>
+        <v>259.417668</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2076528120385409</v>
+        <v>0.2088598967223996</v>
       </c>
       <c r="T6">
-        <v>0.9898716502255048</v>
+        <v>0.9972540298883841</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.49197497939196</v>
+        <v>58.79357998351355</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2001774018862796</v>
+        <v>0.19959970421556</v>
       </c>
       <c r="C7">
-        <v>936.3065306707933</v>
+        <v>926.7459872090124</v>
       </c>
       <c r="D7">
-        <v>248.7065306707934</v>
+        <v>248.9859872090123</v>
       </c>
       <c r="E7">
-        <v>6.300000000000004</v>
+        <v>16.14000000000001</v>
       </c>
       <c r="F7">
-        <v>49.2</v>
+        <v>59.04000000000001</v>
       </c>
       <c r="G7">
         <v>736.8</v>
@@ -1861,28 +1861,28 @@
         <v>145.5</v>
       </c>
       <c r="M7">
-        <v>2.47476</v>
+        <v>2.969712</v>
       </c>
       <c r="N7">
-        <v>143.02524</v>
+        <v>142.530288</v>
       </c>
       <c r="O7">
-        <v>42.90757199999999</v>
+        <v>42.7590864</v>
       </c>
       <c r="P7">
-        <v>100.117668</v>
+        <v>99.77120160000001</v>
       </c>
       <c r="Q7">
-        <v>259.417668</v>
+        <v>259.0712016</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2088598967223996</v>
+        <v>0.2100926640591064</v>
       </c>
       <c r="T7">
-        <v>0.9972540298883841</v>
+        <v>1.004793481458984</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>58.79357998351355</v>
+        <v>48.99464998626129</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.19959970421556</v>
+        <v>0.1990220065448404</v>
       </c>
       <c r="C8">
-        <v>926.7459872090124</v>
+        <v>917.1860724706264</v>
       </c>
       <c r="D8">
-        <v>248.9859872090123</v>
+        <v>249.2660724706264</v>
       </c>
       <c r="E8">
-        <v>16.14</v>
+        <v>25.98</v>
       </c>
       <c r="F8">
-        <v>59.04</v>
+        <v>68.88</v>
       </c>
       <c r="G8">
         <v>736.8</v>
@@ -1943,28 +1943,28 @@
         <v>145.5</v>
       </c>
       <c r="M8">
-        <v>2.969712</v>
+        <v>3.464664</v>
       </c>
       <c r="N8">
-        <v>142.530288</v>
+        <v>142.035336</v>
       </c>
       <c r="O8">
-        <v>42.7590864</v>
+        <v>42.6106008</v>
       </c>
       <c r="P8">
-        <v>99.77120160000001</v>
+        <v>99.4247352</v>
       </c>
       <c r="Q8">
-        <v>259.0712016</v>
+        <v>258.7247352</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2100926640591064</v>
+        <v>0.2113519425213338</v>
       </c>
       <c r="T8">
-        <v>1.004793481458984</v>
+        <v>1.012495071773038</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.9946499862613</v>
+        <v>41.99541427393826</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1990220065448404</v>
+        <v>0.1984443088741208</v>
       </c>
       <c r="C9">
-        <v>917.1860724706264</v>
+        <v>907.6267885797849</v>
       </c>
       <c r="D9">
-        <v>249.2660724706264</v>
+        <v>249.5467885797851</v>
       </c>
       <c r="E9">
-        <v>25.98000000000001</v>
+        <v>35.82</v>
       </c>
       <c r="F9">
-        <v>68.88000000000001</v>
+        <v>78.72</v>
       </c>
       <c r="G9">
         <v>736.8</v>
@@ -2025,28 +2025,28 @@
         <v>145.5</v>
       </c>
       <c r="M9">
-        <v>3.464664</v>
+        <v>3.959616</v>
       </c>
       <c r="N9">
-        <v>142.035336</v>
+        <v>141.540384</v>
       </c>
       <c r="O9">
-        <v>42.6106008</v>
+        <v>42.46211519999999</v>
       </c>
       <c r="P9">
-        <v>99.4247352</v>
+        <v>99.07826879999999</v>
       </c>
       <c r="Q9">
-        <v>258.7247352</v>
+        <v>258.3782688</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2113519425213338</v>
+        <v>0.2126385966023052</v>
       </c>
       <c r="T9">
-        <v>1.012495071773038</v>
+        <v>1.020364087963485</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.99541427393824</v>
+        <v>36.74598748969597</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1984443088741208</v>
+        <v>0.1978666112034012</v>
       </c>
       <c r="C10">
-        <v>907.6267885797849</v>
+        <v>898.0681376702169</v>
       </c>
       <c r="D10">
-        <v>249.5467885797851</v>
+        <v>249.8281376702169</v>
       </c>
       <c r="E10">
-        <v>35.82</v>
+        <v>45.66</v>
       </c>
       <c r="F10">
-        <v>78.72</v>
+        <v>88.56</v>
       </c>
       <c r="G10">
         <v>736.8</v>
@@ -2107,28 +2107,28 @@
         <v>145.5</v>
       </c>
       <c r="M10">
-        <v>3.959616</v>
+        <v>4.454568</v>
       </c>
       <c r="N10">
-        <v>141.540384</v>
+        <v>141.045432</v>
       </c>
       <c r="O10">
-        <v>42.46211519999999</v>
+        <v>42.3136296</v>
       </c>
       <c r="P10">
-        <v>99.07826879999999</v>
+        <v>98.73180240000001</v>
       </c>
       <c r="Q10">
-        <v>258.3782688</v>
+        <v>258.0318024</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2126385966023052</v>
+        <v>0.2139535287949463</v>
       </c>
       <c r="T10">
-        <v>1.020364087963485</v>
+        <v>1.02840604956471</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.74598748969597</v>
+        <v>32.66309999084086</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1978666112034012</v>
+        <v>0.1972889135326815</v>
       </c>
       <c r="C11">
-        <v>898.0681376702169</v>
+        <v>888.5101218852842</v>
       </c>
       <c r="D11">
-        <v>249.8281376702169</v>
+        <v>250.1101218852842</v>
       </c>
       <c r="E11">
-        <v>45.66</v>
+        <v>55.49999999999999</v>
       </c>
       <c r="F11">
-        <v>88.56</v>
+        <v>98.39999999999999</v>
       </c>
       <c r="G11">
         <v>736.8</v>
@@ -2189,28 +2189,28 @@
         <v>145.5</v>
       </c>
       <c r="M11">
-        <v>4.454568</v>
+        <v>4.94952</v>
       </c>
       <c r="N11">
-        <v>141.045432</v>
+        <v>140.55048</v>
       </c>
       <c r="O11">
-        <v>42.3136296</v>
+        <v>42.165144</v>
       </c>
       <c r="P11">
-        <v>98.73180240000001</v>
+        <v>98.385336</v>
       </c>
       <c r="Q11">
-        <v>258.0318024</v>
+        <v>257.685336</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2139535287949463</v>
+        <v>0.2152976817029794</v>
       </c>
       <c r="T11">
-        <v>1.02840604956471</v>
+        <v>1.036626721423741</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.66309999084086</v>
+        <v>29.39678999175678</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1972889135326815</v>
+        <v>0.1967112158619619</v>
       </c>
       <c r="C12">
-        <v>888.5101218852842</v>
+        <v>878.9527433780369</v>
       </c>
       <c r="D12">
-        <v>250.1101218852842</v>
+        <v>250.3927433780369</v>
       </c>
       <c r="E12">
-        <v>55.50000000000001</v>
+        <v>65.34</v>
       </c>
       <c r="F12">
-        <v>98.40000000000001</v>
+        <v>108.24</v>
       </c>
       <c r="G12">
         <v>736.8</v>
@@ -2271,28 +2271,28 @@
         <v>145.5</v>
       </c>
       <c r="M12">
-        <v>4.94952</v>
+        <v>5.444471999999999</v>
       </c>
       <c r="N12">
-        <v>140.55048</v>
+        <v>140.055528</v>
       </c>
       <c r="O12">
-        <v>42.165144</v>
+        <v>42.0166584</v>
       </c>
       <c r="P12">
-        <v>98.385336</v>
+        <v>98.0388696</v>
       </c>
       <c r="Q12">
-        <v>257.685336</v>
+        <v>257.3388696</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2152976817029794</v>
+        <v>0.2166720402943392</v>
       </c>
       <c r="T12">
-        <v>1.036626721423741</v>
+        <v>1.04503212748185</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.39678999175678</v>
+        <v>26.72435453796071</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1967112158619619</v>
+        <v>0.1961335181912423</v>
       </c>
       <c r="C13">
-        <v>878.9527433780369</v>
+        <v>869.3960043112678</v>
       </c>
       <c r="D13">
-        <v>250.3927433780369</v>
+        <v>250.6760043112679</v>
       </c>
       <c r="E13">
-        <v>65.34</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="F13">
-        <v>108.24</v>
+        <v>118.08</v>
       </c>
       <c r="G13">
         <v>736.8</v>
@@ -2353,28 +2353,28 @@
         <v>145.5</v>
       </c>
       <c r="M13">
-        <v>5.444471999999999</v>
+        <v>5.939424</v>
       </c>
       <c r="N13">
-        <v>140.055528</v>
+        <v>139.560576</v>
       </c>
       <c r="O13">
-        <v>42.0166584</v>
+        <v>41.8681728</v>
       </c>
       <c r="P13">
-        <v>98.0388696</v>
+        <v>97.6924032</v>
       </c>
       <c r="Q13">
-        <v>257.3388696</v>
+        <v>256.9924032</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2166720402943392</v>
+        <v>0.2180776343082299</v>
       </c>
       <c r="T13">
-        <v>1.04503212748185</v>
+        <v>1.053628565495826</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.72435453796071</v>
+        <v>24.49732499313065</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1961335181912423</v>
+        <v>0.1955558205205226</v>
       </c>
       <c r="C14">
-        <v>869.3960043112678</v>
+        <v>859.8399068575678</v>
       </c>
       <c r="D14">
-        <v>250.6760043112679</v>
+        <v>250.9599068575678</v>
       </c>
       <c r="E14">
-        <v>75.18000000000001</v>
+        <v>85.02000000000001</v>
       </c>
       <c r="F14">
-        <v>118.08</v>
+        <v>127.92</v>
       </c>
       <c r="G14">
         <v>736.8</v>
@@ -2435,28 +2435,28 @@
         <v>145.5</v>
       </c>
       <c r="M14">
-        <v>5.939424</v>
+        <v>6.434375999999999</v>
       </c>
       <c r="N14">
-        <v>139.560576</v>
+        <v>139.065624</v>
       </c>
       <c r="O14">
-        <v>41.8681728</v>
+        <v>41.7196872</v>
       </c>
       <c r="P14">
-        <v>97.6924032</v>
+        <v>97.3459368</v>
       </c>
       <c r="Q14">
-        <v>256.9924032</v>
+        <v>256.6459368</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2180776343082299</v>
+        <v>0.2195155408281869</v>
       </c>
       <c r="T14">
-        <v>1.053628565495826</v>
+        <v>1.062422622774491</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.49732499313065</v>
+        <v>22.61291537827445</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1955558205205226</v>
+        <v>0.194978122849803</v>
       </c>
       <c r="C15">
-        <v>859.8399068575678</v>
+        <v>850.2844531993806</v>
       </c>
       <c r="D15">
-        <v>250.9599068575678</v>
+        <v>251.2444531993806</v>
       </c>
       <c r="E15">
-        <v>85.02000000000001</v>
+        <v>94.86000000000001</v>
       </c>
       <c r="F15">
-        <v>127.92</v>
+        <v>137.76</v>
       </c>
       <c r="G15">
         <v>736.8</v>
@@ -2517,28 +2517,28 @@
         <v>145.5</v>
       </c>
       <c r="M15">
-        <v>6.434375999999999</v>
+        <v>6.929328000000001</v>
       </c>
       <c r="N15">
-        <v>139.065624</v>
+        <v>138.570672</v>
       </c>
       <c r="O15">
-        <v>41.7196872</v>
+        <v>41.5712016</v>
       </c>
       <c r="P15">
-        <v>97.3459368</v>
+        <v>96.99947040000001</v>
       </c>
       <c r="Q15">
-        <v>256.6459368</v>
+        <v>256.2994704</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2195155408281869</v>
+        <v>0.2209868870346546</v>
       </c>
       <c r="T15">
-        <v>1.062422622774491</v>
+        <v>1.071421193013125</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.61291537827445</v>
+        <v>20.99770713696912</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.194978122849803</v>
+        <v>0.1944004251790834</v>
       </c>
       <c r="C16">
-        <v>850.2844531993806</v>
+        <v>840.7296455290597</v>
       </c>
       <c r="D16">
-        <v>251.2444531993806</v>
+        <v>251.5296455290597</v>
       </c>
       <c r="E16">
-        <v>94.86000000000001</v>
+        <v>104.7</v>
       </c>
       <c r="F16">
-        <v>137.76</v>
+        <v>147.6</v>
       </c>
       <c r="G16">
         <v>736.8</v>
@@ -2599,28 +2599,28 @@
         <v>145.5</v>
       </c>
       <c r="M16">
-        <v>6.929328000000001</v>
+        <v>7.42428</v>
       </c>
       <c r="N16">
-        <v>138.570672</v>
+        <v>138.07572</v>
       </c>
       <c r="O16">
-        <v>41.5712016</v>
+        <v>41.42271599999999</v>
       </c>
       <c r="P16">
-        <v>96.99947040000001</v>
+        <v>96.653004</v>
       </c>
       <c r="Q16">
-        <v>256.2994704</v>
+        <v>255.953004</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2209868870346546</v>
+        <v>0.2224928531518628</v>
       </c>
       <c r="T16">
-        <v>1.071421193013125</v>
+        <v>1.080631494316198</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.99770713696912</v>
+        <v>19.59785999450451</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1944004251790834</v>
+        <v>0.1938227275083637</v>
       </c>
       <c r="C17">
-        <v>840.7296455290597</v>
+        <v>831.1754860489241</v>
       </c>
       <c r="D17">
-        <v>251.5296455290597</v>
+        <v>251.8154860489242</v>
       </c>
       <c r="E17">
-        <v>104.7</v>
+        <v>114.54</v>
       </c>
       <c r="F17">
-        <v>147.6</v>
+        <v>157.44</v>
       </c>
       <c r="G17">
         <v>736.8</v>
@@ -2681,28 +2681,28 @@
         <v>145.5</v>
       </c>
       <c r="M17">
-        <v>7.42428</v>
+        <v>7.919231999999999</v>
       </c>
       <c r="N17">
-        <v>138.07572</v>
+        <v>137.580768</v>
       </c>
       <c r="O17">
-        <v>41.42271599999999</v>
+        <v>41.2742304</v>
       </c>
       <c r="P17">
-        <v>96.653004</v>
+        <v>96.30653760000001</v>
       </c>
       <c r="Q17">
-        <v>255.953004</v>
+        <v>255.6065376</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2224928531518628</v>
+        <v>0.2240346756051949</v>
       </c>
       <c r="T17">
-        <v>1.080631494316198</v>
+        <v>1.090061088507439</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.59785999450452</v>
+        <v>18.37299374484799</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1938227275083637</v>
+        <v>0.1932450298376441</v>
       </c>
       <c r="C18">
-        <v>831.1754860489241</v>
+        <v>821.6219769713153</v>
       </c>
       <c r="D18">
-        <v>251.8154860489242</v>
+        <v>252.1019769713153</v>
       </c>
       <c r="E18">
-        <v>114.54</v>
+        <v>124.38</v>
       </c>
       <c r="F18">
-        <v>157.44</v>
+        <v>167.28</v>
       </c>
       <c r="G18">
         <v>736.8</v>
@@ -2763,28 +2763,28 @@
         <v>145.5</v>
       </c>
       <c r="M18">
-        <v>7.919231999999999</v>
+        <v>8.414183999999999</v>
       </c>
       <c r="N18">
-        <v>137.580768</v>
+        <v>137.085816</v>
       </c>
       <c r="O18">
-        <v>41.2742304</v>
+        <v>41.1257448</v>
       </c>
       <c r="P18">
-        <v>96.30653760000001</v>
+        <v>95.96007119999999</v>
       </c>
       <c r="Q18">
-        <v>255.6065376</v>
+        <v>255.2600712</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2240346756051949</v>
+        <v>0.2256136504068001</v>
       </c>
       <c r="T18">
-        <v>1.090061088507439</v>
+        <v>1.099717901835818</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.37299374484799</v>
+        <v>17.29222940691575</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1932450298376441</v>
+        <v>0.1926673321669244</v>
       </c>
       <c r="C19">
-        <v>821.6219769713153</v>
+        <v>812.0691205186539</v>
       </c>
       <c r="D19">
-        <v>252.1019769713153</v>
+        <v>252.389120518654</v>
       </c>
       <c r="E19">
-        <v>124.38</v>
+        <v>134.22</v>
       </c>
       <c r="F19">
-        <v>167.28</v>
+        <v>177.12</v>
       </c>
       <c r="G19">
         <v>736.8</v>
@@ -2845,28 +2845,28 @@
         <v>145.5</v>
       </c>
       <c r="M19">
-        <v>8.414183999999999</v>
+        <v>8.909136000000002</v>
       </c>
       <c r="N19">
-        <v>137.085816</v>
+        <v>136.590864</v>
       </c>
       <c r="O19">
-        <v>41.1257448</v>
+        <v>40.9772592</v>
       </c>
       <c r="P19">
-        <v>95.96007119999999</v>
+        <v>95.61360480000002</v>
       </c>
       <c r="Q19">
-        <v>255.2600712</v>
+        <v>254.9136048</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2256136504068001</v>
+        <v>0.2272311367889322</v>
       </c>
       <c r="T19">
-        <v>1.099717901835818</v>
+        <v>1.109610247196596</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.29222940691575</v>
+        <v>16.33154999542043</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1926673321669244</v>
+        <v>0.1920896344962048</v>
       </c>
       <c r="C20">
-        <v>812.0691205186539</v>
+        <v>802.5169189234975</v>
       </c>
       <c r="D20">
-        <v>252.3891205186539</v>
+        <v>252.6769189234976</v>
       </c>
       <c r="E20">
-        <v>134.22</v>
+        <v>144.06</v>
       </c>
       <c r="F20">
-        <v>177.12</v>
+        <v>186.96</v>
       </c>
       <c r="G20">
         <v>736.8</v>
@@ -2927,28 +2927,28 @@
         <v>145.5</v>
       </c>
       <c r="M20">
-        <v>8.909136</v>
+        <v>9.404088</v>
       </c>
       <c r="N20">
-        <v>136.590864</v>
+        <v>136.095912</v>
       </c>
       <c r="O20">
-        <v>40.9772592</v>
+        <v>40.8287736</v>
       </c>
       <c r="P20">
-        <v>95.61360480000002</v>
+        <v>95.26713839999999</v>
       </c>
       <c r="Q20">
-        <v>254.9136048</v>
+        <v>254.5671384</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2272311367889322</v>
+        <v>0.2288885611064257</v>
       </c>
       <c r="T20">
-        <v>1.109610247196596</v>
+        <v>1.119746847998382</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.33154999542043</v>
+        <v>15.47199473250357</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1920896344962048</v>
+        <v>0.1915119368254852</v>
       </c>
       <c r="C21">
-        <v>802.5169189234975</v>
+        <v>792.9653744285988</v>
       </c>
       <c r="D21">
-        <v>252.6769189234976</v>
+        <v>252.9653744285988</v>
       </c>
       <c r="E21">
-        <v>144.06</v>
+        <v>153.9</v>
       </c>
       <c r="F21">
-        <v>186.96</v>
+        <v>196.8</v>
       </c>
       <c r="G21">
         <v>736.8</v>
@@ -3009,28 +3009,28 @@
         <v>145.5</v>
       </c>
       <c r="M21">
-        <v>9.404088</v>
+        <v>9.899039999999999</v>
       </c>
       <c r="N21">
-        <v>136.095912</v>
+        <v>135.60096</v>
       </c>
       <c r="O21">
-        <v>40.8287736</v>
+        <v>40.680288</v>
       </c>
       <c r="P21">
-        <v>95.26713839999999</v>
+        <v>94.920672</v>
       </c>
       <c r="Q21">
-        <v>254.5671384</v>
+        <v>254.220672</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2288885611064257</v>
+        <v>0.2305874210318565</v>
       </c>
       <c r="T21">
-        <v>1.119746847998382</v>
+        <v>1.130136863820212</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.47199473250357</v>
+        <v>14.69839499587839</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1915119368254852</v>
+        <v>0.1909342391547655</v>
       </c>
       <c r="C22">
-        <v>792.9653744285988</v>
+        <v>783.4144892869626</v>
       </c>
       <c r="D22">
-        <v>252.9653744285988</v>
+        <v>253.2544892869627</v>
       </c>
       <c r="E22">
-        <v>153.9</v>
+        <v>163.74</v>
       </c>
       <c r="F22">
-        <v>196.8</v>
+        <v>206.64</v>
       </c>
       <c r="G22">
         <v>736.8</v>
@@ -3091,28 +3091,28 @@
         <v>145.5</v>
       </c>
       <c r="M22">
-        <v>9.899039999999999</v>
+        <v>10.393992</v>
       </c>
       <c r="N22">
-        <v>135.60096</v>
+        <v>135.106008</v>
       </c>
       <c r="O22">
-        <v>40.680288</v>
+        <v>40.5318024</v>
       </c>
       <c r="P22">
-        <v>94.920672</v>
+        <v>94.5742056</v>
       </c>
       <c r="Q22">
-        <v>254.220672</v>
+        <v>253.8742056</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2305874210318565</v>
+        <v>0.2323292900693235</v>
       </c>
       <c r="T22">
-        <v>1.130136863820212</v>
+        <v>1.140789918017278</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.69839499587839</v>
+        <v>13.99847142464608</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1909342391547655</v>
+        <v>0.1903565414840459</v>
       </c>
       <c r="C23">
-        <v>783.4144892869626</v>
+        <v>773.8642657619063</v>
       </c>
       <c r="D23">
-        <v>253.2544892869627</v>
+        <v>253.5442657619063</v>
       </c>
       <c r="E23">
-        <v>163.74</v>
+        <v>173.58</v>
       </c>
       <c r="F23">
-        <v>206.64</v>
+        <v>216.48</v>
       </c>
       <c r="G23">
         <v>736.8</v>
@@ -3173,28 +3173,28 @@
         <v>145.5</v>
       </c>
       <c r="M23">
-        <v>10.393992</v>
+        <v>10.888944</v>
       </c>
       <c r="N23">
-        <v>135.106008</v>
+        <v>134.611056</v>
       </c>
       <c r="O23">
-        <v>40.5318024</v>
+        <v>40.3833168</v>
       </c>
       <c r="P23">
-        <v>94.5742056</v>
+        <v>94.2277392</v>
       </c>
       <c r="Q23">
-        <v>253.8742056</v>
+        <v>253.5277392</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2323292900693235</v>
+        <v>0.2341158224154435</v>
       </c>
       <c r="T23">
-        <v>1.140789918017278</v>
+        <v>1.151716127450167</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.99847142464609</v>
+        <v>13.36217726898035</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1903565414840459</v>
+        <v>0.1900203438133263</v>
       </c>
       <c r="C24">
-        <v>773.8642657619063</v>
+        <v>764.1932099033347</v>
       </c>
       <c r="D24">
-        <v>253.5442657619063</v>
+        <v>253.7132099033348</v>
       </c>
       <c r="E24">
-        <v>173.58</v>
+        <v>183.42</v>
       </c>
       <c r="F24">
-        <v>216.48</v>
+        <v>226.32</v>
       </c>
       <c r="G24">
         <v>736.8</v>
@@ -3255,45 +3255,45 @@
         <v>145.5</v>
       </c>
       <c r="M24">
-        <v>10.888944</v>
+        <v>11.723376</v>
       </c>
       <c r="N24">
-        <v>134.611056</v>
+        <v>133.776624</v>
       </c>
       <c r="O24">
-        <v>40.3833168</v>
+        <v>40.1329872</v>
       </c>
       <c r="P24">
-        <v>94.2277392</v>
+        <v>93.6436368</v>
       </c>
       <c r="Q24">
-        <v>253.5277392</v>
+        <v>252.9436368</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2341158224154435</v>
+        <v>0.235948758199125</v>
       </c>
       <c r="T24">
-        <v>1.151716127450167</v>
+        <v>1.162926134530663</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.36217726898035</v>
+        <v>12.41110069317917</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1900203438133263</v>
+        <v>0.1894531461426066</v>
       </c>
       <c r="C25">
-        <v>764.1932099033347</v>
+        <v>754.6387457603507</v>
       </c>
       <c r="D25">
-        <v>253.7132099033348</v>
+        <v>253.9987457603508</v>
       </c>
       <c r="E25">
-        <v>183.42</v>
+        <v>193.26</v>
       </c>
       <c r="F25">
-        <v>226.32</v>
+        <v>236.16</v>
       </c>
       <c r="G25">
         <v>736.8</v>
@@ -3337,28 +3337,28 @@
         <v>145.5</v>
       </c>
       <c r="M25">
-        <v>11.723376</v>
+        <v>12.233088</v>
       </c>
       <c r="N25">
-        <v>133.776624</v>
+        <v>133.266912</v>
       </c>
       <c r="O25">
-        <v>40.1329872</v>
+        <v>39.9800736</v>
       </c>
       <c r="P25">
-        <v>93.6436368</v>
+        <v>93.28683839999999</v>
       </c>
       <c r="Q25">
-        <v>252.9436368</v>
+        <v>252.5868384</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.235948758199125</v>
+        <v>0.2378299291350087</v>
       </c>
       <c r="T25">
-        <v>1.162926134530663</v>
+        <v>1.174431141797488</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.41110069317917</v>
+        <v>11.89397149763003</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1894531461426066</v>
+        <v>0.188885948471887</v>
       </c>
       <c r="C26">
-        <v>754.6387457603508</v>
+        <v>745.0849250413808</v>
       </c>
       <c r="D26">
-        <v>253.9987457603508</v>
+        <v>254.2849250413807</v>
       </c>
       <c r="E26">
-        <v>193.26</v>
+        <v>203.1</v>
       </c>
       <c r="F26">
-        <v>236.16</v>
+        <v>246</v>
       </c>
       <c r="G26">
         <v>736.8</v>
@@ -3419,28 +3419,28 @@
         <v>145.5</v>
       </c>
       <c r="M26">
-        <v>12.233088</v>
+        <v>12.7428</v>
       </c>
       <c r="N26">
-        <v>133.266912</v>
+        <v>132.7572</v>
       </c>
       <c r="O26">
-        <v>39.9800736</v>
+        <v>39.82716</v>
       </c>
       <c r="P26">
-        <v>93.28683839999999</v>
+        <v>92.93004000000002</v>
       </c>
       <c r="Q26">
-        <v>252.5868384</v>
+        <v>252.23004</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2378299291350087</v>
+        <v>0.2397612646291827</v>
       </c>
       <c r="T26">
-        <v>1.174431141797488</v>
+        <v>1.186242949258095</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.89397149763003</v>
+        <v>11.41821263772484</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.188885948471887</v>
+        <v>0.1883187508011674</v>
       </c>
       <c r="C27">
-        <v>745.0849250413808</v>
+        <v>735.5317499237068</v>
       </c>
       <c r="D27">
-        <v>254.2849250413807</v>
+        <v>254.5717499237069</v>
       </c>
       <c r="E27">
-        <v>203.1</v>
+        <v>212.94</v>
       </c>
       <c r="F27">
-        <v>246</v>
+        <v>255.84</v>
       </c>
       <c r="G27">
         <v>736.8</v>
@@ -3501,28 +3501,28 @@
         <v>145.5</v>
       </c>
       <c r="M27">
-        <v>12.7428</v>
+        <v>13.252512</v>
       </c>
       <c r="N27">
-        <v>132.7572</v>
+        <v>132.247488</v>
       </c>
       <c r="O27">
-        <v>39.82716</v>
+        <v>39.6742464</v>
       </c>
       <c r="P27">
-        <v>92.93004000000002</v>
+        <v>92.5732416</v>
       </c>
       <c r="Q27">
-        <v>252.23004</v>
+        <v>251.8732416</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2397612646291827</v>
+        <v>0.2417447983799559</v>
       </c>
       <c r="T27">
-        <v>1.186242949258095</v>
+        <v>1.198373994758178</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.41821263772484</v>
+        <v>10.97905061319696</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1883187508011674</v>
+        <v>0.1877515531304478</v>
       </c>
       <c r="C28">
-        <v>735.5317499237068</v>
+        <v>725.9792225944461</v>
       </c>
       <c r="D28">
-        <v>254.5717499237069</v>
+        <v>254.8592225944462</v>
       </c>
       <c r="E28">
-        <v>212.94</v>
+        <v>222.78</v>
       </c>
       <c r="F28">
-        <v>255.84</v>
+        <v>265.68</v>
       </c>
       <c r="G28">
         <v>736.8</v>
@@ -3583,28 +3583,28 @@
         <v>145.5</v>
       </c>
       <c r="M28">
-        <v>13.252512</v>
+        <v>13.762224</v>
       </c>
       <c r="N28">
-        <v>132.247488</v>
+        <v>131.737776</v>
       </c>
       <c r="O28">
-        <v>39.6742464</v>
+        <v>39.5213328</v>
       </c>
       <c r="P28">
-        <v>92.5732416</v>
+        <v>92.2164432</v>
       </c>
       <c r="Q28">
-        <v>251.8732416</v>
+        <v>251.5164432</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2417447983799559</v>
+        <v>0.2437826755211613</v>
       </c>
       <c r="T28">
-        <v>1.198373994758178</v>
+        <v>1.210837397669222</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.97905061319696</v>
+        <v>10.57241910900447</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1877515531304478</v>
+        <v>0.1871843554597281</v>
       </c>
       <c r="C29">
-        <v>725.9792225944461</v>
+        <v>716.4273452506059</v>
       </c>
       <c r="D29">
-        <v>254.8592225944462</v>
+        <v>255.1473452506059</v>
       </c>
       <c r="E29">
-        <v>222.78</v>
+        <v>232.62</v>
       </c>
       <c r="F29">
-        <v>265.68</v>
+        <v>275.52</v>
       </c>
       <c r="G29">
         <v>736.8</v>
@@ -3665,28 +3665,28 @@
         <v>145.5</v>
       </c>
       <c r="M29">
-        <v>13.762224</v>
+        <v>14.271936</v>
       </c>
       <c r="N29">
-        <v>131.737776</v>
+        <v>131.228064</v>
       </c>
       <c r="O29">
-        <v>39.5213328</v>
+        <v>39.3684192</v>
       </c>
       <c r="P29">
-        <v>92.2164432</v>
+        <v>91.85964479999998</v>
       </c>
       <c r="Q29">
-        <v>251.5164432</v>
+        <v>251.1596448</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2437826755211613</v>
+        <v>0.2458771603607335</v>
       </c>
       <c r="T29">
-        <v>1.210837397669222</v>
+        <v>1.223647006216683</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.57241910900447</v>
+        <v>10.19483271225431</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1871843554597281</v>
+        <v>0.1866171577890085</v>
       </c>
       <c r="C30">
-        <v>716.4273452506059</v>
+        <v>706.8761200991393</v>
       </c>
       <c r="D30">
-        <v>255.1473452506059</v>
+        <v>255.4361200991394</v>
       </c>
       <c r="E30">
-        <v>232.62</v>
+        <v>242.46</v>
       </c>
       <c r="F30">
-        <v>275.52</v>
+        <v>285.36</v>
       </c>
       <c r="G30">
         <v>736.8</v>
@@ -3747,28 +3747,28 @@
         <v>145.5</v>
       </c>
       <c r="M30">
-        <v>14.271936</v>
+        <v>14.781648</v>
       </c>
       <c r="N30">
-        <v>131.228064</v>
+        <v>130.718352</v>
       </c>
       <c r="O30">
-        <v>39.3684192</v>
+        <v>39.2155056</v>
       </c>
       <c r="P30">
-        <v>91.85964479999998</v>
+        <v>91.50284640000001</v>
       </c>
       <c r="Q30">
-        <v>251.1596448</v>
+        <v>250.8028464</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2458771603607335</v>
+        <v>0.2480306447732514</v>
       </c>
       <c r="T30">
-        <v>1.223647006216683</v>
+        <v>1.236817448807736</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.19483271225431</v>
+        <v>9.843286756659339</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1866171577890085</v>
+        <v>0.1864069601182888</v>
       </c>
       <c r="C31">
-        <v>706.8761200991394</v>
+        <v>697.1433031896909</v>
       </c>
       <c r="D31">
-        <v>255.4361200991394</v>
+        <v>255.5433031896909</v>
       </c>
       <c r="E31">
-        <v>242.46</v>
+        <v>252.3</v>
       </c>
       <c r="F31">
-        <v>285.36</v>
+        <v>295.2</v>
       </c>
       <c r="G31">
         <v>736.8</v>
@@ -3829,45 +3829,45 @@
         <v>145.5</v>
       </c>
       <c r="M31">
-        <v>14.781648</v>
+        <v>15.7932</v>
       </c>
       <c r="N31">
-        <v>130.718352</v>
+        <v>129.7068</v>
       </c>
       <c r="O31">
-        <v>39.2155056</v>
+        <v>38.91204</v>
       </c>
       <c r="P31">
-        <v>91.50284640000001</v>
+        <v>90.79476</v>
       </c>
       <c r="Q31">
-        <v>250.8028464</v>
+        <v>250.09476</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2480306447732514</v>
+        <v>0.2502456573118412</v>
       </c>
       <c r="T31">
-        <v>1.236817448807736</v>
+        <v>1.250364189758532</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>9.84328675665934</v>
+        <v>9.212825773117544</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1864069601182888</v>
+        <v>0.1858516624475692</v>
       </c>
       <c r="C32">
-        <v>697.1433031896909</v>
+        <v>687.5868913614217</v>
       </c>
       <c r="D32">
-        <v>255.5433031896909</v>
+        <v>255.8268913614218</v>
       </c>
       <c r="E32">
-        <v>252.3</v>
+        <v>262.14</v>
       </c>
       <c r="F32">
-        <v>295.2</v>
+        <v>305.04</v>
       </c>
       <c r="G32">
         <v>736.8</v>
@@ -3911,28 +3911,28 @@
         <v>145.5</v>
       </c>
       <c r="M32">
-        <v>15.7932</v>
+        <v>16.31964</v>
       </c>
       <c r="N32">
-        <v>129.7068</v>
+        <v>129.18036</v>
       </c>
       <c r="O32">
-        <v>38.91204</v>
+        <v>38.754108</v>
       </c>
       <c r="P32">
-        <v>90.79476</v>
+        <v>90.42625200000001</v>
       </c>
       <c r="Q32">
-        <v>250.09476</v>
+        <v>249.726252</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2502456573118412</v>
+        <v>0.2525248731124191</v>
       </c>
       <c r="T32">
-        <v>1.250364189758532</v>
+        <v>1.264303589867323</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.212825773117544</v>
+        <v>8.915637844952464</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1858516624475692</v>
+        <v>0.1852963647768495</v>
       </c>
       <c r="C33">
-        <v>687.5868913614217</v>
+        <v>678.0311096541346</v>
       </c>
       <c r="D33">
-        <v>255.8268913614218</v>
+        <v>256.1111096541347</v>
       </c>
       <c r="E33">
-        <v>262.14</v>
+        <v>271.98</v>
       </c>
       <c r="F33">
-        <v>305.04</v>
+        <v>314.88</v>
       </c>
       <c r="G33">
         <v>736.8</v>
@@ -3993,28 +3993,28 @@
         <v>145.5</v>
       </c>
       <c r="M33">
-        <v>16.31964</v>
+        <v>16.84608</v>
       </c>
       <c r="N33">
-        <v>129.18036</v>
+        <v>128.65392</v>
       </c>
       <c r="O33">
-        <v>38.754108</v>
+        <v>38.596176</v>
       </c>
       <c r="P33">
-        <v>90.42625200000001</v>
+        <v>90.057744</v>
       </c>
       <c r="Q33">
-        <v>249.726252</v>
+        <v>249.357744</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2525248731124191</v>
+        <v>0.2548711246718376</v>
       </c>
       <c r="T33">
-        <v>1.264303589867323</v>
+        <v>1.278652972332255</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.915637844952464</v>
+        <v>8.637024162297697</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1852963647768495</v>
+        <v>0.1847410671061299</v>
       </c>
       <c r="C34">
-        <v>678.0311096541346</v>
+        <v>668.4759601703188</v>
       </c>
       <c r="D34">
-        <v>256.1111096541347</v>
+        <v>256.3959601703188</v>
       </c>
       <c r="E34">
-        <v>271.98</v>
+        <v>281.8200000000001</v>
       </c>
       <c r="F34">
-        <v>314.88</v>
+        <v>324.72</v>
       </c>
       <c r="G34">
         <v>736.8</v>
@@ -4075,28 +4075,28 @@
         <v>145.5</v>
       </c>
       <c r="M34">
-        <v>16.84608</v>
+        <v>17.37252</v>
       </c>
       <c r="N34">
-        <v>128.65392</v>
+        <v>128.12748</v>
       </c>
       <c r="O34">
-        <v>38.596176</v>
+        <v>38.438244</v>
       </c>
       <c r="P34">
-        <v>90.057744</v>
+        <v>89.68923599999999</v>
       </c>
       <c r="Q34">
-        <v>249.357744</v>
+        <v>248.989236</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2548711246718376</v>
+        <v>0.2572874135912387</v>
       </c>
       <c r="T34">
-        <v>1.278652972332255</v>
+        <v>1.293430694572259</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.637024162297697</v>
+        <v>8.375296157379584</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1847410671061299</v>
+        <v>0.1841857694354103</v>
       </c>
       <c r="C35">
-        <v>668.4759601703188</v>
+        <v>658.9214450218276</v>
       </c>
       <c r="D35">
-        <v>256.3959601703188</v>
+        <v>256.6814450218276</v>
       </c>
       <c r="E35">
-        <v>281.8200000000001</v>
+        <v>291.66</v>
       </c>
       <c r="F35">
-        <v>324.72</v>
+        <v>334.56</v>
       </c>
       <c r="G35">
         <v>736.8</v>
@@ -4157,28 +4157,28 @@
         <v>145.5</v>
       </c>
       <c r="M35">
-        <v>17.37252</v>
+        <v>17.89896</v>
       </c>
       <c r="N35">
-        <v>128.12748</v>
+        <v>127.60104</v>
       </c>
       <c r="O35">
-        <v>38.438244</v>
+        <v>38.280312</v>
       </c>
       <c r="P35">
-        <v>89.68923599999999</v>
+        <v>89.320728</v>
       </c>
       <c r="Q35">
-        <v>248.989236</v>
+        <v>248.620728</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2572874135912387</v>
+        <v>0.2597769233869853</v>
       </c>
       <c r="T35">
-        <v>1.293430694572259</v>
+        <v>1.308656226577112</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.375296157379584</v>
+        <v>8.128963917456657</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1841857694354103</v>
+        <v>0.1836304717646906</v>
       </c>
       <c r="C36">
-        <v>658.9214450218276</v>
+        <v>649.3675663299307</v>
       </c>
       <c r="D36">
-        <v>256.6814450218276</v>
+        <v>256.9675663299308</v>
       </c>
       <c r="E36">
-        <v>291.66</v>
+        <v>301.5000000000001</v>
       </c>
       <c r="F36">
-        <v>334.56</v>
+        <v>344.4</v>
       </c>
       <c r="G36">
         <v>736.8</v>
@@ -4239,28 +4239,28 @@
         <v>145.5</v>
       </c>
       <c r="M36">
-        <v>17.89896</v>
+        <v>18.4254</v>
       </c>
       <c r="N36">
-        <v>127.60104</v>
+        <v>127.0746</v>
       </c>
       <c r="O36">
-        <v>38.280312</v>
+        <v>38.12238</v>
       </c>
       <c r="P36">
-        <v>89.320728</v>
+        <v>88.95222000000001</v>
       </c>
       <c r="Q36">
-        <v>248.620728</v>
+        <v>248.25222</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2597769233869853</v>
+        <v>0.2623430334841395</v>
       </c>
       <c r="T36">
-        <v>1.308656226577112</v>
+        <v>1.324350236489807</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.128963917456657</v>
+        <v>7.896707805529324</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1836304717646906</v>
+        <v>0.183075174093971</v>
       </c>
       <c r="C37">
-        <v>649.3675663299307</v>
+        <v>639.8143262253666</v>
       </c>
       <c r="D37">
-        <v>256.9675663299308</v>
+        <v>257.2543262253666</v>
       </c>
       <c r="E37">
-        <v>301.5000000000001</v>
+        <v>311.3400000000001</v>
       </c>
       <c r="F37">
-        <v>344.4</v>
+        <v>354.2400000000001</v>
       </c>
       <c r="G37">
         <v>736.8</v>
@@ -4321,28 +4321,28 @@
         <v>145.5</v>
       </c>
       <c r="M37">
-        <v>18.4254</v>
+        <v>18.95184</v>
       </c>
       <c r="N37">
-        <v>127.0746</v>
+        <v>126.54816</v>
       </c>
       <c r="O37">
-        <v>38.12238</v>
+        <v>37.964448</v>
       </c>
       <c r="P37">
-        <v>88.95222000000001</v>
+        <v>88.58371199999999</v>
       </c>
       <c r="Q37">
-        <v>248.25222</v>
+        <v>247.883712</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2623430334841395</v>
+        <v>0.2649893345218298</v>
       </c>
       <c r="T37">
-        <v>1.324350236489807</v>
+        <v>1.340534684212273</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.896707805529324</v>
+        <v>7.677354810931285</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1830751740939711</v>
+        <v>0.1827270764232514</v>
       </c>
       <c r="C38">
-        <v>639.8143262253666</v>
+        <v>630.1544130618283</v>
       </c>
       <c r="D38">
-        <v>257.2543262253666</v>
+        <v>257.4344130618283</v>
       </c>
       <c r="E38">
-        <v>311.34</v>
+        <v>321.18</v>
       </c>
       <c r="F38">
-        <v>354.24</v>
+        <v>364.08</v>
       </c>
       <c r="G38">
         <v>736.8</v>
@@ -4403,45 +4403,45 @@
         <v>145.5</v>
       </c>
       <c r="M38">
-        <v>18.95184</v>
+        <v>19.769544</v>
       </c>
       <c r="N38">
-        <v>126.54816</v>
+        <v>125.730456</v>
       </c>
       <c r="O38">
-        <v>37.964448</v>
+        <v>37.7191368</v>
       </c>
       <c r="P38">
-        <v>88.58371199999999</v>
+        <v>88.0113192</v>
       </c>
       <c r="Q38">
-        <v>247.883712</v>
+        <v>247.3113192</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2649893345218298</v>
+        <v>0.267719645116272</v>
       </c>
       <c r="T38">
-        <v>1.340534684212273</v>
+        <v>1.357232923925928</v>
       </c>
       <c r="U38">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>7.677354810931287</v>
+        <v>7.359805567594275</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1827270764232514</v>
+        <v>0.1821773787525318</v>
       </c>
       <c r="C39">
-        <v>630.1544130618283</v>
+        <v>620.5993108140551</v>
       </c>
       <c r="D39">
-        <v>257.4344130618283</v>
+        <v>257.7193108140552</v>
       </c>
       <c r="E39">
-        <v>321.18</v>
+        <v>331.02</v>
       </c>
       <c r="F39">
-        <v>364.08</v>
+        <v>373.92</v>
       </c>
       <c r="G39">
         <v>736.8</v>
@@ -4485,28 +4485,28 @@
         <v>145.5</v>
       </c>
       <c r="M39">
-        <v>19.769544</v>
+        <v>20.303856</v>
       </c>
       <c r="N39">
-        <v>125.730456</v>
+        <v>125.196144</v>
       </c>
       <c r="O39">
-        <v>37.7191368</v>
+        <v>37.5588432</v>
       </c>
       <c r="P39">
-        <v>88.0113192</v>
+        <v>87.63730080000001</v>
       </c>
       <c r="Q39">
-        <v>247.3113192</v>
+        <v>246.9373008</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.267719645116272</v>
+        <v>0.270538030246019</v>
       </c>
       <c r="T39">
-        <v>1.357232923925928</v>
+        <v>1.374469816533573</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.359805567594275</v>
+        <v>7.166126473710216</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1821773787525318</v>
+        <v>0.1816276810818122</v>
       </c>
       <c r="C40">
-        <v>620.5993108140551</v>
+        <v>611.0448398467192</v>
       </c>
       <c r="D40">
-        <v>257.7193108140552</v>
+        <v>258.0048398467193</v>
       </c>
       <c r="E40">
-        <v>331.02</v>
+        <v>340.86</v>
       </c>
       <c r="F40">
-        <v>373.92</v>
+        <v>383.76</v>
       </c>
       <c r="G40">
         <v>736.8</v>
@@ -4567,28 +4567,28 @@
         <v>145.5</v>
       </c>
       <c r="M40">
-        <v>20.303856</v>
+        <v>20.838168</v>
       </c>
       <c r="N40">
-        <v>125.196144</v>
+        <v>124.661832</v>
       </c>
       <c r="O40">
-        <v>37.5588432</v>
+        <v>37.3985496</v>
       </c>
       <c r="P40">
-        <v>87.63730080000001</v>
+        <v>87.26328240000001</v>
       </c>
       <c r="Q40">
-        <v>246.9373008</v>
+        <v>246.5632824</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.270538030246019</v>
+        <v>0.2734488214455937</v>
       </c>
       <c r="T40">
-        <v>1.374469816533573</v>
+        <v>1.39227185316114</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.166126473710216</v>
+        <v>6.982379641050979</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1816276810818122</v>
+        <v>0.1810779834110925</v>
       </c>
       <c r="C41">
-        <v>611.0448398467192</v>
+        <v>601.4910022603478</v>
       </c>
       <c r="D41">
-        <v>258.0048398467193</v>
+        <v>258.2910022603479</v>
       </c>
       <c r="E41">
-        <v>340.86</v>
+        <v>350.7</v>
       </c>
       <c r="F41">
-        <v>383.76</v>
+        <v>393.6</v>
       </c>
       <c r="G41">
         <v>736.8</v>
@@ -4649,28 +4649,28 @@
         <v>145.5</v>
       </c>
       <c r="M41">
-        <v>20.838168</v>
+        <v>21.37248</v>
       </c>
       <c r="N41">
-        <v>124.661832</v>
+        <v>124.12752</v>
       </c>
       <c r="O41">
-        <v>37.3985496</v>
+        <v>37.238256</v>
       </c>
       <c r="P41">
-        <v>87.26328240000001</v>
+        <v>86.889264</v>
       </c>
       <c r="Q41">
-        <v>246.5632824</v>
+        <v>246.189264</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2734488214455937</v>
+        <v>0.2764566390184875</v>
       </c>
       <c r="T41">
-        <v>1.39227185316114</v>
+        <v>1.410667291009627</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.982379641050979</v>
+        <v>6.807820150024704</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1810779834110925</v>
+        <v>0.1805282857403728</v>
       </c>
       <c r="C42">
-        <v>601.4910022603478</v>
+        <v>591.9378001647976</v>
       </c>
       <c r="D42">
-        <v>258.2910022603479</v>
+        <v>258.5778001647977</v>
       </c>
       <c r="E42">
-        <v>350.7</v>
+        <v>360.5400000000001</v>
       </c>
       <c r="F42">
-        <v>393.6</v>
+        <v>403.4400000000001</v>
       </c>
       <c r="G42">
         <v>736.8</v>
@@ -4731,28 +4731,28 @@
         <v>145.5</v>
       </c>
       <c r="M42">
-        <v>21.37248</v>
+        <v>21.906792</v>
       </c>
       <c r="N42">
-        <v>124.12752</v>
+        <v>123.593208</v>
       </c>
       <c r="O42">
-        <v>37.238256</v>
+        <v>37.0779624</v>
       </c>
       <c r="P42">
-        <v>86.889264</v>
+        <v>86.51524560000001</v>
       </c>
       <c r="Q42">
-        <v>246.189264</v>
+        <v>245.8152456</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2764566390184875</v>
+        <v>0.2795664165091065</v>
       </c>
       <c r="T42">
-        <v>1.410667291009627</v>
+        <v>1.429686303022468</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.807820150024704</v>
+        <v>6.641775756121662</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1805282857403728</v>
+        <v>0.1799785880696532</v>
       </c>
       <c r="C43">
-        <v>591.9378001647976</v>
+        <v>582.3852356793066</v>
       </c>
       <c r="D43">
-        <v>258.5778001647977</v>
+        <v>258.8652356793065</v>
       </c>
       <c r="E43">
-        <v>360.5400000000001</v>
+        <v>370.3800000000001</v>
       </c>
       <c r="F43">
-        <v>403.4400000000001</v>
+        <v>413.28</v>
       </c>
       <c r="G43">
         <v>736.8</v>
@@ -4813,28 +4813,28 @@
         <v>145.5</v>
       </c>
       <c r="M43">
-        <v>21.906792</v>
+        <v>22.441104</v>
       </c>
       <c r="N43">
-        <v>123.593208</v>
+        <v>123.058896</v>
       </c>
       <c r="O43">
-        <v>37.0779624</v>
+        <v>36.9176688</v>
       </c>
       <c r="P43">
-        <v>86.51524560000001</v>
+        <v>86.1412272</v>
       </c>
       <c r="Q43">
-        <v>245.8152456</v>
+        <v>245.4412272</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2795664165091065</v>
+        <v>0.2827834277062987</v>
       </c>
       <c r="T43">
-        <v>1.429686303022468</v>
+        <v>1.449361143035752</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.641775756121662</v>
+        <v>6.483638238118766</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1799785880696532</v>
+        <v>0.1794288903989336</v>
       </c>
       <c r="C44">
-        <v>582.3852356793066</v>
+        <v>572.8333109325459</v>
       </c>
       <c r="D44">
-        <v>258.8652356793065</v>
+        <v>259.1533109325459</v>
       </c>
       <c r="E44">
-        <v>370.38</v>
+        <v>380.22</v>
       </c>
       <c r="F44">
-        <v>413.28</v>
+        <v>423.12</v>
       </c>
       <c r="G44">
         <v>736.8</v>
@@ -4895,28 +4895,28 @@
         <v>145.5</v>
       </c>
       <c r="M44">
-        <v>22.441104</v>
+        <v>22.975416</v>
       </c>
       <c r="N44">
-        <v>123.058896</v>
+        <v>122.524584</v>
       </c>
       <c r="O44">
-        <v>36.9176688</v>
+        <v>36.7573752</v>
       </c>
       <c r="P44">
-        <v>86.1412272</v>
+        <v>85.76720880000001</v>
       </c>
       <c r="Q44">
-        <v>245.4412272</v>
+        <v>245.0672088</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2827834277062986</v>
+        <v>0.2861133164893572</v>
       </c>
       <c r="T44">
-        <v>1.449361143035752</v>
+        <v>1.469726328312661</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.483638238118766</v>
+        <v>6.332855953511354</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1794288903989336</v>
+        <v>0.178879192728214</v>
       </c>
       <c r="C45">
-        <v>572.8333109325459</v>
+        <v>563.2820280626734</v>
       </c>
       <c r="D45">
-        <v>259.1533109325459</v>
+        <v>259.4420280626735</v>
       </c>
       <c r="E45">
-        <v>380.22</v>
+        <v>390.06</v>
       </c>
       <c r="F45">
-        <v>423.12</v>
+        <v>432.96</v>
       </c>
       <c r="G45">
         <v>736.8</v>
@@ -4977,28 +4977,28 @@
         <v>145.5</v>
       </c>
       <c r="M45">
-        <v>22.975416</v>
+        <v>23.509728</v>
       </c>
       <c r="N45">
-        <v>122.524584</v>
+        <v>121.990272</v>
       </c>
       <c r="O45">
-        <v>36.7573752</v>
+        <v>36.5970816</v>
       </c>
       <c r="P45">
-        <v>85.76720880000001</v>
+        <v>85.39319040000001</v>
       </c>
       <c r="Q45">
-        <v>245.0672088</v>
+        <v>244.6931904</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2861133164893572</v>
+        <v>0.2895621298718106</v>
       </c>
       <c r="T45">
-        <v>1.469726328312661</v>
+        <v>1.490818841635173</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.332855953511354</v>
+        <v>6.188927409113369</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.178879192728214</v>
+        <v>0.1786444950574944</v>
       </c>
       <c r="C46">
-        <v>563.2820280626734</v>
+        <v>553.565494134599</v>
       </c>
       <c r="D46">
-        <v>259.4420280626735</v>
+        <v>259.565494134599</v>
       </c>
       <c r="E46">
-        <v>390.06</v>
+        <v>399.9</v>
       </c>
       <c r="F46">
-        <v>432.96</v>
+        <v>442.8</v>
       </c>
       <c r="G46">
         <v>736.8</v>
@@ -5059,45 +5059,45 @@
         <v>145.5</v>
       </c>
       <c r="M46">
-        <v>23.509728</v>
+        <v>24.48684</v>
       </c>
       <c r="N46">
-        <v>121.990272</v>
+        <v>121.01316</v>
       </c>
       <c r="O46">
-        <v>36.5970816</v>
+        <v>36.303948</v>
       </c>
       <c r="P46">
-        <v>85.39319040000001</v>
+        <v>84.70921200000001</v>
       </c>
       <c r="Q46">
-        <v>244.6931904</v>
+        <v>244.009212</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2895621298718106</v>
+        <v>0.2931363546499897</v>
       </c>
       <c r="T46">
-        <v>1.490818841635173</v>
+        <v>1.512678355442141</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>6.188927409113369</v>
+        <v>5.94196719544049</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1786444950574944</v>
+        <v>0.1781017973867747</v>
       </c>
       <c r="C47">
-        <v>553.565494134599</v>
+        <v>544.0114385402931</v>
       </c>
       <c r="D47">
-        <v>259.565494134599</v>
+        <v>259.8514385402931</v>
       </c>
       <c r="E47">
-        <v>399.9</v>
+        <v>409.7400000000001</v>
       </c>
       <c r="F47">
-        <v>442.8</v>
+        <v>452.64</v>
       </c>
       <c r="G47">
         <v>736.8</v>
@@ -5141,28 +5141,28 @@
         <v>145.5</v>
       </c>
       <c r="M47">
-        <v>24.48684</v>
+        <v>25.030992</v>
       </c>
       <c r="N47">
-        <v>121.01316</v>
+        <v>120.469008</v>
       </c>
       <c r="O47">
-        <v>36.303948</v>
+        <v>36.1407024</v>
       </c>
       <c r="P47">
-        <v>84.70921200000001</v>
+        <v>84.32830559999999</v>
       </c>
       <c r="Q47">
-        <v>244.009212</v>
+        <v>243.6283056</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2931363546499897</v>
+        <v>0.2968429581236569</v>
       </c>
       <c r="T47">
-        <v>1.512678355442141</v>
+        <v>1.535347480871588</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.94196719544049</v>
+        <v>5.812793995539609</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1781017973867747</v>
+        <v>0.1775590997160551</v>
       </c>
       <c r="C48">
-        <v>544.0114385402931</v>
+        <v>534.4580136490507</v>
       </c>
       <c r="D48">
-        <v>259.8514385402931</v>
+        <v>260.1380136490508</v>
       </c>
       <c r="E48">
-        <v>409.7400000000001</v>
+        <v>419.58</v>
       </c>
       <c r="F48">
-        <v>452.64</v>
+        <v>462.48</v>
       </c>
       <c r="G48">
         <v>736.8</v>
@@ -5223,28 +5223,28 @@
         <v>145.5</v>
       </c>
       <c r="M48">
-        <v>25.030992</v>
+        <v>25.575144</v>
       </c>
       <c r="N48">
-        <v>120.469008</v>
+        <v>119.924856</v>
       </c>
       <c r="O48">
-        <v>36.1407024</v>
+        <v>35.9774568</v>
       </c>
       <c r="P48">
-        <v>84.32830559999999</v>
+        <v>83.94739920000001</v>
       </c>
       <c r="Q48">
-        <v>243.6283056</v>
+        <v>243.2473992</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2968429581236569</v>
+        <v>0.300689433426519</v>
       </c>
       <c r="T48">
-        <v>1.535347480871588</v>
+        <v>1.558872044996487</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.812793995539609</v>
+        <v>5.689117527549405</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1775590997160551</v>
+        <v>0.1770164020453354</v>
       </c>
       <c r="C49">
-        <v>534.4580136490507</v>
+        <v>524.9052215498733</v>
       </c>
       <c r="D49">
-        <v>260.1380136490508</v>
+        <v>260.4252215498734</v>
       </c>
       <c r="E49">
-        <v>419.58</v>
+        <v>429.4200000000001</v>
       </c>
       <c r="F49">
-        <v>462.48</v>
+        <v>472.3200000000001</v>
       </c>
       <c r="G49">
         <v>736.8</v>
@@ -5305,28 +5305,28 @@
         <v>145.5</v>
       </c>
       <c r="M49">
-        <v>25.575144</v>
+        <v>26.119296</v>
       </c>
       <c r="N49">
-        <v>119.924856</v>
+        <v>119.380704</v>
       </c>
       <c r="O49">
-        <v>35.9774568</v>
+        <v>35.8142112</v>
       </c>
       <c r="P49">
-        <v>83.94739920000001</v>
+        <v>83.56649279999999</v>
       </c>
       <c r="Q49">
-        <v>243.2473992</v>
+        <v>242.8664928</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.300689433426519</v>
+        <v>0.3046838500871835</v>
       </c>
       <c r="T49">
-        <v>1.558872044996487</v>
+        <v>1.583301400049266</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.689117527549405</v>
+        <v>5.570594245725458</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1770164020453354</v>
+        <v>0.1764737043746158</v>
       </c>
       <c r="C50">
-        <v>524.9052215498734</v>
+        <v>515.3530643409982</v>
       </c>
       <c r="D50">
-        <v>260.4252215498734</v>
+        <v>260.7130643409982</v>
       </c>
       <c r="E50">
-        <v>429.42</v>
+        <v>439.26</v>
       </c>
       <c r="F50">
-        <v>472.32</v>
+        <v>482.16</v>
       </c>
       <c r="G50">
         <v>736.8</v>
@@ -5387,28 +5387,28 @@
         <v>145.5</v>
       </c>
       <c r="M50">
-        <v>26.119296</v>
+        <v>26.663448</v>
       </c>
       <c r="N50">
-        <v>119.380704</v>
+        <v>118.836552</v>
       </c>
       <c r="O50">
-        <v>35.8142112</v>
+        <v>35.6509656</v>
       </c>
       <c r="P50">
-        <v>83.56649279999999</v>
+        <v>83.18558640000001</v>
       </c>
       <c r="Q50">
-        <v>242.8664928</v>
+        <v>242.4855864</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3046838500871835</v>
+        <v>0.3088349105384623</v>
       </c>
       <c r="T50">
-        <v>1.583301400049266</v>
+        <v>1.608688769025683</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.570594245725458</v>
+        <v>5.456908648873919</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1764737043746158</v>
+        <v>0.1759310067038962</v>
       </c>
       <c r="C51">
-        <v>515.3530643409982</v>
+        <v>505.8015441299492</v>
       </c>
       <c r="D51">
-        <v>260.7130643409982</v>
+        <v>261.0015441299493</v>
       </c>
       <c r="E51">
-        <v>439.26</v>
+        <v>449.1</v>
       </c>
       <c r="F51">
-        <v>482.16</v>
+        <v>492</v>
       </c>
       <c r="G51">
         <v>736.8</v>
@@ -5469,28 +5469,28 @@
         <v>145.5</v>
       </c>
       <c r="M51">
-        <v>26.663448</v>
+        <v>27.2076</v>
       </c>
       <c r="N51">
-        <v>118.836552</v>
+        <v>118.2924</v>
       </c>
       <c r="O51">
-        <v>35.6509656</v>
+        <v>35.48772</v>
       </c>
       <c r="P51">
-        <v>83.18558640000001</v>
+        <v>82.80468</v>
       </c>
       <c r="Q51">
-        <v>242.4855864</v>
+        <v>242.10468</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3088349105384623</v>
+        <v>0.3131520134077923</v>
       </c>
       <c r="T51">
-        <v>1.608688769025683</v>
+        <v>1.635091632761158</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.456908648873919</v>
+        <v>5.347770475896441</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1759310067038962</v>
+        <v>0.1753883090331766</v>
       </c>
       <c r="C52">
-        <v>505.8015441299492</v>
+        <v>496.2506630335888</v>
       </c>
       <c r="D52">
-        <v>261.0015441299493</v>
+        <v>261.2906630335889</v>
       </c>
       <c r="E52">
-        <v>449.1</v>
+        <v>458.9400000000001</v>
       </c>
       <c r="F52">
-        <v>492</v>
+        <v>501.84</v>
       </c>
       <c r="G52">
         <v>736.8</v>
@@ -5551,28 +5551,28 @@
         <v>145.5</v>
       </c>
       <c r="M52">
-        <v>27.2076</v>
+        <v>27.751752</v>
       </c>
       <c r="N52">
-        <v>118.2924</v>
+        <v>117.748248</v>
       </c>
       <c r="O52">
-        <v>35.48772</v>
+        <v>35.32447439999999</v>
       </c>
       <c r="P52">
-        <v>82.80468</v>
+        <v>82.4237736</v>
       </c>
       <c r="Q52">
-        <v>242.10468</v>
+        <v>241.7237736</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3131520134077923</v>
+        <v>0.3176453245575032</v>
       </c>
       <c r="T52">
-        <v>1.635091632761158</v>
+        <v>1.662572164404203</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.347770475896441</v>
+        <v>5.24291223127102</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1753883090331766</v>
+        <v>0.1748456113624569</v>
       </c>
       <c r="C53">
-        <v>496.2506630335888</v>
+        <v>486.7004231781696</v>
       </c>
       <c r="D53">
-        <v>261.2906630335889</v>
+        <v>261.5804231781696</v>
       </c>
       <c r="E53">
-        <v>458.9400000000001</v>
+        <v>468.78</v>
       </c>
       <c r="F53">
-        <v>501.84</v>
+        <v>511.68</v>
       </c>
       <c r="G53">
         <v>736.8</v>
@@ -5633,28 +5633,28 @@
         <v>145.5</v>
       </c>
       <c r="M53">
-        <v>27.751752</v>
+        <v>28.295904</v>
       </c>
       <c r="N53">
-        <v>117.748248</v>
+        <v>117.204096</v>
       </c>
       <c r="O53">
-        <v>35.32447439999999</v>
+        <v>35.1612288</v>
       </c>
       <c r="P53">
-        <v>82.4237736</v>
+        <v>82.04286719999999</v>
       </c>
       <c r="Q53">
-        <v>241.7237736</v>
+        <v>241.3428672</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3176453245575032</v>
+        <v>0.3223258570051186</v>
       </c>
       <c r="T53">
-        <v>1.662572164404203</v>
+        <v>1.691197718199041</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.24291223127102</v>
+        <v>5.142086996054269</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1748456113624569</v>
+        <v>0.1743029136917372</v>
       </c>
       <c r="C54">
-        <v>486.7004231781696</v>
+        <v>477.1508266993858</v>
       </c>
       <c r="D54">
-        <v>261.5804231781696</v>
+        <v>261.8708266993859</v>
       </c>
       <c r="E54">
-        <v>468.78</v>
+        <v>478.62</v>
       </c>
       <c r="F54">
-        <v>511.68</v>
+        <v>521.52</v>
       </c>
       <c r="G54">
         <v>736.8</v>
@@ -5715,28 +5715,28 @@
         <v>145.5</v>
       </c>
       <c r="M54">
-        <v>28.295904</v>
+        <v>28.840056</v>
       </c>
       <c r="N54">
-        <v>117.204096</v>
+        <v>116.659944</v>
       </c>
       <c r="O54">
-        <v>35.1612288</v>
+        <v>34.9979832</v>
       </c>
       <c r="P54">
-        <v>82.04286719999999</v>
+        <v>81.6619608</v>
       </c>
       <c r="Q54">
-        <v>241.3428672</v>
+        <v>240.9619608</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3223258570051186</v>
+        <v>0.3272055610462495</v>
       </c>
       <c r="T54">
-        <v>1.691197718199041</v>
+        <v>1.721041380666</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.142086996054269</v>
+        <v>5.045066486694755</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1743029136917372</v>
+        <v>0.1737602160210176</v>
       </c>
       <c r="C55">
-        <v>477.1508266993858</v>
+        <v>467.6018757424268</v>
       </c>
       <c r="D55">
-        <v>261.8708266993859</v>
+        <v>262.1618757424268</v>
       </c>
       <c r="E55">
-        <v>478.62</v>
+        <v>488.46</v>
       </c>
       <c r="F55">
-        <v>521.52</v>
+        <v>531.36</v>
       </c>
       <c r="G55">
         <v>736.8</v>
@@ -5797,28 +5797,28 @@
         <v>145.5</v>
       </c>
       <c r="M55">
-        <v>28.840056</v>
+        <v>29.384208</v>
       </c>
       <c r="N55">
-        <v>116.659944</v>
+        <v>116.115792</v>
       </c>
       <c r="O55">
-        <v>34.9979832</v>
+        <v>34.8347376</v>
       </c>
       <c r="P55">
-        <v>81.6619608</v>
+        <v>81.2810544</v>
       </c>
       <c r="Q55">
-        <v>240.9619608</v>
+        <v>240.5810544</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3272055610462495</v>
+        <v>0.332297426132647</v>
       </c>
       <c r="T55">
-        <v>1.721041380666</v>
+        <v>1.752182593675</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.045066486694755</v>
+        <v>4.951639329533741</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1737602160210176</v>
+        <v>0.173217518350298</v>
       </c>
       <c r="C56">
-        <v>467.6018757424268</v>
+        <v>458.053572462029</v>
       </c>
       <c r="D56">
-        <v>262.1618757424268</v>
+        <v>262.4535724620291</v>
       </c>
       <c r="E56">
-        <v>488.46</v>
+        <v>498.3000000000001</v>
       </c>
       <c r="F56">
-        <v>531.36</v>
+        <v>541.2</v>
       </c>
       <c r="G56">
         <v>736.8</v>
@@ -5879,28 +5879,28 @@
         <v>145.5</v>
       </c>
       <c r="M56">
-        <v>29.384208</v>
+        <v>29.92836</v>
       </c>
       <c r="N56">
-        <v>116.115792</v>
+        <v>115.57164</v>
       </c>
       <c r="O56">
-        <v>34.8347376</v>
+        <v>34.671492</v>
       </c>
       <c r="P56">
-        <v>81.2810544</v>
+        <v>80.900148</v>
       </c>
       <c r="Q56">
-        <v>240.5810544</v>
+        <v>240.200148</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.332297426132647</v>
+        <v>0.3376155963339956</v>
       </c>
       <c r="T56">
-        <v>1.752182593675</v>
+        <v>1.784707860595512</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.951639329533741</v>
+        <v>4.861609523542218</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.173217518350298</v>
+        <v>0.1726748206795784</v>
       </c>
       <c r="C57">
-        <v>458.053572462029</v>
+        <v>448.5059190225298</v>
       </c>
       <c r="D57">
-        <v>262.4535724620291</v>
+        <v>262.74591902253</v>
       </c>
       <c r="E57">
-        <v>498.3000000000001</v>
+        <v>508.1400000000001</v>
       </c>
       <c r="F57">
-        <v>541.2</v>
+        <v>551.0400000000001</v>
       </c>
       <c r="G57">
         <v>736.8</v>
@@ -5961,28 +5961,28 @@
         <v>145.5</v>
       </c>
       <c r="M57">
-        <v>29.92836</v>
+        <v>30.47251200000001</v>
       </c>
       <c r="N57">
-        <v>115.57164</v>
+        <v>115.027488</v>
       </c>
       <c r="O57">
-        <v>34.671492</v>
+        <v>34.5082464</v>
       </c>
       <c r="P57">
-        <v>80.900148</v>
+        <v>80.51924159999999</v>
       </c>
       <c r="Q57">
-        <v>240.200148</v>
+        <v>239.8192416</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3376155963339956</v>
+        <v>0.3431755015444963</v>
       </c>
       <c r="T57">
-        <v>1.784707860595512</v>
+        <v>1.818711548739684</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.861609523542218</v>
+        <v>4.774795067764678</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1726748206795784</v>
+        <v>0.1721321230088587</v>
       </c>
       <c r="C58">
-        <v>448.5059190225298</v>
+        <v>438.9589175979207</v>
       </c>
       <c r="D58">
-        <v>262.74591902253</v>
+        <v>263.0389175979209</v>
       </c>
       <c r="E58">
-        <v>508.1400000000001</v>
+        <v>517.9800000000001</v>
       </c>
       <c r="F58">
-        <v>551.0400000000001</v>
+        <v>560.8800000000001</v>
       </c>
       <c r="G58">
         <v>736.8</v>
@@ -6043,28 +6043,28 @@
         <v>145.5</v>
       </c>
       <c r="M58">
-        <v>30.47251200000001</v>
+        <v>31.01666400000001</v>
       </c>
       <c r="N58">
-        <v>115.027488</v>
+        <v>114.483336</v>
       </c>
       <c r="O58">
-        <v>34.5082464</v>
+        <v>34.34500079999999</v>
       </c>
       <c r="P58">
-        <v>80.51924159999999</v>
+        <v>80.1383352</v>
       </c>
       <c r="Q58">
-        <v>239.8192416</v>
+        <v>239.4383352</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3431755015444963</v>
+        <v>0.3489940069973459</v>
       </c>
       <c r="T58">
-        <v>1.818711548739684</v>
+        <v>1.854296803774282</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.774795067764678</v>
+        <v>4.691026733242492</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1721321230088587</v>
+        <v>0.1715894253381391</v>
       </c>
       <c r="C59">
-        <v>438.9589175979207</v>
+        <v>429.4125703719012</v>
       </c>
       <c r="D59">
-        <v>263.0389175979209</v>
+        <v>263.3325703719013</v>
       </c>
       <c r="E59">
-        <v>517.9800000000001</v>
+        <v>527.8200000000001</v>
       </c>
       <c r="F59">
-        <v>560.8800000000001</v>
+        <v>570.72</v>
       </c>
       <c r="G59">
         <v>736.8</v>
@@ -6125,28 +6125,28 @@
         <v>145.5</v>
       </c>
       <c r="M59">
-        <v>31.01666400000001</v>
+        <v>31.560816</v>
       </c>
       <c r="N59">
-        <v>114.483336</v>
+        <v>113.939184</v>
       </c>
       <c r="O59">
-        <v>34.34500079999999</v>
+        <v>34.1817552</v>
       </c>
       <c r="P59">
-        <v>80.1383352</v>
+        <v>79.7574288</v>
       </c>
       <c r="Q59">
-        <v>239.4383352</v>
+        <v>239.0574288</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3489940069973459</v>
+        <v>0.3550895841384265</v>
       </c>
       <c r="T59">
-        <v>1.854296803774282</v>
+        <v>1.891576594762908</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.691026733242492</v>
+        <v>4.61014696197969</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1715894253381391</v>
+        <v>0.1710467276674195</v>
       </c>
       <c r="C60">
-        <v>429.4125703719013</v>
+        <v>419.8668795379331</v>
       </c>
       <c r="D60">
-        <v>263.3325703719013</v>
+        <v>263.626879537933</v>
       </c>
       <c r="E60">
-        <v>527.8199999999999</v>
+        <v>537.66</v>
       </c>
       <c r="F60">
-        <v>570.7199999999999</v>
+        <v>580.5599999999999</v>
       </c>
       <c r="G60">
         <v>736.8</v>
@@ -6207,28 +6207,28 @@
         <v>145.5</v>
       </c>
       <c r="M60">
-        <v>31.560816</v>
+        <v>32.104968</v>
       </c>
       <c r="N60">
-        <v>113.939184</v>
+        <v>113.395032</v>
       </c>
       <c r="O60">
-        <v>34.1817552</v>
+        <v>34.0185096</v>
       </c>
       <c r="P60">
-        <v>79.75742880000001</v>
+        <v>79.3765224</v>
       </c>
       <c r="Q60">
-        <v>239.0574288</v>
+        <v>238.6765224</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3550895841384264</v>
+        <v>0.3614825065059011</v>
       </c>
       <c r="T60">
-        <v>1.891576594762908</v>
+        <v>1.930674912141223</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.610146961979691</v>
+        <v>4.53200887787834</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1710467276674195</v>
+        <v>0.1715540299966998</v>
       </c>
       <c r="C61">
-        <v>419.8668795379331</v>
+        <v>409.7517455077186</v>
       </c>
       <c r="D61">
-        <v>263.626879537933</v>
+        <v>263.3517455077186</v>
       </c>
       <c r="E61">
-        <v>537.66</v>
+        <v>547.5</v>
       </c>
       <c r="F61">
-        <v>580.5599999999999</v>
+        <v>590.4</v>
       </c>
       <c r="G61">
         <v>736.8</v>
@@ -6289,45 +6289,45 @@
         <v>145.5</v>
       </c>
       <c r="M61">
-        <v>32.104968</v>
+        <v>34.12512</v>
       </c>
       <c r="N61">
-        <v>113.395032</v>
+        <v>111.37488</v>
       </c>
       <c r="O61">
-        <v>34.0185096</v>
+        <v>33.41246399999999</v>
       </c>
       <c r="P61">
-        <v>79.3765224</v>
+        <v>77.96241599999999</v>
       </c>
       <c r="Q61">
-        <v>238.6765224</v>
+        <v>237.262416</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3614825065059011</v>
+        <v>0.3681950749917496</v>
       </c>
       <c r="T61">
-        <v>1.930674912141223</v>
+        <v>1.971728145388455</v>
       </c>
       <c r="U61">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.53200887787834</v>
+        <v>4.263721270430697</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1715540299966998</v>
+        <v>0.1710288323259802</v>
       </c>
       <c r="C62">
-        <v>409.7517455077186</v>
+        <v>400.1965955251783</v>
       </c>
       <c r="D62">
-        <v>263.3517455077186</v>
+        <v>263.6365955251783</v>
       </c>
       <c r="E62">
-        <v>547.5</v>
+        <v>557.34</v>
       </c>
       <c r="F62">
-        <v>590.4</v>
+        <v>600.24</v>
       </c>
       <c r="G62">
         <v>736.8</v>
@@ -6371,28 +6371,28 @@
         <v>145.5</v>
       </c>
       <c r="M62">
-        <v>34.12512</v>
+        <v>34.69387200000001</v>
       </c>
       <c r="N62">
-        <v>111.37488</v>
+        <v>110.806128</v>
       </c>
       <c r="O62">
-        <v>33.41246399999999</v>
+        <v>33.2418384</v>
       </c>
       <c r="P62">
-        <v>77.96241599999999</v>
+        <v>77.5642896</v>
       </c>
       <c r="Q62">
-        <v>237.262416</v>
+        <v>236.8642896</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3681950749917496</v>
+        <v>0.3752518777589235</v>
       </c>
       <c r="T62">
-        <v>1.971728145388455</v>
+        <v>2.014886672648365</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.263721270430697</v>
+        <v>4.193824200423636</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1710288323259802</v>
+        <v>0.1705036346552606</v>
       </c>
       <c r="C63">
-        <v>400.1965955251783</v>
+        <v>390.6420624163976</v>
       </c>
       <c r="D63">
-        <v>263.6365955251783</v>
+        <v>263.9220624163977</v>
       </c>
       <c r="E63">
-        <v>557.34</v>
+        <v>567.1800000000001</v>
       </c>
       <c r="F63">
-        <v>600.24</v>
+        <v>610.08</v>
       </c>
       <c r="G63">
         <v>736.8</v>
@@ -6453,28 +6453,28 @@
         <v>145.5</v>
       </c>
       <c r="M63">
-        <v>34.69387200000001</v>
+        <v>35.262624</v>
       </c>
       <c r="N63">
-        <v>110.806128</v>
+        <v>110.237376</v>
       </c>
       <c r="O63">
-        <v>33.2418384</v>
+        <v>33.0712128</v>
       </c>
       <c r="P63">
-        <v>77.5642896</v>
+        <v>77.1661632</v>
       </c>
       <c r="Q63">
-        <v>236.8642896</v>
+        <v>236.4661632</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3752518777589235</v>
+        <v>0.3826800911980541</v>
       </c>
       <c r="T63">
-        <v>2.014886672648365</v>
+        <v>2.060316701343007</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.193824200423636</v>
+        <v>4.126181874610352</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1705036346552606</v>
+        <v>0.169978436984541</v>
       </c>
       <c r="C64">
-        <v>390.6420624163976</v>
+        <v>381.08814818741</v>
       </c>
       <c r="D64">
-        <v>263.9220624163977</v>
+        <v>264.20814818741</v>
       </c>
       <c r="E64">
-        <v>567.1800000000001</v>
+        <v>577.02</v>
       </c>
       <c r="F64">
-        <v>610.08</v>
+        <v>619.92</v>
       </c>
       <c r="G64">
         <v>736.8</v>
@@ -6535,28 +6535,28 @@
         <v>145.5</v>
       </c>
       <c r="M64">
-        <v>35.262624</v>
+        <v>35.831376</v>
       </c>
       <c r="N64">
-        <v>110.237376</v>
+        <v>109.668624</v>
       </c>
       <c r="O64">
-        <v>33.0712128</v>
+        <v>32.9005872</v>
       </c>
       <c r="P64">
-        <v>77.1661632</v>
+        <v>76.7680368</v>
       </c>
       <c r="Q64">
-        <v>236.4661632</v>
+        <v>236.0680368</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3826800911980541</v>
+        <v>0.3905098296879485</v>
       </c>
       <c r="T64">
-        <v>2.060316701343007</v>
+        <v>2.108202407264387</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.126181874610352</v>
+        <v>4.060686924219712</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.169978436984541</v>
+        <v>0.1710212393138213</v>
       </c>
       <c r="C65">
-        <v>381.08814818741</v>
+        <v>370.6807182451709</v>
       </c>
       <c r="D65">
-        <v>264.20814818741</v>
+        <v>263.6407182451709</v>
       </c>
       <c r="E65">
-        <v>577.02</v>
+        <v>586.86</v>
       </c>
       <c r="F65">
-        <v>619.92</v>
+        <v>629.76</v>
       </c>
       <c r="G65">
         <v>736.8</v>
@@ -6617,45 +6617,45 @@
         <v>145.5</v>
       </c>
       <c r="M65">
-        <v>35.831376</v>
+        <v>38.604288</v>
       </c>
       <c r="N65">
-        <v>109.668624</v>
+        <v>106.895712</v>
       </c>
       <c r="O65">
-        <v>32.9005872</v>
+        <v>32.0687136</v>
       </c>
       <c r="P65">
-        <v>76.7680368</v>
+        <v>74.82699840000001</v>
       </c>
       <c r="Q65">
-        <v>236.0680368</v>
+        <v>234.1269984</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3905098296879485</v>
+        <v>0.3987745536495036</v>
       </c>
       <c r="T65">
-        <v>2.108202407264387</v>
+        <v>2.158748430181398</v>
       </c>
       <c r="U65">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>4.060686924219712</v>
+        <v>3.769011359567104</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1710212393138213</v>
+        <v>0.1705205416431017</v>
       </c>
       <c r="C66">
-        <v>370.6807182451709</v>
+        <v>361.1128631317303</v>
       </c>
       <c r="D66">
-        <v>263.6407182451709</v>
+        <v>263.9128631317303</v>
       </c>
       <c r="E66">
-        <v>586.86</v>
+        <v>596.7</v>
       </c>
       <c r="F66">
-        <v>629.76</v>
+        <v>639.6</v>
       </c>
       <c r="G66">
         <v>736.8</v>
@@ -6699,28 +6699,28 @@
         <v>145.5</v>
       </c>
       <c r="M66">
-        <v>38.604288</v>
+        <v>39.20748</v>
       </c>
       <c r="N66">
-        <v>106.895712</v>
+        <v>106.29252</v>
       </c>
       <c r="O66">
-        <v>32.0687136</v>
+        <v>31.887756</v>
       </c>
       <c r="P66">
-        <v>74.82699840000001</v>
+        <v>74.404764</v>
       </c>
       <c r="Q66">
-        <v>234.1269984</v>
+        <v>233.704764</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3987745536495036</v>
+        <v>0.407511547551719</v>
       </c>
       <c r="T66">
-        <v>2.158748430181398</v>
+        <v>2.212182797265096</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.769011359567104</v>
+        <v>3.711026569419916</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1705205416431017</v>
+        <v>0.170019843972382</v>
       </c>
       <c r="C67">
-        <v>361.1128631317303</v>
+        <v>351.5455704456008</v>
       </c>
       <c r="D67">
-        <v>263.9128631317303</v>
+        <v>264.1855704456009</v>
       </c>
       <c r="E67">
-        <v>596.7</v>
+        <v>606.5400000000001</v>
       </c>
       <c r="F67">
-        <v>639.6</v>
+        <v>649.4400000000001</v>
       </c>
       <c r="G67">
         <v>736.8</v>
@@ -6781,28 +6781,28 @@
         <v>145.5</v>
       </c>
       <c r="M67">
-        <v>39.20748</v>
+        <v>39.810672</v>
       </c>
       <c r="N67">
-        <v>106.29252</v>
+        <v>105.689328</v>
       </c>
       <c r="O67">
-        <v>31.887756</v>
+        <v>31.7067984</v>
       </c>
       <c r="P67">
-        <v>74.404764</v>
+        <v>73.98252959999999</v>
       </c>
       <c r="Q67">
-        <v>233.704764</v>
+        <v>233.2825296</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.407511547551719</v>
+        <v>0.4167624822717119</v>
       </c>
       <c r="T67">
-        <v>2.212182797265096</v>
+        <v>2.268760362412541</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.711026569419916</v>
+        <v>3.654798894125675</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.170019843972382</v>
+        <v>0.1695191463016624</v>
       </c>
       <c r="C68">
-        <v>351.5455704456008</v>
+        <v>341.9788419320938</v>
       </c>
       <c r="D68">
-        <v>264.1855704456009</v>
+        <v>264.4588419320939</v>
       </c>
       <c r="E68">
-        <v>606.5400000000001</v>
+        <v>616.3800000000001</v>
       </c>
       <c r="F68">
-        <v>649.4400000000001</v>
+        <v>659.2800000000001</v>
       </c>
       <c r="G68">
         <v>736.8</v>
@@ -6863,28 +6863,28 @@
         <v>145.5</v>
       </c>
       <c r="M68">
-        <v>39.810672</v>
+        <v>40.413864</v>
       </c>
       <c r="N68">
-        <v>105.689328</v>
+        <v>105.086136</v>
       </c>
       <c r="O68">
-        <v>31.7067984</v>
+        <v>31.5258408</v>
       </c>
       <c r="P68">
-        <v>73.98252959999999</v>
+        <v>73.5602952</v>
       </c>
       <c r="Q68">
-        <v>233.2825296</v>
+        <v>232.8602952</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4167624822717119</v>
+        <v>0.4265740797020073</v>
       </c>
       <c r="T68">
-        <v>2.268760362412541</v>
+        <v>2.328766870902255</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.654798894125675</v>
+        <v>3.600249656899919</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1695191463016624</v>
+        <v>0.1690184486309428</v>
       </c>
       <c r="C69">
-        <v>341.9788419320938</v>
+        <v>332.4126793437492</v>
       </c>
       <c r="D69">
-        <v>264.4588419320939</v>
+        <v>264.7326793437493</v>
       </c>
       <c r="E69">
-        <v>616.3800000000001</v>
+        <v>626.22</v>
       </c>
       <c r="F69">
-        <v>659.2800000000001</v>
+        <v>669.12</v>
       </c>
       <c r="G69">
         <v>736.8</v>
@@ -6945,28 +6945,28 @@
         <v>145.5</v>
       </c>
       <c r="M69">
-        <v>40.413864</v>
+        <v>41.017056</v>
       </c>
       <c r="N69">
-        <v>105.086136</v>
+        <v>104.482944</v>
       </c>
       <c r="O69">
-        <v>31.5258408</v>
+        <v>31.3448832</v>
       </c>
       <c r="P69">
-        <v>73.5602952</v>
+        <v>73.13806080000001</v>
       </c>
       <c r="Q69">
-        <v>232.8602952</v>
+        <v>232.4380608</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4265740797020073</v>
+        <v>0.4369989019716962</v>
       </c>
       <c r="T69">
-        <v>2.328766870902255</v>
+        <v>2.392523786172577</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.600249656899919</v>
+        <v>3.547304809004332</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1690184486309428</v>
+        <v>0.1698701509602231</v>
       </c>
       <c r="C70">
-        <v>332.4126793437492</v>
+        <v>322.1072109097154</v>
       </c>
       <c r="D70">
-        <v>264.7326793437493</v>
+        <v>264.2672109097154</v>
       </c>
       <c r="E70">
-        <v>626.22</v>
+        <v>636.0600000000001</v>
       </c>
       <c r="F70">
-        <v>669.12</v>
+        <v>678.96</v>
       </c>
       <c r="G70">
         <v>736.8</v>
@@ -7027,45 +7027,45 @@
         <v>145.5</v>
       </c>
       <c r="M70">
-        <v>41.017056</v>
+        <v>43.52133600000001</v>
       </c>
       <c r="N70">
-        <v>104.482944</v>
+        <v>101.978664</v>
       </c>
       <c r="O70">
-        <v>31.3448832</v>
+        <v>30.5935992</v>
       </c>
       <c r="P70">
-        <v>73.13806080000001</v>
+        <v>71.38506479999999</v>
       </c>
       <c r="Q70">
-        <v>232.4380608</v>
+        <v>230.6850648</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4369989019716962</v>
+        <v>0.4480962934200747</v>
       </c>
       <c r="T70">
-        <v>2.392523786172577</v>
+        <v>2.460394050815177</v>
       </c>
       <c r="U70">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V70">
         <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>3.547304809004332</v>
+        <v>3.343187810227149</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1698701509602231</v>
+        <v>0.1693890532895035</v>
       </c>
       <c r="C71">
-        <v>322.1072109097154</v>
+        <v>312.5299368328992</v>
       </c>
       <c r="D71">
-        <v>264.2672109097154</v>
+        <v>264.5299368328994</v>
       </c>
       <c r="E71">
-        <v>636.0600000000001</v>
+        <v>645.9000000000001</v>
       </c>
       <c r="F71">
-        <v>678.96</v>
+        <v>688.8000000000001</v>
       </c>
       <c r="G71">
         <v>736.8</v>
@@ -7109,28 +7109,28 @@
         <v>145.5</v>
       </c>
       <c r="M71">
-        <v>43.52133600000001</v>
+        <v>44.15208000000001</v>
       </c>
       <c r="N71">
-        <v>101.978664</v>
+        <v>101.34792</v>
       </c>
       <c r="O71">
-        <v>30.5935992</v>
+        <v>30.404376</v>
       </c>
       <c r="P71">
-        <v>71.38506479999999</v>
+        <v>70.94354399999999</v>
       </c>
       <c r="Q71">
-        <v>230.6850648</v>
+        <v>230.243544</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4480962934200747</v>
+        <v>0.4599335109650117</v>
       </c>
       <c r="T71">
-        <v>2.460394050815177</v>
+        <v>2.532788999767284</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.343187810227149</v>
+        <v>3.295427984366761</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1693890532895035</v>
+        <v>0.1689079556187839</v>
       </c>
       <c r="C72">
-        <v>312.5299368328992</v>
+        <v>302.95318566319</v>
       </c>
       <c r="D72">
-        <v>264.5299368328994</v>
+        <v>264.7931856631901</v>
       </c>
       <c r="E72">
-        <v>645.9000000000001</v>
+        <v>655.7400000000001</v>
       </c>
       <c r="F72">
-        <v>688.8000000000001</v>
+        <v>698.6400000000001</v>
       </c>
       <c r="G72">
         <v>736.8</v>
@@ -7191,28 +7191,28 @@
         <v>145.5</v>
       </c>
       <c r="M72">
-        <v>44.15208000000001</v>
+        <v>44.78282400000001</v>
       </c>
       <c r="N72">
-        <v>101.34792</v>
+        <v>100.717176</v>
       </c>
       <c r="O72">
-        <v>30.404376</v>
+        <v>30.2151528</v>
       </c>
       <c r="P72">
-        <v>70.94354399999999</v>
+        <v>70.5020232</v>
       </c>
       <c r="Q72">
-        <v>230.243544</v>
+        <v>229.8020232</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4599335109650117</v>
+        <v>0.4725870883406341</v>
       </c>
       <c r="T72">
-        <v>2.532788999767284</v>
+        <v>2.610176703819536</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.295427984366761</v>
+        <v>3.249013505713708</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1689079556187839</v>
+        <v>0.1684268579480642</v>
       </c>
       <c r="C73">
-        <v>302.9531856631901</v>
+        <v>293.3769589632666</v>
       </c>
       <c r="D73">
-        <v>264.7931856631901</v>
+        <v>265.0569589632667</v>
       </c>
       <c r="E73">
-        <v>655.74</v>
+        <v>665.58</v>
       </c>
       <c r="F73">
-        <v>698.64</v>
+        <v>708.48</v>
       </c>
       <c r="G73">
         <v>736.8</v>
@@ -7273,28 +7273,28 @@
         <v>145.5</v>
       </c>
       <c r="M73">
-        <v>44.78282400000001</v>
+        <v>45.41356800000001</v>
       </c>
       <c r="N73">
-        <v>100.717176</v>
+        <v>100.086432</v>
       </c>
       <c r="O73">
-        <v>30.2151528</v>
+        <v>30.0259296</v>
       </c>
       <c r="P73">
-        <v>70.5020232</v>
+        <v>70.0605024</v>
       </c>
       <c r="Q73">
-        <v>229.8020232</v>
+        <v>229.3605024</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.472587088340634</v>
+        <v>0.486144492671658</v>
       </c>
       <c r="T73">
-        <v>2.610176703819536</v>
+        <v>2.693092101018378</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.249013505713708</v>
+        <v>3.203888318134351</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1684268579480642</v>
+        <v>0.1679457602773446</v>
       </c>
       <c r="C74">
-        <v>293.3769589632666</v>
+        <v>283.8012583020414</v>
       </c>
       <c r="D74">
-        <v>265.0569589632667</v>
+        <v>265.3212583020414</v>
       </c>
       <c r="E74">
-        <v>665.58</v>
+        <v>675.42</v>
       </c>
       <c r="F74">
-        <v>708.48</v>
+        <v>718.3199999999999</v>
       </c>
       <c r="G74">
         <v>736.8</v>
@@ -7355,28 +7355,28 @@
         <v>145.5</v>
       </c>
       <c r="M74">
-        <v>45.41356800000001</v>
+        <v>46.044312</v>
       </c>
       <c r="N74">
-        <v>100.086432</v>
+        <v>99.45568800000001</v>
       </c>
       <c r="O74">
-        <v>30.0259296</v>
+        <v>29.8367064</v>
       </c>
       <c r="P74">
-        <v>70.0605024</v>
+        <v>69.61898160000001</v>
       </c>
       <c r="Q74">
-        <v>229.3605024</v>
+        <v>228.9189816</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.486144492671658</v>
+        <v>0.5007061491753503</v>
       </c>
       <c r="T74">
-        <v>2.693092101018378</v>
+        <v>2.782149379491207</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.203888318134351</v>
+        <v>3.159999437064018</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1679457602773446</v>
+        <v>0.167464662606625</v>
       </c>
       <c r="C75">
-        <v>283.8012583020414</v>
+        <v>274.2260852546901</v>
       </c>
       <c r="D75">
-        <v>265.3212583020414</v>
+        <v>265.5860852546901</v>
       </c>
       <c r="E75">
-        <v>675.42</v>
+        <v>685.26</v>
       </c>
       <c r="F75">
-        <v>718.3199999999999</v>
+        <v>728.16</v>
       </c>
       <c r="G75">
         <v>736.8</v>
@@ -7437,28 +7437,28 @@
         <v>145.5</v>
       </c>
       <c r="M75">
-        <v>46.044312</v>
+        <v>46.675056</v>
       </c>
       <c r="N75">
-        <v>99.45568800000001</v>
+        <v>98.824944</v>
       </c>
       <c r="O75">
-        <v>29.8367064</v>
+        <v>29.6474832</v>
       </c>
       <c r="P75">
-        <v>69.61898160000001</v>
+        <v>69.17746080000001</v>
       </c>
       <c r="Q75">
-        <v>228.9189816</v>
+        <v>228.4774608</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5007061491753503</v>
+        <v>0.5163879331024036</v>
       </c>
       <c r="T75">
-        <v>2.782149379491207</v>
+        <v>2.878057217846563</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.159999437064018</v>
+        <v>3.117296741968558</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.167464662606625</v>
+        <v>0.1669835649359053</v>
       </c>
       <c r="C76">
-        <v>274.2260852546901</v>
+        <v>264.6514414026841</v>
       </c>
       <c r="D76">
-        <v>265.5860852546901</v>
+        <v>265.8514414026841</v>
       </c>
       <c r="E76">
-        <v>685.26</v>
+        <v>695.1</v>
       </c>
       <c r="F76">
-        <v>728.16</v>
+        <v>738</v>
       </c>
       <c r="G76">
         <v>736.8</v>
@@ -7519,28 +7519,28 @@
         <v>145.5</v>
       </c>
       <c r="M76">
-        <v>46.675056</v>
+        <v>47.3058</v>
       </c>
       <c r="N76">
-        <v>98.824944</v>
+        <v>98.1942</v>
       </c>
       <c r="O76">
-        <v>29.6474832</v>
+        <v>29.45826</v>
       </c>
       <c r="P76">
-        <v>69.17746080000001</v>
+        <v>68.73594</v>
       </c>
       <c r="Q76">
-        <v>228.4774608</v>
+        <v>228.03594</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5163879331024036</v>
+        <v>0.5333242597436212</v>
       </c>
       <c r="T76">
-        <v>2.878057217846563</v>
+        <v>2.981637683270346</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.117296741968558</v>
+        <v>3.075732785408977</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1669835649359053</v>
+        <v>0.1665024672651857</v>
       </c>
       <c r="C77">
-        <v>264.6514414026841</v>
+        <v>255.0773283338211</v>
       </c>
       <c r="D77">
-        <v>265.8514414026841</v>
+        <v>266.1173283338213</v>
       </c>
       <c r="E77">
-        <v>695.1</v>
+        <v>704.9400000000001</v>
       </c>
       <c r="F77">
-        <v>738</v>
+        <v>747.84</v>
       </c>
       <c r="G77">
         <v>736.8</v>
@@ -7601,28 +7601,28 @@
         <v>145.5</v>
       </c>
       <c r="M77">
-        <v>47.3058</v>
+        <v>47.936544</v>
       </c>
       <c r="N77">
-        <v>98.1942</v>
+        <v>97.563456</v>
       </c>
       <c r="O77">
-        <v>29.45826</v>
+        <v>29.2690368</v>
       </c>
       <c r="P77">
-        <v>68.73594</v>
+        <v>68.29441920000001</v>
       </c>
       <c r="Q77">
-        <v>228.03594</v>
+        <v>227.5944192</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5333242597436212</v>
+        <v>0.5516719469382737</v>
       </c>
       <c r="T77">
-        <v>2.981637683270346</v>
+        <v>3.093849854146113</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.075732785408977</v>
+        <v>3.035262617179912</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1665024672651857</v>
+        <v>0.1702255695944661</v>
       </c>
       <c r="C78">
-        <v>255.0773283338211</v>
+        <v>243.1934528476745</v>
       </c>
       <c r="D78">
-        <v>266.1173283338213</v>
+        <v>264.0734528476747</v>
       </c>
       <c r="E78">
-        <v>704.9400000000001</v>
+        <v>714.7800000000001</v>
       </c>
       <c r="F78">
-        <v>747.84</v>
+        <v>757.6800000000001</v>
       </c>
       <c r="G78">
         <v>736.8</v>
@@ -7683,45 +7683,45 @@
         <v>145.5</v>
       </c>
       <c r="M78">
-        <v>47.936544</v>
+        <v>54.47719200000001</v>
       </c>
       <c r="N78">
-        <v>97.563456</v>
+        <v>91.022808</v>
       </c>
       <c r="O78">
-        <v>29.2690368</v>
+        <v>27.3068424</v>
       </c>
       <c r="P78">
-        <v>68.29441920000001</v>
+        <v>63.7159656</v>
       </c>
       <c r="Q78">
-        <v>227.5944192</v>
+        <v>223.0159656</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5516719469382737</v>
+        <v>0.5716150851933307</v>
       </c>
       <c r="T78">
-        <v>3.093849854146113</v>
+        <v>3.215819605098032</v>
       </c>
       <c r="U78">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V78">
         <v>0.3</v>
       </c>
       <c r="W78">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.035262617179912</v>
+        <v>2.670842505979383</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1702255695944661</v>
+        <v>0.1697990719237464</v>
       </c>
       <c r="C79">
-        <v>243.1934528476745</v>
+        <v>233.585994087294</v>
       </c>
       <c r="D79">
-        <v>264.0734528476747</v>
+        <v>264.3059940872941</v>
       </c>
       <c r="E79">
-        <v>714.7800000000001</v>
+        <v>724.62</v>
       </c>
       <c r="F79">
-        <v>757.6800000000001</v>
+        <v>767.52</v>
       </c>
       <c r="G79">
         <v>736.8</v>
@@ -7765,28 +7765,28 @@
         <v>145.5</v>
       </c>
       <c r="M79">
-        <v>54.47719200000001</v>
+        <v>55.184688</v>
       </c>
       <c r="N79">
-        <v>91.022808</v>
+        <v>90.31531200000001</v>
       </c>
       <c r="O79">
-        <v>27.3068424</v>
+        <v>27.0945936</v>
       </c>
       <c r="P79">
-        <v>63.7159656</v>
+        <v>63.22071840000001</v>
       </c>
       <c r="Q79">
-        <v>223.0159656</v>
+        <v>222.5207184</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5716150851933307</v>
+        <v>0.5933712360170292</v>
       </c>
       <c r="T79">
-        <v>3.215819605098032</v>
+        <v>3.348877515227398</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.670842505979383</v>
+        <v>2.636600935389904</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1697990719237464</v>
+        <v>0.1693725742530268</v>
       </c>
       <c r="C80">
-        <v>233.585994087294</v>
+        <v>223.9789452362621</v>
       </c>
       <c r="D80">
-        <v>264.3059940872941</v>
+        <v>264.5389452362622</v>
       </c>
       <c r="E80">
-        <v>724.62</v>
+        <v>734.46</v>
       </c>
       <c r="F80">
-        <v>767.52</v>
+        <v>777.36</v>
       </c>
       <c r="G80">
         <v>736.8</v>
@@ -7847,28 +7847,28 @@
         <v>145.5</v>
       </c>
       <c r="M80">
-        <v>55.184688</v>
+        <v>55.89218400000001</v>
       </c>
       <c r="N80">
-        <v>90.31531200000001</v>
+        <v>89.60781599999999</v>
       </c>
       <c r="O80">
-        <v>27.0945936</v>
+        <v>26.88234479999999</v>
       </c>
       <c r="P80">
-        <v>63.22071840000001</v>
+        <v>62.72547119999999</v>
       </c>
       <c r="Q80">
-        <v>222.5207184</v>
+        <v>222.0254712</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5933712360170292</v>
+        <v>0.6171994012048895</v>
       </c>
       <c r="T80">
-        <v>3.348877515227398</v>
+        <v>3.494607607273847</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.636600935389904</v>
+        <v>2.603226240005221</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1693725742530268</v>
+        <v>0.1689460765823071</v>
       </c>
       <c r="C81">
-        <v>223.9789452362621</v>
+        <v>214.3723073793794</v>
       </c>
       <c r="D81">
-        <v>264.5389452362622</v>
+        <v>264.7723073793796</v>
       </c>
       <c r="E81">
-        <v>734.46</v>
+        <v>744.3000000000001</v>
       </c>
       <c r="F81">
-        <v>777.36</v>
+        <v>787.2</v>
       </c>
       <c r="G81">
         <v>736.8</v>
@@ -7929,28 +7929,28 @@
         <v>145.5</v>
       </c>
       <c r="M81">
-        <v>55.89218400000001</v>
+        <v>56.59968000000001</v>
       </c>
       <c r="N81">
-        <v>89.60781599999999</v>
+        <v>88.90031999999999</v>
       </c>
       <c r="O81">
-        <v>26.88234479999999</v>
+        <v>26.670096</v>
       </c>
       <c r="P81">
-        <v>62.72547119999999</v>
+        <v>62.23022399999999</v>
       </c>
       <c r="Q81">
-        <v>222.0254712</v>
+        <v>221.530224</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6171994012048895</v>
+        <v>0.6434103829115358</v>
       </c>
       <c r="T81">
-        <v>3.494607607273847</v>
+        <v>3.654910708524941</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.603226240005221</v>
+        <v>2.570685912005156</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1689460765823071</v>
+        <v>0.1685195789115875</v>
       </c>
       <c r="C82">
-        <v>214.3723073793794</v>
+        <v>204.7660816052777</v>
       </c>
       <c r="D82">
-        <v>264.7723073793796</v>
+        <v>265.0060816052778</v>
       </c>
       <c r="E82">
-        <v>744.3000000000001</v>
+        <v>754.1400000000001</v>
       </c>
       <c r="F82">
-        <v>787.2</v>
+        <v>797.0400000000001</v>
       </c>
       <c r="G82">
         <v>736.8</v>
@@ -8011,28 +8011,28 @@
         <v>145.5</v>
       </c>
       <c r="M82">
-        <v>56.59968000000001</v>
+        <v>57.30717600000001</v>
       </c>
       <c r="N82">
-        <v>88.90031999999999</v>
+        <v>88.19282399999999</v>
       </c>
       <c r="O82">
-        <v>26.670096</v>
+        <v>26.4578472</v>
       </c>
       <c r="P82">
-        <v>62.23022399999999</v>
+        <v>61.73497679999999</v>
       </c>
       <c r="Q82">
-        <v>221.530224</v>
+        <v>221.0349768</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6434103829115358</v>
+        <v>0.6723804153241449</v>
       </c>
       <c r="T82">
-        <v>3.654910708524941</v>
+        <v>3.832087820434046</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.570685912005156</v>
+        <v>2.538949048893981</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1685195789115875</v>
+        <v>0.1680930812408679</v>
       </c>
       <c r="C83">
-        <v>204.7660816052777</v>
+        <v>195.1602690064365</v>
       </c>
       <c r="D83">
-        <v>265.0060816052778</v>
+        <v>265.2402690064367</v>
       </c>
       <c r="E83">
-        <v>754.1400000000001</v>
+        <v>763.9800000000001</v>
       </c>
       <c r="F83">
-        <v>797.0400000000001</v>
+        <v>806.8800000000001</v>
       </c>
       <c r="G83">
         <v>736.8</v>
@@ -8093,28 +8093,28 @@
         <v>145.5</v>
       </c>
       <c r="M83">
-        <v>57.30717600000001</v>
+        <v>58.01467200000001</v>
       </c>
       <c r="N83">
-        <v>88.19282399999999</v>
+        <v>87.48532799999998</v>
       </c>
       <c r="O83">
-        <v>26.4578472</v>
+        <v>26.2455984</v>
       </c>
       <c r="P83">
-        <v>61.73497679999999</v>
+        <v>61.23972959999999</v>
       </c>
       <c r="Q83">
-        <v>221.0349768</v>
+        <v>220.5397296</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6723804153241449</v>
+        <v>0.704569340227044</v>
       </c>
       <c r="T83">
-        <v>3.832087820434046</v>
+        <v>4.028951278110828</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.538949048893981</v>
+        <v>2.507986255614786</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1680930812408679</v>
+        <v>0.1699324835701482</v>
       </c>
       <c r="C84">
-        <v>195.1602690064365</v>
+        <v>184.3132094504981</v>
       </c>
       <c r="D84">
-        <v>265.2402690064367</v>
+        <v>264.2332094504981</v>
       </c>
       <c r="E84">
-        <v>763.9800000000001</v>
+        <v>773.8200000000001</v>
       </c>
       <c r="F84">
-        <v>806.8800000000001</v>
+        <v>816.72</v>
       </c>
       <c r="G84">
         <v>736.8</v>
@@ -8175,45 +8175,45 @@
         <v>145.5</v>
       </c>
       <c r="M84">
-        <v>58.01467200000001</v>
+        <v>61.90737600000001</v>
       </c>
       <c r="N84">
-        <v>87.48532799999998</v>
+        <v>83.592624</v>
       </c>
       <c r="O84">
-        <v>26.2455984</v>
+        <v>25.0777872</v>
       </c>
       <c r="P84">
-        <v>61.23972959999999</v>
+        <v>58.5148368</v>
       </c>
       <c r="Q84">
-        <v>220.5397296</v>
+        <v>217.8148368</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.704569340227044</v>
+        <v>0.7405451974714605</v>
       </c>
       <c r="T84">
-        <v>4.028951278110828</v>
+        <v>4.248975142573114</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.3</v>
       </c>
       <c r="W84">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.507986255614786</v>
+        <v>2.350285368257249</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1699324835701482</v>
+        <v>0.1695332858994286</v>
       </c>
       <c r="C85">
-        <v>184.3132094504981</v>
+        <v>174.691117045438</v>
       </c>
       <c r="D85">
-        <v>264.2332094504981</v>
+        <v>264.4511170454381</v>
       </c>
       <c r="E85">
-        <v>773.8200000000001</v>
+        <v>783.6600000000001</v>
       </c>
       <c r="F85">
-        <v>816.72</v>
+        <v>826.5600000000001</v>
       </c>
       <c r="G85">
         <v>736.8</v>
@@ -8257,28 +8257,28 @@
         <v>145.5</v>
       </c>
       <c r="M85">
-        <v>61.90737600000001</v>
+        <v>62.65324800000001</v>
       </c>
       <c r="N85">
-        <v>83.592624</v>
+        <v>82.84675199999998</v>
       </c>
       <c r="O85">
-        <v>25.0777872</v>
+        <v>24.85402559999999</v>
       </c>
       <c r="P85">
-        <v>58.5148368</v>
+        <v>57.99272639999999</v>
       </c>
       <c r="Q85">
-        <v>217.8148368</v>
+        <v>217.2927264</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7405451974714605</v>
+        <v>0.7810180368714292</v>
       </c>
       <c r="T85">
-        <v>4.248975142573114</v>
+        <v>4.496501990093186</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.350285368257249</v>
+        <v>2.3223057805399</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1695332858994286</v>
+        <v>0.169134088228709</v>
       </c>
       <c r="C86">
-        <v>174.6911170454381</v>
+        <v>165.0693843446799</v>
       </c>
       <c r="D86">
-        <v>264.4511170454381</v>
+        <v>264.6693843446799</v>
       </c>
       <c r="E86">
-        <v>783.66</v>
+        <v>793.5</v>
       </c>
       <c r="F86">
-        <v>826.5599999999999</v>
+        <v>836.4</v>
       </c>
       <c r="G86">
         <v>736.8</v>
@@ -8339,28 +8339,28 @@
         <v>145.5</v>
       </c>
       <c r="M86">
-        <v>62.653248</v>
+        <v>63.39912</v>
       </c>
       <c r="N86">
-        <v>82.84675200000001</v>
+        <v>82.10087999999999</v>
       </c>
       <c r="O86">
-        <v>24.8540256</v>
+        <v>24.630264</v>
       </c>
       <c r="P86">
-        <v>57.99272640000001</v>
+        <v>57.47061599999999</v>
       </c>
       <c r="Q86">
-        <v>217.2927264</v>
+        <v>216.770616</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7810180368714287</v>
+        <v>0.8268872548580598</v>
       </c>
       <c r="T86">
-        <v>4.496501990093183</v>
+        <v>4.777032417282598</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.322305780539901</v>
+        <v>2.294984536062961</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.169134088228709</v>
+        <v>0.1687348905579893</v>
       </c>
       <c r="C87">
-        <v>165.0693843446799</v>
+        <v>155.4480122396159</v>
       </c>
       <c r="D87">
-        <v>264.6693843446799</v>
+        <v>264.8880122396159</v>
       </c>
       <c r="E87">
-        <v>793.5</v>
+        <v>803.34</v>
       </c>
       <c r="F87">
-        <v>836.4</v>
+        <v>846.24</v>
       </c>
       <c r="G87">
         <v>736.8</v>
@@ -8421,28 +8421,28 @@
         <v>145.5</v>
       </c>
       <c r="M87">
-        <v>63.39912</v>
+        <v>64.144992</v>
       </c>
       <c r="N87">
-        <v>82.10087999999999</v>
+        <v>81.355008</v>
       </c>
       <c r="O87">
-        <v>24.630264</v>
+        <v>24.4065024</v>
       </c>
       <c r="P87">
-        <v>57.47061599999999</v>
+        <v>56.9485056</v>
       </c>
       <c r="Q87">
-        <v>216.770616</v>
+        <v>216.2485056</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8268872548580598</v>
+        <v>0.8793092182713523</v>
       </c>
       <c r="T87">
-        <v>4.777032417282598</v>
+        <v>5.097638619784785</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.294984536062961</v>
+        <v>2.268298669364555</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1687348905579893</v>
+        <v>0.1683356928872697</v>
       </c>
       <c r="C88">
-        <v>155.4480122396159</v>
+        <v>145.8270016245856</v>
       </c>
       <c r="D88">
-        <v>264.8880122396159</v>
+        <v>265.1070016245857</v>
       </c>
       <c r="E88">
-        <v>803.34</v>
+        <v>813.1800000000001</v>
       </c>
       <c r="F88">
-        <v>846.24</v>
+        <v>856.08</v>
       </c>
       <c r="G88">
         <v>736.8</v>
@@ -8503,28 +8503,28 @@
         <v>145.5</v>
       </c>
       <c r="M88">
-        <v>64.144992</v>
+        <v>64.89086400000001</v>
       </c>
       <c r="N88">
-        <v>81.355008</v>
+        <v>80.60913599999999</v>
       </c>
       <c r="O88">
-        <v>24.4065024</v>
+        <v>24.1827408</v>
       </c>
       <c r="P88">
-        <v>56.9485056</v>
+        <v>56.42639519999999</v>
       </c>
       <c r="Q88">
-        <v>216.2485056</v>
+        <v>215.7263952</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8793092182713523</v>
+        <v>0.9397960991328439</v>
       </c>
       <c r="T88">
-        <v>5.097638619784785</v>
+        <v>5.467568853441156</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.268298669364555</v>
+        <v>2.242226270866111</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1683356928872697</v>
+        <v>0.1679364952165501</v>
       </c>
       <c r="C89">
-        <v>145.8270016245856</v>
+        <v>136.2063533968889</v>
       </c>
       <c r="D89">
-        <v>265.1070016245857</v>
+        <v>265.3263533968889</v>
       </c>
       <c r="E89">
-        <v>813.1800000000001</v>
+        <v>823.02</v>
       </c>
       <c r="F89">
-        <v>856.08</v>
+        <v>865.92</v>
       </c>
       <c r="G89">
         <v>736.8</v>
@@ -8585,28 +8585,28 @@
         <v>145.5</v>
       </c>
       <c r="M89">
-        <v>64.89086400000001</v>
+        <v>65.636736</v>
       </c>
       <c r="N89">
-        <v>80.60913599999999</v>
+        <v>79.863264</v>
       </c>
       <c r="O89">
-        <v>24.1827408</v>
+        <v>23.9589792</v>
       </c>
       <c r="P89">
-        <v>56.42639519999999</v>
+        <v>55.9042848</v>
       </c>
       <c r="Q89">
-        <v>215.7263952</v>
+        <v>215.2042848</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9397960991328439</v>
+        <v>1.010364126804584</v>
       </c>
       <c r="T89">
-        <v>5.467568853441156</v>
+        <v>5.899154126040256</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.242226270866111</v>
+        <v>2.216746426878997</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1679364952165501</v>
+        <v>0.1675372975458304</v>
       </c>
       <c r="C90">
-        <v>136.2063533968889</v>
+        <v>126.5860684567976</v>
       </c>
       <c r="D90">
-        <v>265.3263533968889</v>
+        <v>265.5460684567977</v>
       </c>
       <c r="E90">
-        <v>823.02</v>
+        <v>832.86</v>
       </c>
       <c r="F90">
-        <v>865.92</v>
+        <v>875.76</v>
       </c>
       <c r="G90">
         <v>736.8</v>
@@ -8667,28 +8667,28 @@
         <v>145.5</v>
       </c>
       <c r="M90">
-        <v>65.636736</v>
+        <v>66.382608</v>
       </c>
       <c r="N90">
-        <v>79.863264</v>
+        <v>79.117392</v>
       </c>
       <c r="O90">
-        <v>23.9589792</v>
+        <v>23.7352176</v>
       </c>
       <c r="P90">
-        <v>55.9042848</v>
+        <v>55.3821744</v>
       </c>
       <c r="Q90">
-        <v>215.2042848</v>
+        <v>214.6821744</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.010364126804584</v>
+        <v>1.093762704962095</v>
       </c>
       <c r="T90">
-        <v>5.899154126040256</v>
+        <v>6.409209448202827</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.216746426878997</v>
+        <v>2.191839163655637</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1675372975458304</v>
+        <v>0.1671380998751108</v>
       </c>
       <c r="C91">
-        <v>126.5860684567976</v>
+        <v>116.9661477075682</v>
       </c>
       <c r="D91">
-        <v>265.5460684567977</v>
+        <v>265.7661477075683</v>
       </c>
       <c r="E91">
-        <v>832.86</v>
+        <v>842.7</v>
       </c>
       <c r="F91">
-        <v>875.76</v>
+        <v>885.6</v>
       </c>
       <c r="G91">
         <v>736.8</v>
@@ -8749,28 +8749,28 @@
         <v>145.5</v>
       </c>
       <c r="M91">
-        <v>66.382608</v>
+        <v>67.12848000000001</v>
       </c>
       <c r="N91">
-        <v>79.117392</v>
+        <v>78.37151999999999</v>
       </c>
       <c r="O91">
-        <v>23.7352176</v>
+        <v>23.511456</v>
       </c>
       <c r="P91">
-        <v>55.3821744</v>
+        <v>54.86006399999999</v>
       </c>
       <c r="Q91">
-        <v>214.6821744</v>
+        <v>214.160064</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.093762704962095</v>
+        <v>1.193840998751108</v>
       </c>
       <c r="T91">
-        <v>6.409209448202827</v>
+        <v>7.021275834797914</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.191839163655637</v>
+        <v>2.167485395170574</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1671380998751108</v>
+        <v>0.1667389022043912</v>
       </c>
       <c r="C92">
-        <v>116.9661477075682</v>
+        <v>107.3465920554539</v>
       </c>
       <c r="D92">
-        <v>265.7661477075683</v>
+        <v>265.986592055454</v>
       </c>
       <c r="E92">
-        <v>842.7</v>
+        <v>852.5400000000001</v>
       </c>
       <c r="F92">
-        <v>885.6</v>
+        <v>895.4400000000001</v>
       </c>
       <c r="G92">
         <v>736.8</v>
@@ -8831,28 +8831,28 @@
         <v>145.5</v>
       </c>
       <c r="M92">
-        <v>67.12848000000001</v>
+        <v>67.87435200000002</v>
       </c>
       <c r="N92">
-        <v>78.37151999999999</v>
+        <v>77.62564799999998</v>
       </c>
       <c r="O92">
-        <v>23.511456</v>
+        <v>23.2876944</v>
       </c>
       <c r="P92">
-        <v>54.86006399999999</v>
+        <v>54.33795359999999</v>
       </c>
       <c r="Q92">
-        <v>214.160064</v>
+        <v>213.6379536</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.193840998751108</v>
+        <v>1.316158913382125</v>
       </c>
       <c r="T92">
-        <v>7.021275834797914</v>
+        <v>7.769356973969686</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.167485395170574</v>
+        <v>2.143666874344524</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1667389022043912</v>
+        <v>0.1663397045336715</v>
       </c>
       <c r="C93">
-        <v>107.3465920554539</v>
+        <v>97.72740240971746</v>
       </c>
       <c r="D93">
-        <v>265.986592055454</v>
+        <v>266.2074024097176</v>
       </c>
       <c r="E93">
-        <v>852.5400000000001</v>
+        <v>862.3800000000001</v>
       </c>
       <c r="F93">
-        <v>895.4400000000001</v>
+        <v>905.2800000000001</v>
       </c>
       <c r="G93">
         <v>736.8</v>
@@ -8913,28 +8913,28 @@
         <v>145.5</v>
       </c>
       <c r="M93">
-        <v>67.87435200000002</v>
+        <v>68.62022400000001</v>
       </c>
       <c r="N93">
-        <v>77.62564799999998</v>
+        <v>76.87977599999999</v>
       </c>
       <c r="O93">
-        <v>23.2876944</v>
+        <v>23.0639328</v>
       </c>
       <c r="P93">
-        <v>54.33795359999999</v>
+        <v>53.8158432</v>
       </c>
       <c r="Q93">
-        <v>213.6379536</v>
+        <v>213.1158432</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.316158913382125</v>
+        <v>1.469056306670895</v>
       </c>
       <c r="T93">
-        <v>7.769356973969686</v>
+        <v>8.704458397934403</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.143666874344524</v>
+        <v>2.120366147449475</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1663397045336715</v>
+        <v>0.1659405068629519</v>
       </c>
       <c r="C94">
-        <v>97.72740240971746</v>
+        <v>88.10857968264338</v>
       </c>
       <c r="D94">
-        <v>266.2074024097176</v>
+        <v>266.4285796826434</v>
       </c>
       <c r="E94">
-        <v>862.3800000000001</v>
+        <v>872.22</v>
       </c>
       <c r="F94">
-        <v>905.2800000000001</v>
+        <v>915.12</v>
       </c>
       <c r="G94">
         <v>736.8</v>
@@ -8995,28 +8995,28 @@
         <v>145.5</v>
       </c>
       <c r="M94">
-        <v>68.62022400000001</v>
+        <v>69.36609600000001</v>
       </c>
       <c r="N94">
-        <v>76.87977599999999</v>
+        <v>76.13390399999999</v>
       </c>
       <c r="O94">
-        <v>23.0639328</v>
+        <v>22.8401712</v>
       </c>
       <c r="P94">
-        <v>53.8158432</v>
+        <v>53.29373279999999</v>
       </c>
       <c r="Q94">
-        <v>213.1158432</v>
+        <v>212.5937328</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.469056306670895</v>
+        <v>1.665638669470743</v>
       </c>
       <c r="T94">
-        <v>8.704458397934403</v>
+        <v>9.906731657317609</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.120366147449475</v>
+        <v>2.097566511455394</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1659405068629519</v>
+        <v>0.1655413091922323</v>
       </c>
       <c r="C95">
-        <v>88.10857968264338</v>
+        <v>78.49012478955024</v>
       </c>
       <c r="D95">
-        <v>266.4285796826434</v>
+        <v>266.6501247895504</v>
       </c>
       <c r="E95">
-        <v>872.22</v>
+        <v>882.0600000000001</v>
       </c>
       <c r="F95">
-        <v>915.12</v>
+        <v>924.96</v>
       </c>
       <c r="G95">
         <v>736.8</v>
@@ -9077,28 +9077,28 @@
         <v>145.5</v>
       </c>
       <c r="M95">
-        <v>69.36609600000001</v>
+        <v>70.111968</v>
       </c>
       <c r="N95">
-        <v>76.13390399999999</v>
+        <v>75.388032</v>
       </c>
       <c r="O95">
-        <v>22.8401712</v>
+        <v>22.6164096</v>
       </c>
       <c r="P95">
-        <v>53.29373279999999</v>
+        <v>52.7716224</v>
       </c>
       <c r="Q95">
-        <v>212.5937328</v>
+        <v>212.0716224</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.665638669470743</v>
+        <v>1.927748486537207</v>
       </c>
       <c r="T95">
-        <v>9.906731657317609</v>
+        <v>11.50976266982855</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.097566511455394</v>
+        <v>2.075251974099486</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1655413091922323</v>
+        <v>0.1651421115215126</v>
       </c>
       <c r="C96">
-        <v>78.49012478955024</v>
+        <v>68.87203864880428</v>
       </c>
       <c r="D96">
-        <v>266.6501247895504</v>
+        <v>266.8720386488043</v>
       </c>
       <c r="E96">
-        <v>882.0600000000001</v>
+        <v>891.9000000000001</v>
       </c>
       <c r="F96">
-        <v>924.96</v>
+        <v>934.8000000000001</v>
       </c>
       <c r="G96">
         <v>736.8</v>
@@ -9159,28 +9159,28 @@
         <v>145.5</v>
       </c>
       <c r="M96">
-        <v>70.111968</v>
+        <v>70.85784000000001</v>
       </c>
       <c r="N96">
-        <v>75.388032</v>
+        <v>74.64215999999999</v>
       </c>
       <c r="O96">
-        <v>22.6164096</v>
+        <v>22.392648</v>
       </c>
       <c r="P96">
-        <v>52.7716224</v>
+        <v>52.249512</v>
       </c>
       <c r="Q96">
-        <v>212.0716224</v>
+        <v>211.549512</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.927748486537207</v>
+        <v>2.294702230430256</v>
       </c>
       <c r="T96">
-        <v>11.50976266982855</v>
+        <v>13.75400608734387</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.075251974099486</v>
+        <v>2.053407216477386</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1651421115215126</v>
+        <v>0.164742913850793</v>
       </c>
       <c r="C97">
-        <v>68.87203864880428</v>
+        <v>59.25432218183073</v>
       </c>
       <c r="D97">
-        <v>266.8720386488043</v>
+        <v>267.0943221818309</v>
       </c>
       <c r="E97">
-        <v>891.9000000000001</v>
+        <v>901.7400000000001</v>
       </c>
       <c r="F97">
-        <v>934.8000000000001</v>
+        <v>944.6400000000001</v>
       </c>
       <c r="G97">
         <v>736.8</v>
@@ -9241,28 +9241,28 @@
         <v>145.5</v>
       </c>
       <c r="M97">
-        <v>70.85784000000001</v>
+        <v>71.60371200000002</v>
       </c>
       <c r="N97">
-        <v>74.64215999999999</v>
+        <v>73.89628799999998</v>
       </c>
       <c r="O97">
-        <v>22.392648</v>
+        <v>22.16888639999999</v>
       </c>
       <c r="P97">
-        <v>52.249512</v>
+        <v>51.72740159999999</v>
       </c>
       <c r="Q97">
-        <v>211.549512</v>
+        <v>211.0274016</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.294702230430256</v>
+        <v>2.84513284626983</v>
       </c>
       <c r="T97">
-        <v>13.75400608734387</v>
+        <v>17.12037121361686</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.053407216477386</v>
+        <v>2.032017557972413</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.164742913850793</v>
+        <v>0.1643437161800734</v>
       </c>
       <c r="C98">
-        <v>59.25432218183084</v>
+        <v>49.63697631312812</v>
       </c>
       <c r="D98">
-        <v>267.0943221818309</v>
+        <v>267.3169763131281</v>
       </c>
       <c r="E98">
-        <v>901.74</v>
+        <v>911.58</v>
       </c>
       <c r="F98">
-        <v>944.64</v>
+        <v>954.48</v>
       </c>
       <c r="G98">
         <v>736.8</v>
@@ -9323,28 +9323,28 @@
         <v>145.5</v>
       </c>
       <c r="M98">
-        <v>71.603712</v>
+        <v>72.34958400000001</v>
       </c>
       <c r="N98">
-        <v>73.896288</v>
+        <v>73.15041599999999</v>
       </c>
       <c r="O98">
-        <v>22.1688864</v>
+        <v>21.9451248</v>
       </c>
       <c r="P98">
-        <v>51.7274016</v>
+        <v>51.20529119999999</v>
       </c>
       <c r="Q98">
-        <v>211.0274016</v>
+        <v>210.5052912</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.845132846269823</v>
+        <v>3.762517206002443</v>
       </c>
       <c r="T98">
-        <v>17.12037121361681</v>
+        <v>22.7309797574051</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.032017557972413</v>
+        <v>2.011068923354141</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1643437161800734</v>
+        <v>0.1736857185093537</v>
       </c>
       <c r="C99">
-        <v>49.63697631312812</v>
+        <v>34.68187930464069</v>
       </c>
       <c r="D99">
-        <v>267.3169763131281</v>
+        <v>262.2018793046407</v>
       </c>
       <c r="E99">
-        <v>911.58</v>
+        <v>921.42</v>
       </c>
       <c r="F99">
-        <v>954.48</v>
+        <v>964.3199999999999</v>
       </c>
       <c r="G99">
         <v>736.8</v>
@@ -9405,45 +9405,45 @@
         <v>145.5</v>
       </c>
       <c r="M99">
-        <v>72.34958400000001</v>
+        <v>86.78879999999999</v>
       </c>
       <c r="N99">
-        <v>73.15041599999999</v>
+        <v>58.71120000000001</v>
       </c>
       <c r="O99">
-        <v>21.9451248</v>
+        <v>17.61336</v>
       </c>
       <c r="P99">
-        <v>51.20529119999999</v>
+        <v>41.09784000000001</v>
       </c>
       <c r="Q99">
-        <v>210.5052912</v>
+        <v>200.39784</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.762517206002443</v>
+        <v>5.597285925467682</v>
       </c>
       <c r="T99">
-        <v>22.7309797574051</v>
+        <v>33.95219684498166</v>
       </c>
       <c r="U99">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V99">
         <v>0.3</v>
       </c>
       <c r="W99">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y99">
-        <v>2.011068923354141</v>
+        <v>1.67648360157071</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1736857185093537</v>
+        <v>0.1733859208386341</v>
       </c>
       <c r="C100">
-        <v>34.68187930464069</v>
+        <v>25.0029877049376</v>
       </c>
       <c r="D100">
-        <v>262.2018793046407</v>
+        <v>262.3629877049376</v>
       </c>
       <c r="E100">
-        <v>921.42</v>
+        <v>931.26</v>
       </c>
       <c r="F100">
-        <v>964.3199999999999</v>
+        <v>974.16</v>
       </c>
       <c r="G100">
         <v>736.8</v>
@@ -9487,28 +9487,28 @@
         <v>145.5</v>
       </c>
       <c r="M100">
-        <v>86.78879999999999</v>
+        <v>87.67439999999999</v>
       </c>
       <c r="N100">
-        <v>58.71120000000001</v>
+        <v>57.82560000000001</v>
       </c>
       <c r="O100">
-        <v>17.61336</v>
+        <v>17.34768</v>
       </c>
       <c r="P100">
-        <v>41.09784000000001</v>
+        <v>40.47792000000001</v>
       </c>
       <c r="Q100">
-        <v>200.39784</v>
+        <v>199.77792</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.597285925467682</v>
+        <v>11.1015920838634</v>
       </c>
       <c r="T100">
-        <v>33.95219684498166</v>
+        <v>67.61584810771136</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.67648360157071</v>
+        <v>1.659549423777066</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1733859208386341</v>
-      </c>
-      <c r="C101">
-        <v>25.0029877049376</v>
-      </c>
-      <c r="D101">
-        <v>262.3629877049376</v>
-      </c>
-      <c r="E101">
-        <v>931.26</v>
-      </c>
-      <c r="F101">
-        <v>974.16</v>
-      </c>
-      <c r="G101">
-        <v>736.8</v>
-      </c>
-      <c r="H101">
-        <v>941.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>304.8</v>
-      </c>
-      <c r="K101">
-        <v>159.3</v>
-      </c>
-      <c r="L101">
-        <v>145.5</v>
-      </c>
-      <c r="M101">
-        <v>87.67439999999999</v>
-      </c>
-      <c r="N101">
-        <v>57.82560000000001</v>
-      </c>
-      <c r="O101">
-        <v>17.34768</v>
-      </c>
-      <c r="P101">
-        <v>40.47792000000001</v>
-      </c>
-      <c r="Q101">
-        <v>199.77792</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.1015920838634</v>
-      </c>
-      <c r="T101">
-        <v>67.61584810771136</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.063</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.659549423777066</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
